--- a/public/templates/cs12.xlsx
+++ b/public/templates/cs12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB59A85-D47D-48D5-B258-17FAD13DC992}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629F4DCD-E967-4702-B643-AF583ECC201C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="39">
   <si>
     <t>Nº</t>
   </si>
@@ -163,7 +163,7 @@
     <numFmt numFmtId="166" formatCode="#.00"/>
     <numFmt numFmtId="167" formatCode="%#.00"/>
   </numFmts>
-  <fonts count="30" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +358,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1122,7 +1130,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1269,7 +1277,22 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1281,26 +1304,23 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1326,35 +1346,44 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="71">
@@ -1430,7 +1459,37 @@
     <cellStyle name="Title" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Warning Text" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1958,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CB52"/>
+  <dimension ref="A2:CR52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" customWidth="1"/>
@@ -1966,485 +2025,564 @@
     <col min="3" max="50" width="3.88671875" customWidth="1"/>
     <col min="51" max="51" width="3" customWidth="1"/>
     <col min="52" max="52" width="25.88671875" customWidth="1"/>
-    <col min="53" max="80" width="4.5546875" customWidth="1"/>
-    <col min="81" max="82" width="4.6640625" customWidth="1"/>
+    <col min="53" max="96" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A2" s="59" t="s">
+    <row r="2" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A2" s="56" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="E2" s="59"/>
-      <c r="F2" s="59"/>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
-      <c r="J2" s="59"/>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="59"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="59"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="59"/>
-      <c r="AR2" s="59"/>
-      <c r="AS2" s="59"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59" t="str">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="56"/>
+      <c r="AP2" s="56"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="56"/>
+      <c r="AU2" s="56"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56" t="str">
         <f>A2</f>
         <v>CENTRALIZADOR DE NOTAS</v>
       </c>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="59"/>
-      <c r="BB2" s="59"/>
-      <c r="BC2" s="59"/>
-      <c r="BD2" s="59"/>
-      <c r="BE2" s="59"/>
-      <c r="BF2" s="59"/>
-      <c r="BG2" s="59"/>
-      <c r="BH2" s="59"/>
-      <c r="BI2" s="59"/>
-      <c r="BJ2" s="59"/>
-      <c r="BK2" s="59"/>
-      <c r="BL2" s="59"/>
-      <c r="BM2" s="59"/>
-      <c r="BN2" s="59"/>
-      <c r="BO2" s="59"/>
-      <c r="BP2" s="59"/>
-      <c r="BQ2" s="59"/>
-      <c r="BR2" s="59"/>
-      <c r="BS2" s="59"/>
-      <c r="BT2" s="59"/>
-      <c r="BU2" s="59"/>
-      <c r="BV2" s="59"/>
-      <c r="BW2" s="59"/>
-      <c r="BX2" s="59"/>
-      <c r="BY2" s="59"/>
-      <c r="BZ2" s="59"/>
-      <c r="CA2" s="59"/>
-      <c r="CB2" s="59"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="56"/>
+      <c r="BC2" s="56"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="56"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="56"/>
+      <c r="BJ2" s="56"/>
+      <c r="BK2" s="56"/>
+      <c r="BL2" s="56"/>
+      <c r="BM2" s="56"/>
+      <c r="BN2" s="56"/>
+      <c r="BO2" s="56"/>
+      <c r="BP2" s="56"/>
+      <c r="BQ2" s="56"/>
+      <c r="BR2" s="56"/>
+      <c r="BS2" s="56"/>
+      <c r="BT2" s="56"/>
+      <c r="BU2" s="56"/>
+      <c r="BV2" s="56"/>
+      <c r="BW2" s="56"/>
+      <c r="BX2" s="56"/>
+      <c r="BY2" s="56"/>
+      <c r="BZ2" s="56"/>
+      <c r="CA2" s="56"/>
+      <c r="CB2" s="56"/>
+      <c r="CC2" s="56"/>
+      <c r="CD2" s="56"/>
+      <c r="CE2" s="56"/>
+      <c r="CF2" s="56"/>
+      <c r="CG2" s="56"/>
+      <c r="CH2" s="56"/>
+      <c r="CI2" s="56"/>
+      <c r="CJ2" s="56"/>
+      <c r="CK2" s="56"/>
+      <c r="CL2" s="56"/>
+      <c r="CM2" s="56"/>
+      <c r="CN2" s="56"/>
+      <c r="CO2" s="56"/>
+      <c r="CP2" s="56"/>
+      <c r="CQ2" s="56"/>
+      <c r="CR2" s="56"/>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A3" s="75" t="s">
+    <row r="3" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="75"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="75"/>
-      <c r="P3" s="75"/>
-      <c r="Q3" s="75"/>
-      <c r="R3" s="75"/>
-      <c r="S3" s="75"/>
-      <c r="T3" s="75"/>
-      <c r="U3" s="75"/>
-      <c r="V3" s="75"/>
-      <c r="W3" s="75"/>
-      <c r="X3" s="75"/>
-      <c r="Y3" s="75"/>
-      <c r="Z3" s="75"/>
-      <c r="AA3" s="75"/>
-      <c r="AB3" s="75"/>
-      <c r="AC3" s="75"/>
-      <c r="AD3" s="75"/>
-      <c r="AE3" s="75"/>
-      <c r="AF3" s="75"/>
-      <c r="AG3" s="75"/>
-      <c r="AH3" s="75"/>
-      <c r="AI3" s="75"/>
-      <c r="AJ3" s="75"/>
-      <c r="AK3" s="75"/>
-      <c r="AL3" s="75"/>
-      <c r="AM3" s="75"/>
-      <c r="AN3" s="75"/>
-      <c r="AO3" s="75"/>
-      <c r="AP3" s="75"/>
-      <c r="AQ3" s="75"/>
-      <c r="AR3" s="75"/>
-      <c r="AS3" s="75"/>
-      <c r="AT3" s="75"/>
-      <c r="AU3" s="75"/>
-      <c r="AV3" s="75"/>
-      <c r="AW3" s="75"/>
-      <c r="AX3" s="75"/>
-      <c r="AY3" s="59" t="str">
-        <f t="shared" ref="AY3:AY4" si="0">A3</f>
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="56" t="str">
+        <f>A3</f>
         <v>(CONSEJEROS Y DIRECCIONES TÉCNICAS)</v>
       </c>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="59"/>
-      <c r="BN3" s="59"/>
-      <c r="BO3" s="59"/>
-      <c r="BP3" s="59"/>
-      <c r="BQ3" s="59"/>
-      <c r="BR3" s="59"/>
-      <c r="BS3" s="59"/>
-      <c r="BT3" s="59"/>
-      <c r="BU3" s="59"/>
-      <c r="BV3" s="59"/>
-      <c r="BW3" s="59"/>
-      <c r="BX3" s="59"/>
-      <c r="BY3" s="59"/>
-      <c r="BZ3" s="59"/>
-      <c r="CA3" s="59"/>
-      <c r="CB3" s="59"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="56"/>
+      <c r="BD3" s="56"/>
+      <c r="BE3" s="56"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="56"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="56"/>
+      <c r="BL3" s="56"/>
+      <c r="BM3" s="56"/>
+      <c r="BN3" s="56"/>
+      <c r="BO3" s="56"/>
+      <c r="BP3" s="56"/>
+      <c r="BQ3" s="56"/>
+      <c r="BR3" s="56"/>
+      <c r="BS3" s="56"/>
+      <c r="BT3" s="56"/>
+      <c r="BU3" s="56"/>
+      <c r="BV3" s="56"/>
+      <c r="BW3" s="56"/>
+      <c r="BX3" s="56"/>
+      <c r="BY3" s="56"/>
+      <c r="BZ3" s="56"/>
+      <c r="CA3" s="56"/>
+      <c r="CB3" s="56"/>
+      <c r="CC3" s="56"/>
+      <c r="CD3" s="56"/>
+      <c r="CE3" s="56"/>
+      <c r="CF3" s="56"/>
+      <c r="CG3" s="56"/>
+      <c r="CH3" s="56"/>
+      <c r="CI3" s="56"/>
+      <c r="CJ3" s="56"/>
+      <c r="CK3" s="56"/>
+      <c r="CL3" s="56"/>
+      <c r="CM3" s="56"/>
+      <c r="CN3" s="56"/>
+      <c r="CO3" s="56"/>
+      <c r="CP3" s="56"/>
+      <c r="CQ3" s="56"/>
+      <c r="CR3" s="56"/>
     </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A4" s="76"/>
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="76"/>
-      <c r="K4" s="76"/>
-      <c r="L4" s="76"/>
-      <c r="M4" s="76"/>
-      <c r="N4" s="76"/>
-      <c r="O4" s="76"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="76"/>
-      <c r="R4" s="76"/>
-      <c r="S4" s="76"/>
-      <c r="T4" s="76"/>
-      <c r="U4" s="76"/>
-      <c r="V4" s="76"/>
-      <c r="W4" s="76"/>
-      <c r="X4" s="76"/>
-      <c r="Y4" s="76"/>
-      <c r="Z4" s="76"/>
-      <c r="AA4" s="76"/>
-      <c r="AB4" s="76"/>
-      <c r="AC4" s="76"/>
-      <c r="AD4" s="76"/>
-      <c r="AE4" s="76"/>
-      <c r="AF4" s="76"/>
-      <c r="AG4" s="76"/>
-      <c r="AH4" s="76"/>
-      <c r="AI4" s="76"/>
-      <c r="AJ4" s="76"/>
-      <c r="AK4" s="76"/>
-      <c r="AL4" s="76"/>
-      <c r="AM4" s="76"/>
-      <c r="AN4" s="76"/>
-      <c r="AO4" s="76"/>
-      <c r="AP4" s="76"/>
-      <c r="AQ4" s="76"/>
-      <c r="AR4" s="76"/>
-      <c r="AS4" s="76"/>
-      <c r="AT4" s="76"/>
-      <c r="AU4" s="76"/>
-      <c r="AV4" s="76"/>
-      <c r="AW4" s="76"/>
-      <c r="AX4" s="76"/>
-      <c r="AY4" s="59">
-        <f t="shared" si="0"/>
+    <row r="4" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58"/>
+      <c r="AE4" s="58"/>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="58"/>
+      <c r="AH4" s="58"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="58"/>
+      <c r="AR4" s="58"/>
+      <c r="AS4" s="58"/>
+      <c r="AT4" s="58"/>
+      <c r="AU4" s="58"/>
+      <c r="AV4" s="58"/>
+      <c r="AW4" s="58"/>
+      <c r="AX4" s="58"/>
+      <c r="AY4" s="56">
+        <f t="shared" ref="AY3:AY4" si="0">A4</f>
         <v>0</v>
       </c>
-      <c r="AZ4" s="59"/>
-      <c r="BA4" s="59"/>
-      <c r="BB4" s="59"/>
-      <c r="BC4" s="59"/>
-      <c r="BD4" s="59"/>
-      <c r="BE4" s="59"/>
-      <c r="BF4" s="59"/>
-      <c r="BG4" s="59"/>
-      <c r="BH4" s="59"/>
-      <c r="BI4" s="59"/>
-      <c r="BJ4" s="59"/>
-      <c r="BK4" s="59"/>
-      <c r="BL4" s="59"/>
-      <c r="BM4" s="59"/>
-      <c r="BN4" s="59"/>
-      <c r="BO4" s="59"/>
-      <c r="BP4" s="59"/>
-      <c r="BQ4" s="59"/>
-      <c r="BR4" s="59"/>
-      <c r="BS4" s="59"/>
-      <c r="BT4" s="59"/>
-      <c r="BU4" s="59"/>
-      <c r="BV4" s="59"/>
-      <c r="BW4" s="59"/>
-      <c r="BX4" s="59"/>
-      <c r="BY4" s="59"/>
-      <c r="BZ4" s="59"/>
-      <c r="CA4" s="59"/>
-      <c r="CB4" s="59"/>
+      <c r="AZ4" s="56"/>
+      <c r="BA4" s="56"/>
+      <c r="BB4" s="56"/>
+      <c r="BC4" s="56"/>
+      <c r="BD4" s="56"/>
+      <c r="BE4" s="56"/>
+      <c r="BF4" s="56"/>
+      <c r="BG4" s="56"/>
+      <c r="BH4" s="56"/>
+      <c r="BI4" s="56"/>
+      <c r="BJ4" s="56"/>
+      <c r="BK4" s="56"/>
+      <c r="BL4" s="56"/>
+      <c r="BM4" s="56"/>
+      <c r="BN4" s="56"/>
+      <c r="BO4" s="56"/>
+      <c r="BP4" s="56"/>
+      <c r="BQ4" s="56"/>
+      <c r="BR4" s="56"/>
+      <c r="BS4" s="56"/>
+      <c r="BT4" s="56"/>
+      <c r="BU4" s="56"/>
+      <c r="BV4" s="56"/>
+      <c r="BW4" s="56"/>
+      <c r="BX4" s="56"/>
+      <c r="BY4" s="56"/>
+      <c r="BZ4" s="56"/>
+      <c r="CA4" s="56"/>
+      <c r="CB4" s="56"/>
+      <c r="CC4" s="56"/>
+      <c r="CD4" s="56"/>
+      <c r="CE4" s="56"/>
+      <c r="CF4" s="56"/>
+      <c r="CG4" s="56"/>
+      <c r="CH4" s="56"/>
+      <c r="CI4" s="56"/>
+      <c r="CJ4" s="56"/>
+      <c r="CK4" s="56"/>
+      <c r="CL4" s="56"/>
+      <c r="CM4" s="56"/>
+      <c r="CN4" s="56"/>
+      <c r="CO4" s="56"/>
+      <c r="CP4" s="56"/>
+      <c r="CQ4" s="56"/>
+      <c r="CR4" s="56"/>
     </row>
-    <row r="5" spans="1:80" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="77"/>
-      <c r="B5" s="77"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="77"/>
-      <c r="H5" s="77"/>
-      <c r="I5" s="77"/>
-      <c r="J5" s="77"/>
-      <c r="K5" s="77"/>
-      <c r="L5" s="77"/>
-      <c r="M5" s="77"/>
-      <c r="N5" s="77"/>
-      <c r="O5" s="77"/>
-      <c r="P5" s="77"/>
-      <c r="Q5" s="77"/>
-      <c r="R5" s="77"/>
-      <c r="S5" s="77"/>
-      <c r="T5" s="77"/>
-      <c r="U5" s="77"/>
-      <c r="V5" s="77"/>
-      <c r="W5" s="77"/>
-      <c r="X5" s="77"/>
-      <c r="Y5" s="77"/>
-      <c r="Z5" s="77"/>
-      <c r="AA5" s="77"/>
-      <c r="AB5" s="77"/>
-      <c r="AC5" s="77"/>
-      <c r="AD5" s="77"/>
-      <c r="AE5" s="77"/>
-      <c r="AF5" s="77"/>
-      <c r="AG5" s="77"/>
-      <c r="AH5" s="77"/>
-      <c r="AI5" s="77"/>
-      <c r="AJ5" s="77"/>
-      <c r="AK5" s="77"/>
-      <c r="AL5" s="77"/>
-      <c r="AM5" s="77"/>
-      <c r="AN5" s="77"/>
-      <c r="AO5" s="77"/>
-      <c r="AP5" s="77"/>
-      <c r="AQ5" s="77"/>
-      <c r="AR5" s="77"/>
-      <c r="AS5" s="77"/>
-      <c r="AT5" s="77"/>
-      <c r="AU5" s="77"/>
-      <c r="AV5" s="77"/>
-      <c r="AW5" s="77"/>
-      <c r="AX5" s="77"/>
-      <c r="AY5" s="60">
+    <row r="5" spans="1:96" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="59"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="59"/>
+      <c r="AE5" s="59"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="80">
         <f>A5</f>
         <v>0</v>
       </c>
-      <c r="AZ5" s="60"/>
-      <c r="BA5" s="60"/>
-      <c r="BB5" s="60"/>
-      <c r="BC5" s="60"/>
-      <c r="BD5" s="60"/>
-      <c r="BE5" s="60"/>
-      <c r="BF5" s="60"/>
-      <c r="BG5" s="60"/>
-      <c r="BH5" s="60"/>
-      <c r="BI5" s="60"/>
-      <c r="BJ5" s="60"/>
-      <c r="BK5" s="60"/>
-      <c r="BL5" s="60"/>
-      <c r="BM5" s="60"/>
-      <c r="BN5" s="60"/>
-      <c r="BO5" s="60"/>
-      <c r="BP5" s="60"/>
-      <c r="BQ5" s="60"/>
-      <c r="BR5" s="60"/>
-      <c r="BS5" s="60"/>
-      <c r="BT5" s="60"/>
-      <c r="BU5" s="60"/>
-      <c r="BV5" s="60"/>
-      <c r="BW5" s="60"/>
-      <c r="BX5" s="60"/>
-      <c r="BY5" s="60"/>
-      <c r="BZ5" s="60"/>
-      <c r="CA5" s="60"/>
-      <c r="CB5" s="60"/>
+      <c r="AZ5" s="80"/>
+      <c r="BA5" s="80"/>
+      <c r="BB5" s="80"/>
+      <c r="BC5" s="80"/>
+      <c r="BD5" s="80"/>
+      <c r="BE5" s="80"/>
+      <c r="BF5" s="80"/>
+      <c r="BG5" s="80"/>
+      <c r="BH5" s="80"/>
+      <c r="BI5" s="80"/>
+      <c r="BJ5" s="80"/>
+      <c r="BK5" s="80"/>
+      <c r="BL5" s="80"/>
+      <c r="BM5" s="80"/>
+      <c r="BN5" s="80"/>
+      <c r="BO5" s="80"/>
+      <c r="BP5" s="80"/>
+      <c r="BQ5" s="80"/>
+      <c r="BR5" s="80"/>
+      <c r="BS5" s="80"/>
+      <c r="BT5" s="80"/>
+      <c r="BU5" s="80"/>
+      <c r="BV5" s="80"/>
+      <c r="BW5" s="80"/>
+      <c r="BX5" s="80"/>
+      <c r="BY5" s="80"/>
+      <c r="BZ5" s="80"/>
+      <c r="CA5" s="80"/>
+      <c r="CB5" s="80"/>
+      <c r="CC5" s="80"/>
+      <c r="CD5" s="80"/>
+      <c r="CE5" s="80"/>
+      <c r="CF5" s="80"/>
+      <c r="CG5" s="80"/>
+      <c r="CH5" s="80"/>
+      <c r="CI5" s="80"/>
+      <c r="CJ5" s="80"/>
+      <c r="CK5" s="80"/>
+      <c r="CL5" s="80"/>
+      <c r="CM5" s="80"/>
+      <c r="CN5" s="80"/>
+      <c r="CO5" s="80"/>
+      <c r="CP5" s="80"/>
+      <c r="CQ5" s="80"/>
+      <c r="CR5" s="80"/>
     </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A6" s="67" t="s">
+    <row r="6" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A6" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="69" t="s">
+      <c r="B6" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="56"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="55" t="s">
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="56"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="55" t="s">
+      <c r="H6" s="61"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="L6" s="56"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="55" t="s">
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="P6" s="56"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="55" t="s">
+      <c r="P6" s="61"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="T6" s="56"/>
-      <c r="U6" s="57"/>
-      <c r="V6" s="57"/>
-      <c r="W6" s="55" t="s">
+      <c r="T6" s="61"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="X6" s="56"/>
-      <c r="Y6" s="57"/>
-      <c r="Z6" s="78"/>
-      <c r="AA6" s="55" t="s">
+      <c r="X6" s="61"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="AB6" s="56"/>
-      <c r="AC6" s="57"/>
-      <c r="AD6" s="58"/>
-      <c r="AE6" s="55" t="s">
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="62"/>
+      <c r="AD6" s="64"/>
+      <c r="AE6" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="AF6" s="56"/>
-      <c r="AG6" s="57"/>
-      <c r="AH6" s="57"/>
-      <c r="AI6" s="55" t="s">
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="AJ6" s="56"/>
-      <c r="AK6" s="57"/>
-      <c r="AL6" s="57"/>
-      <c r="AM6" s="55" t="s">
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="62"/>
+      <c r="AM6" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="AN6" s="56"/>
-      <c r="AO6" s="57"/>
-      <c r="AP6" s="78"/>
-      <c r="AQ6" s="55" t="s">
+      <c r="AN6" s="61"/>
+      <c r="AO6" s="62"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="AR6" s="56"/>
-      <c r="AS6" s="57"/>
-      <c r="AT6" s="58"/>
-      <c r="AU6" s="79" t="s">
+      <c r="AR6" s="61"/>
+      <c r="AS6" s="62"/>
+      <c r="AT6" s="64"/>
+      <c r="AU6" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="AV6" s="80"/>
-      <c r="AW6" s="81"/>
-      <c r="AX6" s="82"/>
-      <c r="AY6" s="67" t="s">
+      <c r="AV6" s="66"/>
+      <c r="AW6" s="67"/>
+      <c r="AX6" s="68"/>
+      <c r="AY6" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="AZ6" s="69" t="s">
+      <c r="AZ6" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="BA6" s="61" t="s">
+      <c r="BA6" s="81" t="s">
         <v>16</v>
       </c>
-      <c r="BB6" s="54"/>
-      <c r="BC6" s="54"/>
-      <c r="BD6" s="54"/>
-      <c r="BE6" s="61" t="s">
+      <c r="BB6" s="79"/>
+      <c r="BC6" s="79"/>
+      <c r="BD6" s="79"/>
+      <c r="BE6" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="BF6" s="54"/>
-      <c r="BG6" s="54"/>
-      <c r="BH6" s="54"/>
-      <c r="BI6" s="55" t="s">
+      <c r="BF6" s="79"/>
+      <c r="BG6" s="79"/>
+      <c r="BH6" s="79"/>
+      <c r="BI6" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="BJ6" s="56"/>
-      <c r="BK6" s="57"/>
-      <c r="BL6" s="58"/>
-      <c r="BM6" s="61" t="s">
+      <c r="BJ6" s="61"/>
+      <c r="BK6" s="62"/>
+      <c r="BL6" s="64"/>
+      <c r="BM6" s="81" t="s">
         <v>6</v>
       </c>
-      <c r="BN6" s="54"/>
-      <c r="BO6" s="54"/>
-      <c r="BP6" s="54"/>
-      <c r="BQ6" s="61" t="s">
+      <c r="BN6" s="79"/>
+      <c r="BO6" s="79"/>
+      <c r="BP6" s="79"/>
+      <c r="BQ6" s="81" t="s">
         <v>32</v>
       </c>
-      <c r="BR6" s="54"/>
-      <c r="BS6" s="54"/>
-      <c r="BT6" s="62"/>
-      <c r="BU6" s="54" t="s">
+      <c r="BR6" s="79"/>
+      <c r="BS6" s="79"/>
+      <c r="BT6" s="82"/>
+      <c r="BU6" s="79" t="s">
         <v>33</v>
       </c>
-      <c r="BV6" s="54"/>
-      <c r="BW6" s="54"/>
-      <c r="BX6" s="54"/>
-      <c r="BY6" s="55" t="s">
+      <c r="BV6" s="79"/>
+      <c r="BW6" s="79"/>
+      <c r="BX6" s="79"/>
+      <c r="BY6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="BZ6" s="56"/>
-      <c r="CA6" s="57"/>
-      <c r="CB6" s="58"/>
+      <c r="BZ6" s="61"/>
+      <c r="CA6" s="62"/>
+      <c r="CB6" s="64"/>
+      <c r="CC6" s="81"/>
+      <c r="CD6" s="79"/>
+      <c r="CE6" s="79"/>
+      <c r="CF6" s="79"/>
+      <c r="CG6" s="81"/>
+      <c r="CH6" s="79"/>
+      <c r="CI6" s="79"/>
+      <c r="CJ6" s="82"/>
+      <c r="CK6" s="79"/>
+      <c r="CL6" s="79"/>
+      <c r="CM6" s="79"/>
+      <c r="CN6" s="79"/>
+      <c r="CO6" s="83"/>
+      <c r="CP6" s="84"/>
+      <c r="CQ6" s="85"/>
+      <c r="CR6" s="86"/>
     </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A7" s="68"/>
-      <c r="B7" s="70"/>
+    <row r="7" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A7" s="72"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="2" t="s">
         <v>24</v>
       </c>
@@ -2589,8 +2727,8 @@
       <c r="AX7" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="AY7" s="68"/>
-      <c r="AZ7" s="70"/>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="74"/>
       <c r="BA7" s="11" t="s">
         <v>24</v>
       </c>
@@ -2675,8 +2813,56 @@
       <c r="CB7" s="5" t="s">
         <v>27</v>
       </c>
+      <c r="CC7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="CD7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="CE7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CF7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CG7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="CH7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="CI7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CJ7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="CK7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="CL7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="CM7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CN7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="CO7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="CP7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="CQ7" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="CR7" s="15" t="s">
+        <v>27</v>
+      </c>
     </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A8" s="16">
         <v>1</v>
       </c>
@@ -2693,7 +2879,7 @@
         <v/>
       </c>
       <c r="H8" s="19" t="str">
-        <f t="shared" ref="F8:J23" si="2">IF(BJ8="","",BJ8)</f>
+        <f t="shared" ref="H8:J8" si="2">IF(BJ8="","",BJ8)</f>
         <v/>
       </c>
       <c r="I8" s="20" t="str">
@@ -2839,8 +3025,36 @@
         <f t="shared" ref="CB8:CB37" si="19">IF(SUM(BY8:CA8)=0,"",ROUND(AVERAGE(BY8:CA8),0))</f>
         <v/>
       </c>
+      <c r="CC8" s="29"/>
+      <c r="CD8" s="27"/>
+      <c r="CE8" s="28"/>
+      <c r="CF8" s="28" t="str">
+        <f t="shared" ref="CF8:CF37" si="20">IF(SUM(CC8:CE8)=0,"",ROUND(AVERAGE(CC8:CE8),0))</f>
+        <v/>
+      </c>
+      <c r="CG8" s="29"/>
+      <c r="CH8" s="27"/>
+      <c r="CI8" s="28"/>
+      <c r="CJ8" s="30" t="str">
+        <f t="shared" ref="CJ8:CJ37" si="21">IF(SUM(CG8:CI8)=0,"",ROUND(AVERAGE(CG8:CI8),0))</f>
+        <v/>
+      </c>
+      <c r="CK8" s="29"/>
+      <c r="CL8" s="27"/>
+      <c r="CM8" s="28"/>
+      <c r="CN8" s="28" t="str">
+        <f t="shared" ref="CN8:CN37" si="22">IF(SUM(CK8:CM8)=0,"",ROUND(AVERAGE(CK8:CM8),0))</f>
+        <v/>
+      </c>
+      <c r="CO8" s="29"/>
+      <c r="CP8" s="27"/>
+      <c r="CQ8" s="28"/>
+      <c r="CR8" s="87" t="str">
+        <f t="shared" ref="CR8:CR37" si="23">IF(SUM(CO8:CQ8)=0,"",ROUND(AVERAGE(CO8:CQ8),0))</f>
+        <v/>
+      </c>
     </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A9" s="31">
         <v>2</v>
       </c>
@@ -2853,19 +3067,19 @@
         <v/>
       </c>
       <c r="G9" s="33" t="str">
-        <f t="shared" ref="G9:G37" si="20">IF(BI9="","",BI9)</f>
+        <f t="shared" ref="G9:G37" si="24">IF(BI9="","",BI9)</f>
         <v/>
       </c>
       <c r="H9" s="34" t="str">
-        <f t="shared" ref="H9:H37" si="21">IF(BJ9="","",BJ9)</f>
+        <f t="shared" ref="H9:H37" si="25">IF(BJ9="","",BJ9)</f>
         <v/>
       </c>
       <c r="I9" s="35" t="str">
-        <f t="shared" ref="I9:I37" si="22">IF(BK9="","",BK9)</f>
+        <f t="shared" ref="I9:I37" si="26">IF(BK9="","",BK9)</f>
         <v/>
       </c>
       <c r="J9" s="36" t="str">
-        <f t="shared" ref="J9:J37" si="23">IF(BL9="","",BL9)</f>
+        <f t="shared" ref="J9:J37" si="27">IF(BL9="","",BL9)</f>
         <v/>
       </c>
       <c r="K9" s="33"/>
@@ -2911,7 +3125,7 @@
         <v/>
       </c>
       <c r="AI9" s="33" t="str">
-        <f t="shared" ref="AI9:AI37" si="24">IF(BY9="","",BY9)</f>
+        <f t="shared" ref="AI9:AI37" si="28">IF(BY9="","",BY9)</f>
         <v/>
       </c>
       <c r="AJ9" s="34" t="str">
@@ -2951,7 +3165,7 @@
         <v>2</v>
       </c>
       <c r="AZ9" s="32" t="str">
-        <f t="shared" ref="AZ9:AZ37" si="25">IF(B9="","",B9)</f>
+        <f t="shared" ref="AZ9:AZ37" si="29">IF(B9="","",B9)</f>
         <v/>
       </c>
       <c r="BA9" s="40"/>
@@ -3003,8 +3217,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC9" s="40"/>
+      <c r="CD9" s="38"/>
+      <c r="CE9" s="39"/>
+      <c r="CF9" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG9" s="40"/>
+      <c r="CH9" s="38"/>
+      <c r="CI9" s="39"/>
+      <c r="CJ9" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK9" s="40"/>
+      <c r="CL9" s="38"/>
+      <c r="CM9" s="39"/>
+      <c r="CN9" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO9" s="40"/>
+      <c r="CP9" s="38"/>
+      <c r="CQ9" s="39"/>
+      <c r="CR9" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A10" s="31">
         <v>3</v>
       </c>
@@ -3017,19 +3259,19 @@
         <v/>
       </c>
       <c r="G10" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H10" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I10" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J10" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K10" s="33"/>
@@ -3075,7 +3317,7 @@
         <v/>
       </c>
       <c r="AI10" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ10" s="34" t="str">
@@ -3115,7 +3357,7 @@
         <v>3</v>
       </c>
       <c r="AZ10" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA10" s="40"/>
@@ -3167,8 +3409,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC10" s="40"/>
+      <c r="CD10" s="38"/>
+      <c r="CE10" s="39"/>
+      <c r="CF10" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG10" s="40"/>
+      <c r="CH10" s="38"/>
+      <c r="CI10" s="39"/>
+      <c r="CJ10" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK10" s="40"/>
+      <c r="CL10" s="38"/>
+      <c r="CM10" s="39"/>
+      <c r="CN10" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO10" s="40"/>
+      <c r="CP10" s="38"/>
+      <c r="CQ10" s="39"/>
+      <c r="CR10" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A11" s="31">
         <v>4</v>
       </c>
@@ -3181,19 +3451,19 @@
         <v/>
       </c>
       <c r="G11" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H11" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I11" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J11" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K11" s="33"/>
@@ -3239,7 +3509,7 @@
         <v/>
       </c>
       <c r="AI11" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ11" s="34" t="str">
@@ -3279,7 +3549,7 @@
         <v>4</v>
       </c>
       <c r="AZ11" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA11" s="40"/>
@@ -3331,8 +3601,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC11" s="40"/>
+      <c r="CD11" s="38"/>
+      <c r="CE11" s="39"/>
+      <c r="CF11" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG11" s="40"/>
+      <c r="CH11" s="38"/>
+      <c r="CI11" s="39"/>
+      <c r="CJ11" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK11" s="40"/>
+      <c r="CL11" s="38"/>
+      <c r="CM11" s="39"/>
+      <c r="CN11" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO11" s="40"/>
+      <c r="CP11" s="38"/>
+      <c r="CQ11" s="39"/>
+      <c r="CR11" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A12" s="31">
         <v>5</v>
       </c>
@@ -3345,19 +3643,19 @@
         <v/>
       </c>
       <c r="G12" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H12" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I12" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J12" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K12" s="33"/>
@@ -3403,7 +3701,7 @@
         <v/>
       </c>
       <c r="AI12" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ12" s="34" t="str">
@@ -3443,7 +3741,7 @@
         <v>5</v>
       </c>
       <c r="AZ12" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA12" s="40"/>
@@ -3495,8 +3793,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC12" s="40"/>
+      <c r="CD12" s="38"/>
+      <c r="CE12" s="39"/>
+      <c r="CF12" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG12" s="40"/>
+      <c r="CH12" s="38"/>
+      <c r="CI12" s="39"/>
+      <c r="CJ12" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK12" s="40"/>
+      <c r="CL12" s="38"/>
+      <c r="CM12" s="39"/>
+      <c r="CN12" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO12" s="40"/>
+      <c r="CP12" s="38"/>
+      <c r="CQ12" s="39"/>
+      <c r="CR12" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A13" s="31">
         <v>6</v>
       </c>
@@ -3509,19 +3835,19 @@
         <v/>
       </c>
       <c r="G13" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H13" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I13" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J13" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K13" s="33"/>
@@ -3567,7 +3893,7 @@
         <v/>
       </c>
       <c r="AI13" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ13" s="34" t="str">
@@ -3607,7 +3933,7 @@
         <v>6</v>
       </c>
       <c r="AZ13" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA13" s="40"/>
@@ -3659,8 +3985,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC13" s="40"/>
+      <c r="CD13" s="38"/>
+      <c r="CE13" s="39"/>
+      <c r="CF13" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG13" s="40"/>
+      <c r="CH13" s="38"/>
+      <c r="CI13" s="39"/>
+      <c r="CJ13" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK13" s="40"/>
+      <c r="CL13" s="38"/>
+      <c r="CM13" s="39"/>
+      <c r="CN13" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO13" s="40"/>
+      <c r="CP13" s="38"/>
+      <c r="CQ13" s="39"/>
+      <c r="CR13" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A14" s="31">
         <v>7</v>
       </c>
@@ -3673,19 +4027,19 @@
         <v/>
       </c>
       <c r="G14" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H14" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I14" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J14" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K14" s="33"/>
@@ -3731,7 +4085,7 @@
         <v/>
       </c>
       <c r="AI14" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ14" s="34" t="str">
@@ -3771,7 +4125,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA14" s="40"/>
@@ -3823,8 +4177,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC14" s="40"/>
+      <c r="CD14" s="38"/>
+      <c r="CE14" s="39"/>
+      <c r="CF14" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG14" s="40"/>
+      <c r="CH14" s="38"/>
+      <c r="CI14" s="39"/>
+      <c r="CJ14" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK14" s="40"/>
+      <c r="CL14" s="38"/>
+      <c r="CM14" s="39"/>
+      <c r="CN14" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO14" s="40"/>
+      <c r="CP14" s="38"/>
+      <c r="CQ14" s="39"/>
+      <c r="CR14" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A15" s="31">
         <v>8</v>
       </c>
@@ -3837,19 +4219,19 @@
         <v/>
       </c>
       <c r="G15" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H15" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I15" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J15" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K15" s="33"/>
@@ -3895,7 +4277,7 @@
         <v/>
       </c>
       <c r="AI15" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ15" s="34" t="str">
@@ -3935,7 +4317,7 @@
         <v>8</v>
       </c>
       <c r="AZ15" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA15" s="40"/>
@@ -3987,8 +4369,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC15" s="40"/>
+      <c r="CD15" s="38"/>
+      <c r="CE15" s="39"/>
+      <c r="CF15" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG15" s="40"/>
+      <c r="CH15" s="38"/>
+      <c r="CI15" s="39"/>
+      <c r="CJ15" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK15" s="40"/>
+      <c r="CL15" s="38"/>
+      <c r="CM15" s="39"/>
+      <c r="CN15" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO15" s="40"/>
+      <c r="CP15" s="38"/>
+      <c r="CQ15" s="39"/>
+      <c r="CR15" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A16" s="31">
         <v>9</v>
       </c>
@@ -4001,19 +4411,19 @@
         <v/>
       </c>
       <c r="G16" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H16" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I16" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J16" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K16" s="33"/>
@@ -4059,7 +4469,7 @@
         <v/>
       </c>
       <c r="AI16" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ16" s="34" t="str">
@@ -4099,7 +4509,7 @@
         <v>9</v>
       </c>
       <c r="AZ16" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA16" s="40"/>
@@ -4151,8 +4561,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC16" s="40"/>
+      <c r="CD16" s="38"/>
+      <c r="CE16" s="39"/>
+      <c r="CF16" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG16" s="40"/>
+      <c r="CH16" s="38"/>
+      <c r="CI16" s="39"/>
+      <c r="CJ16" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK16" s="40"/>
+      <c r="CL16" s="38"/>
+      <c r="CM16" s="39"/>
+      <c r="CN16" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO16" s="40"/>
+      <c r="CP16" s="38"/>
+      <c r="CQ16" s="39"/>
+      <c r="CR16" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="17" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A17" s="31">
         <v>10</v>
       </c>
@@ -4165,19 +4603,19 @@
         <v/>
       </c>
       <c r="G17" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H17" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I17" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J17" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K17" s="33"/>
@@ -4223,7 +4661,7 @@
         <v/>
       </c>
       <c r="AI17" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ17" s="34" t="str">
@@ -4263,7 +4701,7 @@
         <v>10</v>
       </c>
       <c r="AZ17" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA17" s="40"/>
@@ -4315,8 +4753,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC17" s="40"/>
+      <c r="CD17" s="38"/>
+      <c r="CE17" s="39"/>
+      <c r="CF17" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG17" s="40"/>
+      <c r="CH17" s="38"/>
+      <c r="CI17" s="39"/>
+      <c r="CJ17" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK17" s="40"/>
+      <c r="CL17" s="38"/>
+      <c r="CM17" s="39"/>
+      <c r="CN17" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO17" s="40"/>
+      <c r="CP17" s="38"/>
+      <c r="CQ17" s="39"/>
+      <c r="CR17" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="18" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A18" s="31">
         <v>11</v>
       </c>
@@ -4329,19 +4795,19 @@
         <v/>
       </c>
       <c r="G18" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H18" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I18" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J18" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K18" s="33"/>
@@ -4387,7 +4853,7 @@
         <v/>
       </c>
       <c r="AI18" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ18" s="34" t="str">
@@ -4427,7 +4893,7 @@
         <v>11</v>
       </c>
       <c r="AZ18" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA18" s="40"/>
@@ -4479,8 +4945,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC18" s="40"/>
+      <c r="CD18" s="38"/>
+      <c r="CE18" s="39"/>
+      <c r="CF18" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG18" s="40"/>
+      <c r="CH18" s="38"/>
+      <c r="CI18" s="39"/>
+      <c r="CJ18" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK18" s="40"/>
+      <c r="CL18" s="38"/>
+      <c r="CM18" s="39"/>
+      <c r="CN18" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO18" s="40"/>
+      <c r="CP18" s="38"/>
+      <c r="CQ18" s="39"/>
+      <c r="CR18" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="19" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A19" s="31">
         <v>12</v>
       </c>
@@ -4493,19 +4987,19 @@
         <v/>
       </c>
       <c r="G19" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H19" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I19" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J19" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K19" s="33"/>
@@ -4551,7 +5045,7 @@
         <v/>
       </c>
       <c r="AI19" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ19" s="34" t="str">
@@ -4591,7 +5085,7 @@
         <v>12</v>
       </c>
       <c r="AZ19" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA19" s="40"/>
@@ -4643,8 +5137,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC19" s="40"/>
+      <c r="CD19" s="38"/>
+      <c r="CE19" s="39"/>
+      <c r="CF19" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG19" s="40"/>
+      <c r="CH19" s="38"/>
+      <c r="CI19" s="39"/>
+      <c r="CJ19" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK19" s="40"/>
+      <c r="CL19" s="38"/>
+      <c r="CM19" s="39"/>
+      <c r="CN19" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO19" s="40"/>
+      <c r="CP19" s="38"/>
+      <c r="CQ19" s="39"/>
+      <c r="CR19" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="20" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A20" s="31">
         <v>13</v>
       </c>
@@ -4657,19 +5179,19 @@
         <v/>
       </c>
       <c r="G20" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H20" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I20" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J20" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K20" s="33"/>
@@ -4715,7 +5237,7 @@
         <v/>
       </c>
       <c r="AI20" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ20" s="34" t="str">
@@ -4755,7 +5277,7 @@
         <v>13</v>
       </c>
       <c r="AZ20" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA20" s="40"/>
@@ -4807,8 +5329,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC20" s="40"/>
+      <c r="CD20" s="38"/>
+      <c r="CE20" s="39"/>
+      <c r="CF20" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG20" s="40"/>
+      <c r="CH20" s="38"/>
+      <c r="CI20" s="39"/>
+      <c r="CJ20" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK20" s="40"/>
+      <c r="CL20" s="38"/>
+      <c r="CM20" s="39"/>
+      <c r="CN20" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO20" s="40"/>
+      <c r="CP20" s="38"/>
+      <c r="CQ20" s="39"/>
+      <c r="CR20" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="21" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A21" s="31">
         <v>14</v>
       </c>
@@ -4821,19 +5371,19 @@
         <v/>
       </c>
       <c r="G21" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H21" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I21" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J21" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K21" s="33"/>
@@ -4879,7 +5429,7 @@
         <v/>
       </c>
       <c r="AI21" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ21" s="34" t="str">
@@ -4919,7 +5469,7 @@
         <v>14</v>
       </c>
       <c r="AZ21" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA21" s="40"/>
@@ -4971,8 +5521,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC21" s="40"/>
+      <c r="CD21" s="38"/>
+      <c r="CE21" s="39"/>
+      <c r="CF21" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG21" s="40"/>
+      <c r="CH21" s="38"/>
+      <c r="CI21" s="39"/>
+      <c r="CJ21" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK21" s="40"/>
+      <c r="CL21" s="38"/>
+      <c r="CM21" s="39"/>
+      <c r="CN21" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO21" s="40"/>
+      <c r="CP21" s="38"/>
+      <c r="CQ21" s="39"/>
+      <c r="CR21" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="22" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A22" s="31">
         <v>15</v>
       </c>
@@ -4985,19 +5563,19 @@
         <v/>
       </c>
       <c r="G22" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H22" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I22" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J22" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K22" s="33"/>
@@ -5043,7 +5621,7 @@
         <v/>
       </c>
       <c r="AI22" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ22" s="34" t="str">
@@ -5083,7 +5661,7 @@
         <v>15</v>
       </c>
       <c r="AZ22" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA22" s="40"/>
@@ -5135,8 +5713,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC22" s="40"/>
+      <c r="CD22" s="38"/>
+      <c r="CE22" s="39"/>
+      <c r="CF22" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG22" s="40"/>
+      <c r="CH22" s="38"/>
+      <c r="CI22" s="39"/>
+      <c r="CJ22" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK22" s="40"/>
+      <c r="CL22" s="38"/>
+      <c r="CM22" s="39"/>
+      <c r="CN22" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO22" s="40"/>
+      <c r="CP22" s="38"/>
+      <c r="CQ22" s="39"/>
+      <c r="CR22" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="23" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A23" s="31">
         <v>16</v>
       </c>
@@ -5149,19 +5755,19 @@
         <v/>
       </c>
       <c r="G23" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H23" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I23" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J23" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K23" s="33"/>
@@ -5207,7 +5813,7 @@
         <v/>
       </c>
       <c r="AI23" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ23" s="34" t="str">
@@ -5247,7 +5853,7 @@
         <v>16</v>
       </c>
       <c r="AZ23" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA23" s="40"/>
@@ -5299,8 +5905,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC23" s="40"/>
+      <c r="CD23" s="38"/>
+      <c r="CE23" s="39"/>
+      <c r="CF23" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG23" s="40"/>
+      <c r="CH23" s="38"/>
+      <c r="CI23" s="39"/>
+      <c r="CJ23" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK23" s="40"/>
+      <c r="CL23" s="38"/>
+      <c r="CM23" s="39"/>
+      <c r="CN23" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO23" s="40"/>
+      <c r="CP23" s="38"/>
+      <c r="CQ23" s="39"/>
+      <c r="CR23" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="24" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A24" s="31">
         <v>17</v>
       </c>
@@ -5313,19 +5947,19 @@
         <v/>
       </c>
       <c r="G24" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H24" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I24" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J24" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K24" s="33"/>
@@ -5371,19 +6005,19 @@
         <v/>
       </c>
       <c r="AI24" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ24" s="34" t="str">
-        <f t="shared" ref="AJ24:AJ37" si="26">IF(BZ24="","",BZ24)</f>
+        <f t="shared" ref="AJ24:AJ37" si="30">IF(BZ24="","",BZ24)</f>
         <v/>
       </c>
       <c r="AK24" s="35" t="str">
-        <f t="shared" ref="AK24:AK37" si="27">IF(CA24="","",CA24)</f>
+        <f t="shared" ref="AK24:AK37" si="31">IF(CA24="","",CA24)</f>
         <v/>
       </c>
       <c r="AL24" s="35" t="str">
-        <f t="shared" ref="AL24:AL37" si="28">IF(CB24="","",CB24)</f>
+        <f t="shared" ref="AL24:AL37" si="32">IF(CB24="","",CB24)</f>
         <v/>
       </c>
       <c r="AM24" s="33"/>
@@ -5411,7 +6045,7 @@
         <v>17</v>
       </c>
       <c r="AZ24" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA24" s="40"/>
@@ -5463,8 +6097,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC24" s="40"/>
+      <c r="CD24" s="38"/>
+      <c r="CE24" s="39"/>
+      <c r="CF24" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG24" s="40"/>
+      <c r="CH24" s="38"/>
+      <c r="CI24" s="39"/>
+      <c r="CJ24" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK24" s="40"/>
+      <c r="CL24" s="38"/>
+      <c r="CM24" s="39"/>
+      <c r="CN24" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO24" s="40"/>
+      <c r="CP24" s="38"/>
+      <c r="CQ24" s="39"/>
+      <c r="CR24" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="25" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A25" s="31">
         <v>18</v>
       </c>
@@ -5477,19 +6139,19 @@
         <v/>
       </c>
       <c r="G25" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H25" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I25" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J25" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K25" s="33"/>
@@ -5535,19 +6197,19 @@
         <v/>
       </c>
       <c r="AI25" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ25" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK25" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL25" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM25" s="33"/>
@@ -5575,7 +6237,7 @@
         <v>18</v>
       </c>
       <c r="AZ25" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA25" s="40"/>
@@ -5627,8 +6289,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC25" s="40"/>
+      <c r="CD25" s="38"/>
+      <c r="CE25" s="39"/>
+      <c r="CF25" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG25" s="40"/>
+      <c r="CH25" s="38"/>
+      <c r="CI25" s="39"/>
+      <c r="CJ25" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK25" s="40"/>
+      <c r="CL25" s="38"/>
+      <c r="CM25" s="39"/>
+      <c r="CN25" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO25" s="40"/>
+      <c r="CP25" s="38"/>
+      <c r="CQ25" s="39"/>
+      <c r="CR25" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="26" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A26" s="31">
         <v>19</v>
       </c>
@@ -5641,19 +6331,19 @@
         <v/>
       </c>
       <c r="G26" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H26" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I26" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J26" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K26" s="33"/>
@@ -5699,19 +6389,19 @@
         <v/>
       </c>
       <c r="AI26" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ26" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK26" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL26" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM26" s="33"/>
@@ -5739,7 +6429,7 @@
         <v>19</v>
       </c>
       <c r="AZ26" s="46" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA26" s="40"/>
@@ -5791,8 +6481,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC26" s="40"/>
+      <c r="CD26" s="38"/>
+      <c r="CE26" s="39"/>
+      <c r="CF26" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG26" s="40"/>
+      <c r="CH26" s="38"/>
+      <c r="CI26" s="39"/>
+      <c r="CJ26" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK26" s="40"/>
+      <c r="CL26" s="38"/>
+      <c r="CM26" s="39"/>
+      <c r="CN26" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO26" s="40"/>
+      <c r="CP26" s="38"/>
+      <c r="CQ26" s="39"/>
+      <c r="CR26" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="27" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A27" s="31">
         <v>20</v>
       </c>
@@ -5805,19 +6523,19 @@
         <v/>
       </c>
       <c r="G27" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H27" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I27" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J27" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K27" s="33"/>
@@ -5863,19 +6581,19 @@
         <v/>
       </c>
       <c r="AI27" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ27" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK27" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL27" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM27" s="33"/>
@@ -5903,7 +6621,7 @@
         <v>20</v>
       </c>
       <c r="AZ27" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA27" s="40"/>
@@ -5955,8 +6673,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC27" s="40"/>
+      <c r="CD27" s="38"/>
+      <c r="CE27" s="39"/>
+      <c r="CF27" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG27" s="40"/>
+      <c r="CH27" s="38"/>
+      <c r="CI27" s="39"/>
+      <c r="CJ27" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK27" s="40"/>
+      <c r="CL27" s="38"/>
+      <c r="CM27" s="39"/>
+      <c r="CN27" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO27" s="40"/>
+      <c r="CP27" s="38"/>
+      <c r="CQ27" s="39"/>
+      <c r="CR27" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="28" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A28" s="31">
         <v>21</v>
       </c>
@@ -5969,19 +6715,19 @@
         <v/>
       </c>
       <c r="G28" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H28" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I28" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J28" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K28" s="33"/>
@@ -6027,19 +6773,19 @@
         <v/>
       </c>
       <c r="AI28" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ28" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK28" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL28" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM28" s="33"/>
@@ -6067,7 +6813,7 @@
         <v>21</v>
       </c>
       <c r="AZ28" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA28" s="40"/>
@@ -6119,8 +6865,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC28" s="40"/>
+      <c r="CD28" s="38"/>
+      <c r="CE28" s="39"/>
+      <c r="CF28" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG28" s="40"/>
+      <c r="CH28" s="38"/>
+      <c r="CI28" s="39"/>
+      <c r="CJ28" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK28" s="40"/>
+      <c r="CL28" s="38"/>
+      <c r="CM28" s="39"/>
+      <c r="CN28" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO28" s="40"/>
+      <c r="CP28" s="38"/>
+      <c r="CQ28" s="39"/>
+      <c r="CR28" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="29" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A29" s="31">
         <v>22</v>
       </c>
@@ -6133,19 +6907,19 @@
         <v/>
       </c>
       <c r="G29" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H29" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I29" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J29" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K29" s="33"/>
@@ -6191,19 +6965,19 @@
         <v/>
       </c>
       <c r="AI29" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ29" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK29" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL29" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM29" s="33"/>
@@ -6231,7 +7005,7 @@
         <v>22</v>
       </c>
       <c r="AZ29" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA29" s="40"/>
@@ -6257,7 +7031,7 @@
       </c>
       <c r="BM29" s="40"/>
       <c r="BN29" s="38"/>
-      <c r="BO29" s="39"/>
+      <c r="BO29" s="89"/>
       <c r="BP29" s="39" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -6283,8 +7057,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC29" s="40"/>
+      <c r="CD29" s="38"/>
+      <c r="CE29" s="39"/>
+      <c r="CF29" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG29" s="40"/>
+      <c r="CH29" s="38"/>
+      <c r="CI29" s="39"/>
+      <c r="CJ29" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK29" s="40"/>
+      <c r="CL29" s="38"/>
+      <c r="CM29" s="39"/>
+      <c r="CN29" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO29" s="40"/>
+      <c r="CP29" s="38"/>
+      <c r="CQ29" s="39"/>
+      <c r="CR29" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="30" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A30" s="31">
         <v>23</v>
       </c>
@@ -6297,19 +7099,19 @@
         <v/>
       </c>
       <c r="G30" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H30" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I30" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J30" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K30" s="33"/>
@@ -6355,19 +7157,19 @@
         <v/>
       </c>
       <c r="AI30" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ30" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK30" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL30" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM30" s="33"/>
@@ -6395,7 +7197,7 @@
         <v>23</v>
       </c>
       <c r="AZ30" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA30" s="40"/>
@@ -6447,8 +7249,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC30" s="40"/>
+      <c r="CD30" s="38"/>
+      <c r="CE30" s="39"/>
+      <c r="CF30" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG30" s="40"/>
+      <c r="CH30" s="38"/>
+      <c r="CI30" s="39"/>
+      <c r="CJ30" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK30" s="40"/>
+      <c r="CL30" s="38"/>
+      <c r="CM30" s="39"/>
+      <c r="CN30" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO30" s="40"/>
+      <c r="CP30" s="38"/>
+      <c r="CQ30" s="39"/>
+      <c r="CR30" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="31" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A31" s="31">
         <v>24</v>
       </c>
@@ -6461,19 +7291,19 @@
         <v/>
       </c>
       <c r="G31" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H31" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I31" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J31" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K31" s="33"/>
@@ -6519,19 +7349,19 @@
         <v/>
       </c>
       <c r="AI31" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ31" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK31" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL31" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM31" s="33"/>
@@ -6559,7 +7389,7 @@
         <v>24</v>
       </c>
       <c r="AZ31" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA31" s="40"/>
@@ -6611,8 +7441,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC31" s="40"/>
+      <c r="CD31" s="38"/>
+      <c r="CE31" s="39"/>
+      <c r="CF31" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG31" s="40"/>
+      <c r="CH31" s="38"/>
+      <c r="CI31" s="39"/>
+      <c r="CJ31" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK31" s="40"/>
+      <c r="CL31" s="38"/>
+      <c r="CM31" s="39"/>
+      <c r="CN31" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO31" s="40"/>
+      <c r="CP31" s="38"/>
+      <c r="CQ31" s="39"/>
+      <c r="CR31" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="32" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A32" s="31">
         <v>25</v>
       </c>
@@ -6625,19 +7483,19 @@
         <v/>
       </c>
       <c r="G32" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H32" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I32" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J32" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K32" s="33"/>
@@ -6683,19 +7541,19 @@
         <v/>
       </c>
       <c r="AI32" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ32" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK32" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL32" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM32" s="33"/>
@@ -6723,7 +7581,7 @@
         <v>25</v>
       </c>
       <c r="AZ32" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA32" s="40"/>
@@ -6775,8 +7633,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC32" s="40"/>
+      <c r="CD32" s="38"/>
+      <c r="CE32" s="39"/>
+      <c r="CF32" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG32" s="40"/>
+      <c r="CH32" s="38"/>
+      <c r="CI32" s="39"/>
+      <c r="CJ32" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK32" s="40"/>
+      <c r="CL32" s="38"/>
+      <c r="CM32" s="39"/>
+      <c r="CN32" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO32" s="40"/>
+      <c r="CP32" s="38"/>
+      <c r="CQ32" s="39"/>
+      <c r="CR32" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="33" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A33" s="31">
         <v>26</v>
       </c>
@@ -6789,19 +7675,19 @@
         <v/>
       </c>
       <c r="G33" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H33" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I33" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J33" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K33" s="33"/>
@@ -6847,19 +7733,19 @@
         <v/>
       </c>
       <c r="AI33" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ33" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK33" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL33" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM33" s="33"/>
@@ -6887,7 +7773,7 @@
         <v>26</v>
       </c>
       <c r="AZ33" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA33" s="40"/>
@@ -6939,8 +7825,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC33" s="40"/>
+      <c r="CD33" s="38"/>
+      <c r="CE33" s="39"/>
+      <c r="CF33" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG33" s="40"/>
+      <c r="CH33" s="38"/>
+      <c r="CI33" s="39"/>
+      <c r="CJ33" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK33" s="40"/>
+      <c r="CL33" s="38"/>
+      <c r="CM33" s="39"/>
+      <c r="CN33" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO33" s="40"/>
+      <c r="CP33" s="38"/>
+      <c r="CQ33" s="39"/>
+      <c r="CR33" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="34" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A34" s="31">
         <v>27</v>
       </c>
@@ -6953,19 +7867,19 @@
         <v/>
       </c>
       <c r="G34" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H34" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I34" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J34" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K34" s="33"/>
@@ -7011,19 +7925,19 @@
         <v/>
       </c>
       <c r="AI34" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ34" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK34" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL34" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM34" s="33"/>
@@ -7051,7 +7965,7 @@
         <v>27</v>
       </c>
       <c r="AZ34" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA34" s="40"/>
@@ -7103,8 +8017,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC34" s="40"/>
+      <c r="CD34" s="38"/>
+      <c r="CE34" s="39"/>
+      <c r="CF34" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG34" s="40"/>
+      <c r="CH34" s="38"/>
+      <c r="CI34" s="39"/>
+      <c r="CJ34" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK34" s="40"/>
+      <c r="CL34" s="38"/>
+      <c r="CM34" s="39"/>
+      <c r="CN34" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO34" s="40"/>
+      <c r="CP34" s="38"/>
+      <c r="CQ34" s="39"/>
+      <c r="CR34" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="35" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A35" s="31">
         <v>28</v>
       </c>
@@ -7117,19 +8059,19 @@
         <v/>
       </c>
       <c r="G35" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H35" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I35" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J35" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K35" s="33"/>
@@ -7175,19 +8117,19 @@
         <v/>
       </c>
       <c r="AI35" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ35" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK35" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL35" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM35" s="33"/>
@@ -7215,7 +8157,7 @@
         <v>28</v>
       </c>
       <c r="AZ35" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA35" s="40"/>
@@ -7267,8 +8209,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC35" s="40"/>
+      <c r="CD35" s="38"/>
+      <c r="CE35" s="39"/>
+      <c r="CF35" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG35" s="40"/>
+      <c r="CH35" s="38"/>
+      <c r="CI35" s="39"/>
+      <c r="CJ35" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK35" s="40"/>
+      <c r="CL35" s="38"/>
+      <c r="CM35" s="39"/>
+      <c r="CN35" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO35" s="40"/>
+      <c r="CP35" s="38"/>
+      <c r="CQ35" s="39"/>
+      <c r="CR35" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="36" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A36" s="31">
         <v>29</v>
       </c>
@@ -7281,19 +8251,19 @@
         <v/>
       </c>
       <c r="G36" s="33" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H36" s="34" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I36" s="35" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J36" s="36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K36" s="33"/>
@@ -7339,19 +8309,19 @@
         <v/>
       </c>
       <c r="AI36" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ36" s="34" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK36" s="35" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL36" s="35" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM36" s="33"/>
@@ -7379,7 +8349,7 @@
         <v>29</v>
       </c>
       <c r="AZ36" s="32" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA36" s="40"/>
@@ -7431,8 +8401,36 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC36" s="40"/>
+      <c r="CD36" s="38"/>
+      <c r="CE36" s="39"/>
+      <c r="CF36" s="39" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG36" s="40"/>
+      <c r="CH36" s="38"/>
+      <c r="CI36" s="39"/>
+      <c r="CJ36" s="41" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK36" s="40"/>
+      <c r="CL36" s="38"/>
+      <c r="CM36" s="39"/>
+      <c r="CN36" s="39" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO36" s="40"/>
+      <c r="CP36" s="38"/>
+      <c r="CQ36" s="39"/>
+      <c r="CR36" s="88" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="37" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A37" s="47">
         <v>30</v>
       </c>
@@ -7445,19 +8443,19 @@
         <v/>
       </c>
       <c r="G37" s="2" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="H37" s="3" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="I37" s="4" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="J37" s="5" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="K37" s="2"/>
@@ -7503,19 +8501,19 @@
         <v/>
       </c>
       <c r="AI37" s="2" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="AJ37" s="3" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="AK37" s="4" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="AL37" s="4" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM37" s="2"/>
@@ -7543,7 +8541,7 @@
         <v>30</v>
       </c>
       <c r="AZ37" s="48" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="BA37" s="13"/>
@@ -7595,806 +8593,962 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
+      <c r="CC37" s="13"/>
+      <c r="CD37" s="11"/>
+      <c r="CE37" s="12"/>
+      <c r="CF37" s="12" t="str">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="CG37" s="13"/>
+      <c r="CH37" s="11"/>
+      <c r="CI37" s="12"/>
+      <c r="CJ37" s="14" t="str">
+        <f t="shared" si="21"/>
+        <v/>
+      </c>
+      <c r="CK37" s="13"/>
+      <c r="CL37" s="11"/>
+      <c r="CM37" s="12"/>
+      <c r="CN37" s="12" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="CO37" s="13"/>
+      <c r="CP37" s="11"/>
+      <c r="CQ37" s="12"/>
+      <c r="CR37" s="15" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
     </row>
-    <row r="38" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A38" s="71" t="s">
+    <row r="38" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A38" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="72"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="33" t="str">
-        <f t="shared" ref="C38:AX38" si="29">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
+        <f t="shared" ref="C38:AX38" si="33">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
       </c>
       <c r="D38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="E38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="F38" s="36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="G38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="H38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="I38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="J38" s="36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="K38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="L38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="M38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="N38" s="37" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="P38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Q38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="R38" s="36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="S38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="T38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="U38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="V38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="W38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="X38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Y38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="Z38" s="37" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AA38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AB38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AC38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AD38" s="36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AE38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AF38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AG38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AH38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AI38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AJ38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AK38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AL38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AM38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AN38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AO38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AP38" s="37" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AQ38" s="33" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AR38" s="34" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AS38" s="35" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AT38" s="36" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AU38" s="23" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AV38" s="24" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AW38" s="25" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="AX38" s="50" t="str">
-        <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="AY38" s="71" t="s">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="AY38" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="AZ38" s="72"/>
+      <c r="AZ38" s="76"/>
       <c r="BA38" s="33" t="str">
-        <f t="shared" ref="BA38:BL38" si="30">IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
+        <f t="shared" ref="BA38:BL38" si="34">IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB38" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BC38" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BD38" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BE38" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BF38" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BG38" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BH38" s="37" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BI38" s="33" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BJ38" s="34" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BK38" s="35" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BL38" s="36" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="BM38" s="33" t="str">
-        <f t="shared" ref="BM38:BT38" si="31">IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
+        <f t="shared" ref="BM38:BT38" si="35">IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
         <v/>
       </c>
       <c r="BN38" s="34" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BO38" s="35" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BP38" s="35" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BQ38" s="33" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BR38" s="34" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BS38" s="35" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BT38" s="37" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="BU38" s="33" t="str">
-        <f t="shared" ref="BU38:CB38" si="32">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
+        <f t="shared" ref="BU38:CJ38" si="36">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
         <v/>
       </c>
       <c r="BV38" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BW38" s="35" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BX38" s="35" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BY38" s="33" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="BZ38" s="34" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="CA38" s="35" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="CB38" s="36" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CC38" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CD38" s="34" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CE38" s="35" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CF38" s="35" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CG38" s="33" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CH38" s="34" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CI38" s="35" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CJ38" s="37" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="CK38" s="33" t="str">
+        <f t="shared" ref="CK38:CR38" si="37">IF(SUM(CK8:CK37)=0,"",AVERAGE(CK8:CK37))</f>
+        <v/>
+      </c>
+      <c r="CL38" s="34" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CM38" s="35" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CN38" s="35" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CO38" s="40" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CP38" s="38" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CQ38" s="39" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="CR38" s="88" t="str">
+        <f t="shared" si="37"/>
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A39" s="63" t="s">
+    <row r="39" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A39" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B39" s="64"/>
+      <c r="B39" s="78"/>
       <c r="C39" s="33" t="str">
-        <f t="shared" ref="C39:AX39" si="33">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
+        <f t="shared" ref="C39:AX39" si="38">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
         <v/>
       </c>
       <c r="D39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="E39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="F39" s="36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="G39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="H39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="I39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="J39" s="36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="K39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="L39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="M39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="N39" s="37" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="O39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="P39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Q39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="R39" s="36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="S39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="T39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="U39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="V39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="W39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="X39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Y39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="Z39" s="37" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AA39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AB39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AC39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AD39" s="36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AE39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AF39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AG39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AH39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AI39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AJ39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AK39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AL39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AM39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AN39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AO39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AP39" s="37" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AQ39" s="33" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AR39" s="34" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AS39" s="35" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AT39" s="36" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AU39" s="23" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AV39" s="24" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AW39" s="25" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="38"/>
         <v/>
       </c>
       <c r="AX39" s="50" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="AY39" s="63" t="s">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="AY39" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="AZ39" s="64"/>
+      <c r="AZ39" s="78"/>
       <c r="BA39" s="33" t="str">
-        <f t="shared" ref="BA39:BL39" si="34">IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
+        <f t="shared" ref="BA39:BL39" si="39">IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB39" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BC39" s="35" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BD39" s="35" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BE39" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BF39" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BG39" s="35" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BH39" s="37" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BI39" s="33" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BJ39" s="34" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BK39" s="35" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BL39" s="36" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="39"/>
         <v/>
       </c>
       <c r="BM39" s="33" t="str">
-        <f t="shared" ref="BM39:BT39" si="35">IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
+        <f t="shared" ref="BM39:BT39" si="40">IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
         <v/>
       </c>
       <c r="BN39" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BO39" s="35" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BP39" s="35" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BQ39" s="33" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BR39" s="34" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BS39" s="35" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BT39" s="37" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="40"/>
         <v/>
       </c>
       <c r="BU39" s="33" t="str">
-        <f t="shared" ref="BU39:CB39" si="36">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
+        <f t="shared" ref="BU39:CJ39" si="41">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
         <v/>
       </c>
       <c r="BV39" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BW39" s="35" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BX39" s="35" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BY39" s="33" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="BZ39" s="34" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="CA39" s="35" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
         <v/>
       </c>
       <c r="CB39" s="36" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CC39" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CD39" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CE39" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CF39" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CG39" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CH39" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CI39" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CJ39" s="37" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="CK39" s="33" t="str">
+        <f t="shared" ref="CK39:CR39" si="42">IF(SUM(CK8:CK37)=0,"",MEDIAN(CK8:CK37))</f>
+        <v/>
+      </c>
+      <c r="CL39" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CM39" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CN39" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CO39" s="40" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CP39" s="38" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CQ39" s="39" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="CR39" s="88" t="str">
+        <f t="shared" si="42"/>
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A40" s="63" t="s">
+    <row r="40" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A40" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B40" s="64"/>
+      <c r="B40" s="78"/>
       <c r="C40" s="33" t="str">
-        <f t="shared" ref="C40:AX40" si="37">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
+        <f t="shared" ref="C40:AX40" si="43">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
         <v/>
       </c>
       <c r="D40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="E40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="F40" s="36" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="G40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="H40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="I40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="J40" s="36" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="K40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="L40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="M40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="N40" s="37" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="O40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="P40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="R40" s="36" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="S40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="T40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="U40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="V40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="W40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="X40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Y40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Z40" s="37" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AA40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AB40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AC40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AD40" s="36" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AE40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AF40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AG40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AH40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AI40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AJ40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AK40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AL40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AM40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AN40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AO40" s="35" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AP40" s="37" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AQ40" s="33" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AR40" s="34" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AS40" s="35" t="str">
@@ -8402,771 +9556,963 @@
         <v/>
       </c>
       <c r="AT40" s="36" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AU40" s="23" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AV40" s="24" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AW40" s="25" t="str">
-        <f t="shared" si="37"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="AX40" s="50" t="str">
-        <f t="shared" si="37"/>
-        <v/>
-      </c>
-      <c r="AY40" s="63" t="s">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="AY40" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="AZ40" s="64"/>
+      <c r="AZ40" s="78"/>
       <c r="BA40" s="33" t="str">
-        <f t="shared" ref="BA40:BL40" si="38">IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
+        <f t="shared" ref="BA40:BL40" si="44">IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB40" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BC40" s="35" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BD40" s="35" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BE40" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BF40" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BG40" s="35" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BH40" s="37" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BI40" s="33" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BJ40" s="34" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BK40" s="35" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BL40" s="36" t="str">
-        <f t="shared" si="38"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="BM40" s="33" t="str">
-        <f t="shared" ref="BM40:BT40" si="39">IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
+        <f t="shared" ref="BM40:BT40" si="45">IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
         <v/>
       </c>
       <c r="BN40" s="34" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BO40" s="35" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BP40" s="35" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BQ40" s="33" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BR40" s="34" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BS40" s="35" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BT40" s="37" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="45"/>
         <v/>
       </c>
       <c r="BU40" s="33" t="str">
-        <f t="shared" ref="BU40:CB40" si="40">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
+        <f t="shared" ref="BU40:CJ40" si="46">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
         <v/>
       </c>
       <c r="BV40" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="BW40" s="35" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="BX40" s="35" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="BY40" s="33" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="BZ40" s="34" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="CA40" s="35" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
         <v/>
       </c>
       <c r="CB40" s="36" t="str">
-        <f t="shared" si="40"/>
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CC40" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CD40" s="34" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CE40" s="35" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CF40" s="35" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CG40" s="33" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CH40" s="34" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CI40" s="35" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CJ40" s="37" t="str">
+        <f t="shared" si="46"/>
+        <v/>
+      </c>
+      <c r="CK40" s="33" t="str">
+        <f t="shared" ref="CK40:CR40" si="47">IF(SUM(CK8:CK37)=0,"",MAX(CK8:CK37))</f>
+        <v/>
+      </c>
+      <c r="CL40" s="34" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CM40" s="35" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CN40" s="35" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CO40" s="40" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CP40" s="38" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CQ40" s="39" t="str">
+        <f t="shared" si="47"/>
+        <v/>
+      </c>
+      <c r="CR40" s="88" t="str">
+        <f t="shared" si="47"/>
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A41" s="63" t="s">
+    <row r="41" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A41" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="B41" s="64"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="33" t="str">
-        <f t="shared" ref="C41:AX41" si="41">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
+        <f t="shared" ref="C41:AX41" si="48">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
         <v/>
       </c>
       <c r="D41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="E41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="F41" s="36" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="G41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="H41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="I41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="J41" s="36" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="K41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="L41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="M41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="N41" s="37" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="O41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="P41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Q41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="R41" s="36" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="S41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="T41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="U41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="V41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="W41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="X41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Y41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="Z41" s="37" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AA41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AB41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AC41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AD41" s="36" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AE41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AF41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AG41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AH41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AI41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AJ41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AK41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AL41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AM41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AN41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AO41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AP41" s="37" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AQ41" s="33" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AR41" s="34" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AS41" s="35" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AT41" s="36" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AU41" s="23" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AV41" s="24" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AW41" s="25" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="48"/>
         <v/>
       </c>
       <c r="AX41" s="50" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="AY41" s="63" t="s">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="AY41" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="AZ41" s="64"/>
+      <c r="AZ41" s="78"/>
       <c r="BA41" s="33" t="str">
-        <f t="shared" ref="BA41:BL41" si="42">IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
+        <f t="shared" ref="BA41:BL41" si="49">IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
         <v/>
       </c>
       <c r="BB41" s="34" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BC41" s="35" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BD41" s="35" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BE41" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BF41" s="34" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BG41" s="35" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BH41" s="37" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BI41" s="33" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BJ41" s="34" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BK41" s="35" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BL41" s="36" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="49"/>
         <v/>
       </c>
       <c r="BM41" s="33" t="str">
-        <f t="shared" ref="BM41:BT41" si="43">IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
+        <f t="shared" ref="BM41:BT41" si="50">IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
         <v/>
       </c>
       <c r="BN41" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BO41" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BP41" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BQ41" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BR41" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BS41" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BT41" s="37" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="50"/>
         <v/>
       </c>
       <c r="BU41" s="33" t="str">
-        <f t="shared" ref="BU41:CB41" si="44">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
+        <f t="shared" ref="BU41:CJ41" si="51">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
         <v/>
       </c>
       <c r="BV41" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="BW41" s="35" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="BX41" s="35" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="BY41" s="33" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="BZ41" s="34" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="CA41" s="35" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
         <v/>
       </c>
       <c r="CB41" s="36" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CC41" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CD41" s="34" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CE41" s="35" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CF41" s="35" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CG41" s="33" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CH41" s="34" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CI41" s="35" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CJ41" s="37" t="str">
+        <f t="shared" si="51"/>
+        <v/>
+      </c>
+      <c r="CK41" s="33" t="str">
+        <f t="shared" ref="CK41:CR41" si="52">IF(SUM(CK8:CK37)=0,"",MIN(CK8:CK37))</f>
+        <v/>
+      </c>
+      <c r="CL41" s="34" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CM41" s="35" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CN41" s="35" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CO41" s="40" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CP41" s="38" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CQ41" s="39" t="str">
+        <f t="shared" si="52"/>
+        <v/>
+      </c>
+      <c r="CR41" s="88" t="str">
+        <f t="shared" si="52"/>
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:80" x14ac:dyDescent="0.3">
-      <c r="A42" s="65" t="s">
+    <row r="42" spans="1:96" x14ac:dyDescent="0.3">
+      <c r="A42" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="66"/>
+      <c r="B42" s="70"/>
       <c r="C42" s="2" t="str">
-        <f t="shared" ref="C42:AX42" si="45">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
+        <f t="shared" ref="C42:AX42" si="53">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
         <v/>
       </c>
       <c r="D42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="E42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="F42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="G42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="H42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="I42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="J42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="K42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="L42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="M42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="N42" s="6" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="O42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="P42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="Q42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="R42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="S42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="T42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="U42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="V42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="W42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="X42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="Y42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="Z42" s="6" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AA42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AB42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AC42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AD42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AE42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AF42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AG42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AH42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AI42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AJ42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AK42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AL42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AM42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AN42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AO42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AP42" s="6" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AQ42" s="2" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AR42" s="3" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AS42" s="4" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AT42" s="5" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AU42" s="7" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AV42" s="8" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AW42" s="9" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="53"/>
         <v/>
       </c>
       <c r="AX42" s="10" t="str">
-        <f t="shared" si="45"/>
-        <v/>
-      </c>
-      <c r="AY42" s="65" t="s">
+        <f t="shared" si="53"/>
+        <v/>
+      </c>
+      <c r="AY42" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="AZ42" s="66"/>
+      <c r="AZ42" s="70"/>
       <c r="BA42" s="2" t="str">
-        <f t="shared" ref="BA42:BL42" si="46">IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
+        <f t="shared" ref="BA42:BL42" si="54">IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
         <v/>
       </c>
       <c r="BB42" s="3" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BC42" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BD42" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BE42" s="2" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BF42" s="3" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BG42" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BH42" s="6" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BI42" s="2" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BJ42" s="3" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BK42" s="4" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BL42" s="5" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="54"/>
         <v/>
       </c>
       <c r="BM42" s="2" t="str">
-        <f t="shared" ref="BM42:BT42" si="47">IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
+        <f t="shared" ref="BM42:BT42" si="55">IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
         <v/>
       </c>
       <c r="BN42" s="3" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BO42" s="4" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BP42" s="4" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BQ42" s="2" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BR42" s="3" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BS42" s="4" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BT42" s="6" t="str">
-        <f t="shared" si="47"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="BU42" s="2" t="str">
-        <f t="shared" ref="BU42:CB42" si="48">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
+        <f t="shared" ref="BU42:CJ42" si="56">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
         <v/>
       </c>
       <c r="BV42" s="3" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="BW42" s="4" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="BX42" s="4" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="BY42" s="2" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="BZ42" s="3" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="CA42" s="4" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
         <v/>
       </c>
       <c r="CB42" s="5" t="str">
-        <f t="shared" si="48"/>
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CC42" s="2" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CD42" s="3" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CE42" s="4" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CF42" s="4" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CG42" s="2" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CH42" s="3" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CI42" s="4" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CJ42" s="6" t="str">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+      <c r="CK42" s="2" t="str">
+        <f t="shared" ref="CK42:CR42" si="57">IF(CK38="","",COUNTIF(CK8:CK37,"&lt;51")/COUNT(CK8:CK37)*100)</f>
+        <v/>
+      </c>
+      <c r="CL42" s="3" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CM42" s="4" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CN42" s="4" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CO42" s="13" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CP42" s="11" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CQ42" s="12" t="str">
+        <f t="shared" si="57"/>
+        <v/>
+      </c>
+      <c r="CR42" s="15" t="str">
+        <f t="shared" si="57"/>
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:80" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:96" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -9218,7 +10564,7 @@
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
     </row>
-    <row r="44" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -9270,7 +10616,7 @@
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
     </row>
-    <row r="45" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -9316,7 +10662,7 @@
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
     </row>
-    <row r="46" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -9338,7 +10684,7 @@
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
-    <row r="47" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -9366,7 +10712,7 @@
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
     </row>
-    <row r="48" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -9472,169 +10818,194 @@
     </row>
     <row r="50" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="B51" s="73" t="s">
+      <c r="B51" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="C51" s="73"/>
-      <c r="D51" s="73"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="73"/>
-      <c r="G51" s="73"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
       <c r="H51" s="53"/>
       <c r="I51" s="53"/>
       <c r="J51" s="53"/>
-      <c r="M51" s="73" t="s">
+      <c r="M51" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="N51" s="73"/>
-      <c r="O51" s="73"/>
-      <c r="P51" s="73"/>
-      <c r="Q51" s="73"/>
-      <c r="R51" s="73"/>
-      <c r="S51" s="73"/>
-      <c r="T51" s="73"/>
-      <c r="U51" s="73"/>
-      <c r="V51" s="73"/>
-      <c r="W51" s="73"/>
-      <c r="X51" s="73"/>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="55"/>
+      <c r="Q51" s="55"/>
+      <c r="R51" s="55"/>
+      <c r="S51" s="55"/>
+      <c r="T51" s="55"/>
+      <c r="U51" s="55"/>
+      <c r="V51" s="55"/>
+      <c r="W51" s="55"/>
+      <c r="X51" s="55"/>
       <c r="Y51" s="53"/>
       <c r="Z51" s="53"/>
-      <c r="AD51" s="73" t="s">
+      <c r="AD51" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="AE51" s="73"/>
-      <c r="AF51" s="73"/>
-      <c r="AG51" s="73"/>
-      <c r="AH51" s="73"/>
-      <c r="AI51" s="73"/>
-      <c r="AJ51" s="73"/>
-      <c r="AK51" s="73"/>
-      <c r="AL51" s="73"/>
-      <c r="AM51" s="73"/>
-      <c r="AN51" s="73"/>
-      <c r="AO51" s="73"/>
+      <c r="AE51" s="55"/>
+      <c r="AF51" s="55"/>
+      <c r="AG51" s="55"/>
+      <c r="AH51" s="55"/>
+      <c r="AI51" s="55"/>
+      <c r="AJ51" s="55"/>
+      <c r="AK51" s="55"/>
+      <c r="AL51" s="55"/>
+      <c r="AM51" s="55"/>
+      <c r="AN51" s="55"/>
+      <c r="AO51" s="55"/>
       <c r="AP51" s="53"/>
-      <c r="AY51" s="73" t="s">
+      <c r="AY51" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="AZ51" s="73"/>
-      <c r="BA51" s="73"/>
-      <c r="BB51" s="73"/>
-      <c r="BC51" s="73"/>
-      <c r="BD51" s="73"/>
-      <c r="BE51" s="73"/>
-      <c r="BF51" s="73"/>
-      <c r="BG51" s="73"/>
-      <c r="BH51" s="73"/>
+      <c r="AZ51" s="55"/>
+      <c r="BA51" s="55"/>
+      <c r="BB51" s="55"/>
+      <c r="BC51" s="55"/>
+      <c r="BD51" s="55"/>
+      <c r="BE51" s="55"/>
+      <c r="BF51" s="55"/>
+      <c r="BG51" s="55"/>
+      <c r="BH51" s="55"/>
       <c r="BI51" s="52"/>
       <c r="BJ51" s="53"/>
       <c r="BK51" s="53"/>
       <c r="BL51" s="53"/>
-      <c r="BM51" s="73" t="s">
+      <c r="BM51" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="BN51" s="73"/>
-      <c r="BO51" s="73"/>
-      <c r="BP51" s="73"/>
-      <c r="BQ51" s="73"/>
-      <c r="BR51" s="73"/>
-      <c r="BS51" s="73"/>
-      <c r="BT51" s="73"/>
-      <c r="BU51" s="73"/>
-      <c r="BV51" s="73"/>
-      <c r="BW51" s="73"/>
-      <c r="BX51" s="73"/>
+      <c r="BN51" s="55"/>
+      <c r="BO51" s="55"/>
+      <c r="BP51" s="55"/>
+      <c r="BQ51" s="55"/>
+      <c r="BR51" s="55"/>
+      <c r="BS51" s="55"/>
+      <c r="BT51" s="55"/>
+      <c r="BU51" s="55"/>
+      <c r="BV51" s="55"/>
+      <c r="BW51" s="55"/>
+      <c r="BX51" s="55"/>
     </row>
     <row r="52" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="B52" s="74" t="s">
+      <c r="B52" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="74"/>
-      <c r="D52" s="74"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
       <c r="H52" s="53"/>
       <c r="I52" s="53"/>
       <c r="J52" s="53"/>
-      <c r="M52" s="74" t="s">
+      <c r="M52" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="N52" s="74"/>
-      <c r="O52" s="74"/>
-      <c r="P52" s="74"/>
-      <c r="Q52" s="74"/>
-      <c r="R52" s="74"/>
-      <c r="S52" s="74"/>
-      <c r="T52" s="74"/>
-      <c r="U52" s="74"/>
-      <c r="V52" s="74"/>
-      <c r="W52" s="74"/>
-      <c r="X52" s="74"/>
+      <c r="N52" s="54"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="54"/>
+      <c r="Q52" s="54"/>
+      <c r="R52" s="54"/>
+      <c r="S52" s="54"/>
+      <c r="T52" s="54"/>
+      <c r="U52" s="54"/>
+      <c r="V52" s="54"/>
+      <c r="W52" s="54"/>
+      <c r="X52" s="54"/>
       <c r="Y52" s="53"/>
       <c r="Z52" s="53"/>
-      <c r="AD52" s="74" t="s">
+      <c r="AD52" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="AE52" s="74"/>
-      <c r="AF52" s="74"/>
-      <c r="AG52" s="74"/>
-      <c r="AH52" s="74"/>
-      <c r="AI52" s="74"/>
-      <c r="AJ52" s="74"/>
-      <c r="AK52" s="74"/>
-      <c r="AL52" s="74"/>
-      <c r="AM52" s="74"/>
-      <c r="AN52" s="74"/>
-      <c r="AO52" s="74"/>
+      <c r="AE52" s="54"/>
+      <c r="AF52" s="54"/>
+      <c r="AG52" s="54"/>
+      <c r="AH52" s="54"/>
+      <c r="AI52" s="54"/>
+      <c r="AJ52" s="54"/>
+      <c r="AK52" s="54"/>
+      <c r="AL52" s="54"/>
+      <c r="AM52" s="54"/>
+      <c r="AN52" s="54"/>
+      <c r="AO52" s="54"/>
       <c r="AP52" s="53"/>
       <c r="AW52" t="s">
         <v>36</v>
       </c>
-      <c r="AY52" s="74" t="s">
+      <c r="AY52" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="AZ52" s="74"/>
-      <c r="BA52" s="74"/>
-      <c r="BB52" s="74"/>
-      <c r="BC52" s="74"/>
-      <c r="BD52" s="74"/>
-      <c r="BE52" s="74"/>
-      <c r="BF52" s="74"/>
-      <c r="BG52" s="74"/>
-      <c r="BH52" s="74"/>
+      <c r="AZ52" s="54"/>
+      <c r="BA52" s="54"/>
+      <c r="BB52" s="54"/>
+      <c r="BC52" s="54"/>
+      <c r="BD52" s="54"/>
+      <c r="BE52" s="54"/>
+      <c r="BF52" s="54"/>
+      <c r="BG52" s="54"/>
+      <c r="BH52" s="54"/>
       <c r="BI52" s="53"/>
       <c r="BJ52" s="53"/>
       <c r="BK52" s="53"/>
       <c r="BL52" s="53"/>
-      <c r="BM52" s="74" t="s">
+      <c r="BM52" s="54" t="s">
         <v>23</v>
       </c>
-      <c r="BN52" s="74"/>
-      <c r="BO52" s="74"/>
-      <c r="BP52" s="74"/>
-      <c r="BQ52" s="74"/>
-      <c r="BR52" s="74"/>
-      <c r="BS52" s="74"/>
-      <c r="BT52" s="74"/>
-      <c r="BU52" s="74"/>
-      <c r="BV52" s="74"/>
-      <c r="BW52" s="74"/>
-      <c r="BX52" s="74"/>
+      <c r="BN52" s="54"/>
+      <c r="BO52" s="54"/>
+      <c r="BP52" s="54"/>
+      <c r="BQ52" s="54"/>
+      <c r="BR52" s="54"/>
+      <c r="BS52" s="54"/>
+      <c r="BT52" s="54"/>
+      <c r="BU52" s="54"/>
+      <c r="BV52" s="54"/>
+      <c r="BW52" s="54"/>
+      <c r="BX52" s="54"/>
       <c r="CA52" s="51" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="53">
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="M52:X52"/>
-    <mergeCell ref="AD52:AO52"/>
-    <mergeCell ref="AY51:AZ51"/>
-    <mergeCell ref="BA51:BH51"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="M51:X51"/>
-    <mergeCell ref="AD51:AO51"/>
+  <mergeCells count="57">
+    <mergeCell ref="CC6:CF6"/>
+    <mergeCell ref="CG6:CJ6"/>
+    <mergeCell ref="CK6:CN6"/>
+    <mergeCell ref="CO6:CR6"/>
+    <mergeCell ref="AY2:CR2"/>
+    <mergeCell ref="AY3:CR3"/>
+    <mergeCell ref="AY4:CR4"/>
+    <mergeCell ref="AY5:CR5"/>
+    <mergeCell ref="BU6:BX6"/>
+    <mergeCell ref="BY6:CB6"/>
+    <mergeCell ref="BA6:BD6"/>
+    <mergeCell ref="BE6:BH6"/>
+    <mergeCell ref="BI6:BL6"/>
+    <mergeCell ref="BM6:BP6"/>
+    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="AY41:AZ41"/>
+    <mergeCell ref="AY42:AZ42"/>
+    <mergeCell ref="AY6:AY7"/>
+    <mergeCell ref="AZ6:AZ7"/>
+    <mergeCell ref="AY38:AZ38"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="AY40:AZ40"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="BM51:BX51"/>
     <mergeCell ref="AY52:AZ52"/>
     <mergeCell ref="BA52:BH52"/>
@@ -9651,55 +11022,52 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="W6:Z6"/>
     <mergeCell ref="AI6:AL6"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="AY41:AZ41"/>
-    <mergeCell ref="AY42:AZ42"/>
-    <mergeCell ref="AY6:AY7"/>
-    <mergeCell ref="AZ6:AZ7"/>
-    <mergeCell ref="AY38:AZ38"/>
-    <mergeCell ref="AY39:AZ39"/>
-    <mergeCell ref="AY40:AZ40"/>
-    <mergeCell ref="BU6:BX6"/>
-    <mergeCell ref="BY6:CB6"/>
-    <mergeCell ref="AY2:CB2"/>
-    <mergeCell ref="AY3:CB3"/>
-    <mergeCell ref="AY4:CB4"/>
-    <mergeCell ref="AY5:CB5"/>
-    <mergeCell ref="BA6:BD6"/>
-    <mergeCell ref="BE6:BH6"/>
-    <mergeCell ref="BI6:BL6"/>
-    <mergeCell ref="BM6:BP6"/>
-    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="M52:X52"/>
+    <mergeCell ref="AD52:AO52"/>
+    <mergeCell ref="AY51:AZ51"/>
+    <mergeCell ref="BA51:BH51"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="M51:X51"/>
+    <mergeCell ref="AD51:AO51"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:AX37 BA8:BL37">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM8:BT37">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
+      <formula>1</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU8:BX37">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
+      <formula>1</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BY8:CB37">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
+      <formula>1</formula>
+      <formula>50</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="CC8:CJ37">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BU8:BX37">
+  <conditionalFormatting sqref="CK8:CN37">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="BY8:CB37">
+  <conditionalFormatting sqref="CO8:CR37">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>1</formula>
       <formula>50</formula>

--- a/public/templates/cs12.xlsx
+++ b/public/templates/cs12.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629F4DCD-E967-4702-B643-AF583ECC201C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61D4B03-37B6-45E0-B6B2-EFD7370260E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="39">
   <si>
     <t>Nº</t>
   </si>
@@ -82,6 +85,9 @@
   </si>
   <si>
     <t>Porcentaje de Reprobados (%)</t>
+  </si>
+  <si>
+    <t>Lenguaje</t>
   </si>
   <si>
     <t>Literature</t>
@@ -149,9 +155,6 @@
   <si>
     <t>1 de 2</t>
   </si>
-  <si>
-    <t>Lenguaje</t>
-  </si>
 </sst>
 </file>
 
@@ -163,7 +166,7 @@
     <numFmt numFmtId="166" formatCode="#.00"/>
     <numFmt numFmtId="167" formatCode="%#.00"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,14 +361,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1130,7 +1125,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1275,24 +1270,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1304,23 +1283,26 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1346,45 +1328,37 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="71">
     <cellStyle name="20% - Accent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1459,37 +1433,7 @@
     <cellStyle name="Title" xfId="69" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
     <cellStyle name="Warning Text" xfId="70" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2017,852 +1961,726 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:CR52"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:CB52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
-    <col min="3" max="50" width="3.88671875" customWidth="1"/>
+    <col min="3" max="50" width="3.85546875" customWidth="1"/>
     <col min="51" max="51" width="3" customWidth="1"/>
-    <col min="52" max="52" width="25.88671875" customWidth="1"/>
-    <col min="53" max="96" width="4.33203125" customWidth="1"/>
+    <col min="52" max="52" width="35" customWidth="1"/>
+    <col min="53" max="64" width="5" customWidth="1"/>
+    <col min="65" max="80" width="4.5703125" customWidth="1"/>
+    <col min="81" max="82" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A2" s="56" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="56"/>
-      <c r="N2" s="56"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="56"/>
-      <c r="Q2" s="56"/>
-      <c r="R2" s="56"/>
-      <c r="S2" s="56"/>
-      <c r="T2" s="56"/>
-      <c r="U2" s="56"/>
-      <c r="V2" s="56"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="56"/>
-      <c r="Y2" s="56"/>
-      <c r="Z2" s="56"/>
-      <c r="AA2" s="56"/>
-      <c r="AB2" s="56"/>
-      <c r="AC2" s="56"/>
-      <c r="AD2" s="56"/>
-      <c r="AE2" s="56"/>
-      <c r="AF2" s="56"/>
-      <c r="AG2" s="56"/>
-      <c r="AH2" s="56"/>
-      <c r="AI2" s="56"/>
-      <c r="AJ2" s="56"/>
-      <c r="AK2" s="56"/>
-      <c r="AL2" s="56"/>
-      <c r="AM2" s="56"/>
-      <c r="AN2" s="56"/>
-      <c r="AO2" s="56"/>
-      <c r="AP2" s="56"/>
-      <c r="AQ2" s="56"/>
-      <c r="AR2" s="56"/>
-      <c r="AS2" s="56"/>
-      <c r="AT2" s="56"/>
-      <c r="AU2" s="56"/>
-      <c r="AV2" s="56"/>
-      <c r="AW2" s="56"/>
-      <c r="AX2" s="56"/>
-      <c r="AY2" s="56" t="str">
+    <row r="2" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="58"/>
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="58"/>
+      <c r="Z2" s="58"/>
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="58"/>
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="58"/>
+      <c r="AI2" s="58"/>
+      <c r="AJ2" s="58"/>
+      <c r="AK2" s="58"/>
+      <c r="AL2" s="58"/>
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="58"/>
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="58"/>
+      <c r="AR2" s="58"/>
+      <c r="AS2" s="58"/>
+      <c r="AT2" s="58"/>
+      <c r="AU2" s="58"/>
+      <c r="AV2" s="58"/>
+      <c r="AW2" s="58"/>
+      <c r="AX2" s="58"/>
+      <c r="AY2" s="58" t="str">
         <f>A2</f>
         <v>CENTRALIZADOR DE NOTAS</v>
       </c>
-      <c r="AZ2" s="56"/>
-      <c r="BA2" s="56"/>
-      <c r="BB2" s="56"/>
-      <c r="BC2" s="56"/>
-      <c r="BD2" s="56"/>
-      <c r="BE2" s="56"/>
-      <c r="BF2" s="56"/>
-      <c r="BG2" s="56"/>
-      <c r="BH2" s="56"/>
-      <c r="BI2" s="56"/>
-      <c r="BJ2" s="56"/>
-      <c r="BK2" s="56"/>
-      <c r="BL2" s="56"/>
-      <c r="BM2" s="56"/>
-      <c r="BN2" s="56"/>
-      <c r="BO2" s="56"/>
-      <c r="BP2" s="56"/>
-      <c r="BQ2" s="56"/>
-      <c r="BR2" s="56"/>
-      <c r="BS2" s="56"/>
-      <c r="BT2" s="56"/>
-      <c r="BU2" s="56"/>
-      <c r="BV2" s="56"/>
-      <c r="BW2" s="56"/>
-      <c r="BX2" s="56"/>
-      <c r="BY2" s="56"/>
-      <c r="BZ2" s="56"/>
-      <c r="CA2" s="56"/>
-      <c r="CB2" s="56"/>
-      <c r="CC2" s="56"/>
-      <c r="CD2" s="56"/>
-      <c r="CE2" s="56"/>
-      <c r="CF2" s="56"/>
-      <c r="CG2" s="56"/>
-      <c r="CH2" s="56"/>
-      <c r="CI2" s="56"/>
-      <c r="CJ2" s="56"/>
-      <c r="CK2" s="56"/>
-      <c r="CL2" s="56"/>
-      <c r="CM2" s="56"/>
-      <c r="CN2" s="56"/>
-      <c r="CO2" s="56"/>
-      <c r="CP2" s="56"/>
-      <c r="CQ2" s="56"/>
-      <c r="CR2" s="56"/>
+      <c r="AZ2" s="58"/>
+      <c r="BA2" s="58"/>
+      <c r="BB2" s="58"/>
+      <c r="BC2" s="58"/>
+      <c r="BD2" s="58"/>
+      <c r="BE2" s="58"/>
+      <c r="BF2" s="58"/>
+      <c r="BG2" s="58"/>
+      <c r="BH2" s="58"/>
+      <c r="BI2" s="58"/>
+      <c r="BJ2" s="58"/>
+      <c r="BK2" s="58"/>
+      <c r="BL2" s="58"/>
+      <c r="BM2" s="58"/>
+      <c r="BN2" s="58"/>
+      <c r="BO2" s="58"/>
+      <c r="BP2" s="58"/>
+      <c r="BQ2" s="58"/>
+      <c r="BR2" s="58"/>
+      <c r="BS2" s="58"/>
+      <c r="BT2" s="58"/>
+      <c r="BU2" s="58"/>
+      <c r="BV2" s="58"/>
+      <c r="BW2" s="58"/>
+      <c r="BX2" s="58"/>
+      <c r="BY2" s="58"/>
+      <c r="BZ2" s="58"/>
+      <c r="CA2" s="58"/>
+      <c r="CB2" s="58"/>
     </row>
-    <row r="3" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A3" s="57" t="s">
+    <row r="3" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A3" s="72" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="57"/>
-      <c r="C3" s="57"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-      <c r="J3" s="57"/>
-      <c r="K3" s="57"/>
-      <c r="L3" s="57"/>
-      <c r="M3" s="57"/>
-      <c r="N3" s="57"/>
-      <c r="O3" s="57"/>
-      <c r="P3" s="57"/>
-      <c r="Q3" s="57"/>
-      <c r="R3" s="57"/>
-      <c r="S3" s="57"/>
-      <c r="T3" s="57"/>
-      <c r="U3" s="57"/>
-      <c r="V3" s="57"/>
-      <c r="W3" s="57"/>
-      <c r="X3" s="57"/>
-      <c r="Y3" s="57"/>
-      <c r="Z3" s="57"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="57"/>
-      <c r="AC3" s="57"/>
-      <c r="AD3" s="57"/>
-      <c r="AE3" s="57"/>
-      <c r="AF3" s="57"/>
-      <c r="AG3" s="57"/>
-      <c r="AH3" s="57"/>
-      <c r="AI3" s="57"/>
-      <c r="AJ3" s="57"/>
-      <c r="AK3" s="57"/>
-      <c r="AL3" s="57"/>
-      <c r="AM3" s="57"/>
-      <c r="AN3" s="57"/>
-      <c r="AO3" s="57"/>
-      <c r="AP3" s="57"/>
-      <c r="AQ3" s="57"/>
-      <c r="AR3" s="57"/>
-      <c r="AS3" s="57"/>
-      <c r="AT3" s="57"/>
-      <c r="AU3" s="57"/>
-      <c r="AV3" s="57"/>
-      <c r="AW3" s="57"/>
-      <c r="AX3" s="57"/>
-      <c r="AY3" s="56" t="str">
-        <f>A3</f>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+      <c r="E3" s="72"/>
+      <c r="F3" s="72"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="72"/>
+      <c r="N3" s="72"/>
+      <c r="O3" s="72"/>
+      <c r="P3" s="72"/>
+      <c r="Q3" s="72"/>
+      <c r="R3" s="72"/>
+      <c r="S3" s="72"/>
+      <c r="T3" s="72"/>
+      <c r="U3" s="72"/>
+      <c r="V3" s="72"/>
+      <c r="W3" s="72"/>
+      <c r="X3" s="72"/>
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="72"/>
+      <c r="AB3" s="72"/>
+      <c r="AC3" s="72"/>
+      <c r="AD3" s="72"/>
+      <c r="AE3" s="72"/>
+      <c r="AF3" s="72"/>
+      <c r="AG3" s="72"/>
+      <c r="AH3" s="72"/>
+      <c r="AI3" s="72"/>
+      <c r="AJ3" s="72"/>
+      <c r="AK3" s="72"/>
+      <c r="AL3" s="72"/>
+      <c r="AM3" s="72"/>
+      <c r="AN3" s="72"/>
+      <c r="AO3" s="72"/>
+      <c r="AP3" s="72"/>
+      <c r="AQ3" s="72"/>
+      <c r="AR3" s="72"/>
+      <c r="AS3" s="72"/>
+      <c r="AT3" s="72"/>
+      <c r="AU3" s="72"/>
+      <c r="AV3" s="72"/>
+      <c r="AW3" s="72"/>
+      <c r="AX3" s="72"/>
+      <c r="AY3" s="58" t="str">
+        <f t="shared" ref="AY3:AY4" si="0">A3</f>
         <v>(CONSEJEROS Y DIRECCIONES TÉCNICAS)</v>
       </c>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="56"/>
-      <c r="BB3" s="56"/>
-      <c r="BC3" s="56"/>
-      <c r="BD3" s="56"/>
-      <c r="BE3" s="56"/>
-      <c r="BF3" s="56"/>
-      <c r="BG3" s="56"/>
-      <c r="BH3" s="56"/>
-      <c r="BI3" s="56"/>
-      <c r="BJ3" s="56"/>
-      <c r="BK3" s="56"/>
-      <c r="BL3" s="56"/>
-      <c r="BM3" s="56"/>
-      <c r="BN3" s="56"/>
-      <c r="BO3" s="56"/>
-      <c r="BP3" s="56"/>
-      <c r="BQ3" s="56"/>
-      <c r="BR3" s="56"/>
-      <c r="BS3" s="56"/>
-      <c r="BT3" s="56"/>
-      <c r="BU3" s="56"/>
-      <c r="BV3" s="56"/>
-      <c r="BW3" s="56"/>
-      <c r="BX3" s="56"/>
-      <c r="BY3" s="56"/>
-      <c r="BZ3" s="56"/>
-      <c r="CA3" s="56"/>
-      <c r="CB3" s="56"/>
-      <c r="CC3" s="56"/>
-      <c r="CD3" s="56"/>
-      <c r="CE3" s="56"/>
-      <c r="CF3" s="56"/>
-      <c r="CG3" s="56"/>
-      <c r="CH3" s="56"/>
-      <c r="CI3" s="56"/>
-      <c r="CJ3" s="56"/>
-      <c r="CK3" s="56"/>
-      <c r="CL3" s="56"/>
-      <c r="CM3" s="56"/>
-      <c r="CN3" s="56"/>
-      <c r="CO3" s="56"/>
-      <c r="CP3" s="56"/>
-      <c r="CQ3" s="56"/>
-      <c r="CR3" s="56"/>
+      <c r="AZ3" s="58"/>
+      <c r="BA3" s="58"/>
+      <c r="BB3" s="58"/>
+      <c r="BC3" s="58"/>
+      <c r="BD3" s="58"/>
+      <c r="BE3" s="58"/>
+      <c r="BF3" s="58"/>
+      <c r="BG3" s="58"/>
+      <c r="BH3" s="58"/>
+      <c r="BI3" s="58"/>
+      <c r="BJ3" s="58"/>
+      <c r="BK3" s="58"/>
+      <c r="BL3" s="58"/>
+      <c r="BM3" s="58"/>
+      <c r="BN3" s="58"/>
+      <c r="BO3" s="58"/>
+      <c r="BP3" s="58"/>
+      <c r="BQ3" s="58"/>
+      <c r="BR3" s="58"/>
+      <c r="BS3" s="58"/>
+      <c r="BT3" s="58"/>
+      <c r="BU3" s="58"/>
+      <c r="BV3" s="58"/>
+      <c r="BW3" s="58"/>
+      <c r="BX3" s="58"/>
+      <c r="BY3" s="58"/>
+      <c r="BZ3" s="58"/>
+      <c r="CA3" s="58"/>
+      <c r="CB3" s="58"/>
     </row>
-    <row r="4" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A4" s="58"/>
-      <c r="B4" s="58"/>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="58"/>
-      <c r="X4" s="58"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="58"/>
-      <c r="AB4" s="58"/>
-      <c r="AC4" s="58"/>
-      <c r="AD4" s="58"/>
-      <c r="AE4" s="58"/>
-      <c r="AF4" s="58"/>
-      <c r="AG4" s="58"/>
-      <c r="AH4" s="58"/>
-      <c r="AI4" s="58"/>
-      <c r="AJ4" s="58"/>
-      <c r="AK4" s="58"/>
-      <c r="AL4" s="58"/>
-      <c r="AM4" s="58"/>
-      <c r="AN4" s="58"/>
-      <c r="AO4" s="58"/>
-      <c r="AP4" s="58"/>
-      <c r="AQ4" s="58"/>
-      <c r="AR4" s="58"/>
-      <c r="AS4" s="58"/>
-      <c r="AT4" s="58"/>
-      <c r="AU4" s="58"/>
-      <c r="AV4" s="58"/>
-      <c r="AW4" s="58"/>
-      <c r="AX4" s="58"/>
-      <c r="AY4" s="56">
-        <f t="shared" ref="AY3:AY4" si="0">A4</f>
+    <row r="4" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A4" s="73"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="73"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="73"/>
+      <c r="O4" s="73"/>
+      <c r="P4" s="73"/>
+      <c r="Q4" s="73"/>
+      <c r="R4" s="73"/>
+      <c r="S4" s="73"/>
+      <c r="T4" s="73"/>
+      <c r="U4" s="73"/>
+      <c r="V4" s="73"/>
+      <c r="W4" s="73"/>
+      <c r="X4" s="73"/>
+      <c r="Y4" s="73"/>
+      <c r="Z4" s="73"/>
+      <c r="AA4" s="73"/>
+      <c r="AB4" s="73"/>
+      <c r="AC4" s="73"/>
+      <c r="AD4" s="73"/>
+      <c r="AE4" s="73"/>
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="73"/>
+      <c r="AJ4" s="73"/>
+      <c r="AK4" s="73"/>
+      <c r="AL4" s="73"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73"/>
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="73"/>
+      <c r="AR4" s="73"/>
+      <c r="AS4" s="73"/>
+      <c r="AT4" s="73"/>
+      <c r="AU4" s="73"/>
+      <c r="AV4" s="73"/>
+      <c r="AW4" s="73"/>
+      <c r="AX4" s="73"/>
+      <c r="AY4" s="58">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AZ4" s="56"/>
-      <c r="BA4" s="56"/>
-      <c r="BB4" s="56"/>
-      <c r="BC4" s="56"/>
-      <c r="BD4" s="56"/>
-      <c r="BE4" s="56"/>
-      <c r="BF4" s="56"/>
-      <c r="BG4" s="56"/>
-      <c r="BH4" s="56"/>
-      <c r="BI4" s="56"/>
-      <c r="BJ4" s="56"/>
-      <c r="BK4" s="56"/>
-      <c r="BL4" s="56"/>
-      <c r="BM4" s="56"/>
-      <c r="BN4" s="56"/>
-      <c r="BO4" s="56"/>
-      <c r="BP4" s="56"/>
-      <c r="BQ4" s="56"/>
-      <c r="BR4" s="56"/>
-      <c r="BS4" s="56"/>
-      <c r="BT4" s="56"/>
-      <c r="BU4" s="56"/>
-      <c r="BV4" s="56"/>
-      <c r="BW4" s="56"/>
-      <c r="BX4" s="56"/>
-      <c r="BY4" s="56"/>
-      <c r="BZ4" s="56"/>
-      <c r="CA4" s="56"/>
-      <c r="CB4" s="56"/>
-      <c r="CC4" s="56"/>
-      <c r="CD4" s="56"/>
-      <c r="CE4" s="56"/>
-      <c r="CF4" s="56"/>
-      <c r="CG4" s="56"/>
-      <c r="CH4" s="56"/>
-      <c r="CI4" s="56"/>
-      <c r="CJ4" s="56"/>
-      <c r="CK4" s="56"/>
-      <c r="CL4" s="56"/>
-      <c r="CM4" s="56"/>
-      <c r="CN4" s="56"/>
-      <c r="CO4" s="56"/>
-      <c r="CP4" s="56"/>
-      <c r="CQ4" s="56"/>
-      <c r="CR4" s="56"/>
+      <c r="AZ4" s="58"/>
+      <c r="BA4" s="58"/>
+      <c r="BB4" s="58"/>
+      <c r="BC4" s="58"/>
+      <c r="BD4" s="58"/>
+      <c r="BE4" s="58"/>
+      <c r="BF4" s="58"/>
+      <c r="BG4" s="58"/>
+      <c r="BH4" s="58"/>
+      <c r="BI4" s="58"/>
+      <c r="BJ4" s="58"/>
+      <c r="BK4" s="58"/>
+      <c r="BL4" s="58"/>
+      <c r="BM4" s="58"/>
+      <c r="BN4" s="58"/>
+      <c r="BO4" s="58"/>
+      <c r="BP4" s="58"/>
+      <c r="BQ4" s="58"/>
+      <c r="BR4" s="58"/>
+      <c r="BS4" s="58"/>
+      <c r="BT4" s="58"/>
+      <c r="BU4" s="58"/>
+      <c r="BV4" s="58"/>
+      <c r="BW4" s="58"/>
+      <c r="BX4" s="58"/>
+      <c r="BY4" s="58"/>
+      <c r="BZ4" s="58"/>
+      <c r="CA4" s="58"/>
+      <c r="CB4" s="58"/>
     </row>
-    <row r="5" spans="1:96" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="59"/>
-      <c r="E5" s="59"/>
-      <c r="F5" s="59"/>
-      <c r="G5" s="59"/>
-      <c r="H5" s="59"/>
-      <c r="I5" s="59"/>
-      <c r="J5" s="59"/>
-      <c r="K5" s="59"/>
-      <c r="L5" s="59"/>
-      <c r="M5" s="59"/>
-      <c r="N5" s="59"/>
-      <c r="O5" s="59"/>
-      <c r="P5" s="59"/>
-      <c r="Q5" s="59"/>
-      <c r="R5" s="59"/>
-      <c r="S5" s="59"/>
-      <c r="T5" s="59"/>
-      <c r="U5" s="59"/>
-      <c r="V5" s="59"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="59"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="59"/>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="59"/>
-      <c r="AE5" s="59"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="59"/>
-      <c r="AH5" s="59"/>
-      <c r="AI5" s="59"/>
-      <c r="AJ5" s="59"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="59"/>
-      <c r="AM5" s="59"/>
-      <c r="AN5" s="59"/>
-      <c r="AO5" s="59"/>
-      <c r="AP5" s="59"/>
-      <c r="AQ5" s="59"/>
-      <c r="AR5" s="59"/>
-      <c r="AS5" s="59"/>
-      <c r="AT5" s="59"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="59"/>
-      <c r="AW5" s="59"/>
-      <c r="AX5" s="59"/>
-      <c r="AY5" s="80">
+    <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="74"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="74"/>
+      <c r="U5" s="74"/>
+      <c r="V5" s="74"/>
+      <c r="W5" s="74"/>
+      <c r="X5" s="74"/>
+      <c r="Y5" s="74"/>
+      <c r="Z5" s="74"/>
+      <c r="AA5" s="74"/>
+      <c r="AB5" s="74"/>
+      <c r="AC5" s="74"/>
+      <c r="AD5" s="74"/>
+      <c r="AE5" s="74"/>
+      <c r="AF5" s="74"/>
+      <c r="AG5" s="74"/>
+      <c r="AH5" s="74"/>
+      <c r="AI5" s="74"/>
+      <c r="AJ5" s="74"/>
+      <c r="AK5" s="74"/>
+      <c r="AL5" s="74"/>
+      <c r="AM5" s="74"/>
+      <c r="AN5" s="74"/>
+      <c r="AO5" s="74"/>
+      <c r="AP5" s="74"/>
+      <c r="AQ5" s="74"/>
+      <c r="AR5" s="74"/>
+      <c r="AS5" s="74"/>
+      <c r="AT5" s="74"/>
+      <c r="AU5" s="74"/>
+      <c r="AV5" s="74"/>
+      <c r="AW5" s="74"/>
+      <c r="AX5" s="74"/>
+      <c r="AY5" s="59">
         <f>A5</f>
         <v>0</v>
       </c>
-      <c r="AZ5" s="80"/>
-      <c r="BA5" s="80"/>
-      <c r="BB5" s="80"/>
-      <c r="BC5" s="80"/>
-      <c r="BD5" s="80"/>
-      <c r="BE5" s="80"/>
-      <c r="BF5" s="80"/>
-      <c r="BG5" s="80"/>
-      <c r="BH5" s="80"/>
-      <c r="BI5" s="80"/>
-      <c r="BJ5" s="80"/>
-      <c r="BK5" s="80"/>
-      <c r="BL5" s="80"/>
-      <c r="BM5" s="80"/>
-      <c r="BN5" s="80"/>
-      <c r="BO5" s="80"/>
-      <c r="BP5" s="80"/>
-      <c r="BQ5" s="80"/>
-      <c r="BR5" s="80"/>
-      <c r="BS5" s="80"/>
-      <c r="BT5" s="80"/>
-      <c r="BU5" s="80"/>
-      <c r="BV5" s="80"/>
-      <c r="BW5" s="80"/>
-      <c r="BX5" s="80"/>
-      <c r="BY5" s="80"/>
-      <c r="BZ5" s="80"/>
-      <c r="CA5" s="80"/>
-      <c r="CB5" s="80"/>
-      <c r="CC5" s="80"/>
-      <c r="CD5" s="80"/>
-      <c r="CE5" s="80"/>
-      <c r="CF5" s="80"/>
-      <c r="CG5" s="80"/>
-      <c r="CH5" s="80"/>
-      <c r="CI5" s="80"/>
-      <c r="CJ5" s="80"/>
-      <c r="CK5" s="80"/>
-      <c r="CL5" s="80"/>
-      <c r="CM5" s="80"/>
-      <c r="CN5" s="80"/>
-      <c r="CO5" s="80"/>
-      <c r="CP5" s="80"/>
-      <c r="CQ5" s="80"/>
-      <c r="CR5" s="80"/>
+      <c r="AZ5" s="59"/>
+      <c r="BA5" s="59"/>
+      <c r="BB5" s="59"/>
+      <c r="BC5" s="59"/>
+      <c r="BD5" s="59"/>
+      <c r="BE5" s="59"/>
+      <c r="BF5" s="59"/>
+      <c r="BG5" s="59"/>
+      <c r="BH5" s="59"/>
+      <c r="BI5" s="59"/>
+      <c r="BJ5" s="59"/>
+      <c r="BK5" s="59"/>
+      <c r="BL5" s="59"/>
+      <c r="BM5" s="59"/>
+      <c r="BN5" s="59"/>
+      <c r="BO5" s="59"/>
+      <c r="BP5" s="59"/>
+      <c r="BQ5" s="59"/>
+      <c r="BR5" s="59"/>
+      <c r="BS5" s="59"/>
+      <c r="BT5" s="59"/>
+      <c r="BU5" s="59"/>
+      <c r="BV5" s="59"/>
+      <c r="BW5" s="59"/>
+      <c r="BX5" s="59"/>
+      <c r="BY5" s="59"/>
+      <c r="BZ5" s="59"/>
+      <c r="CA5" s="59"/>
+      <c r="CB5" s="59"/>
     </row>
-    <row r="6" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A6" s="71" t="s">
+    <row r="6" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A6" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="73" t="s">
+      <c r="B6" s="68" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="60" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="61"/>
-      <c r="E6" s="62"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="60" t="s">
+      <c r="C6" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="55"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="55"/>
+      <c r="I6" s="56"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="55"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="75"/>
+      <c r="O6" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="T6" s="55"/>
+      <c r="U6" s="56"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="X6" s="55"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="75"/>
+      <c r="AA6" s="54" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="55"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="57"/>
+      <c r="AE6" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="AF6" s="55"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
+      <c r="AI6" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="55"/>
+      <c r="AK6" s="56"/>
+      <c r="AL6" s="56"/>
+      <c r="AM6" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN6" s="55"/>
+      <c r="AO6" s="56"/>
+      <c r="AP6" s="75"/>
+      <c r="AQ6" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR6" s="55"/>
+      <c r="AS6" s="56"/>
+      <c r="AT6" s="57"/>
+      <c r="AU6" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV6" s="77"/>
+      <c r="AW6" s="78"/>
+      <c r="AX6" s="79"/>
+      <c r="AY6" s="66" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="68" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H6" s="61"/>
-      <c r="I6" s="62"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="60" t="s">
-        <v>2</v>
-      </c>
-      <c r="L6" s="61"/>
-      <c r="M6" s="62"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="60" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="61"/>
-      <c r="Q6" s="62"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="T6" s="61"/>
-      <c r="U6" s="62"/>
-      <c r="V6" s="62"/>
-      <c r="W6" s="60" t="s">
+      <c r="BB6" s="53"/>
+      <c r="BC6" s="53"/>
+      <c r="BD6" s="53"/>
+      <c r="BE6" s="60" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF6" s="53"/>
+      <c r="BG6" s="53"/>
+      <c r="BH6" s="53"/>
+      <c r="BI6" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="X6" s="61"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="60" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="61"/>
-      <c r="AC6" s="62"/>
-      <c r="AD6" s="64"/>
-      <c r="AE6" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="AF6" s="61"/>
-      <c r="AG6" s="62"/>
-      <c r="AH6" s="62"/>
-      <c r="AI6" s="60" t="s">
+      <c r="BJ6" s="55"/>
+      <c r="BK6" s="56"/>
+      <c r="BL6" s="57"/>
+      <c r="BM6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="AJ6" s="61"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="60" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN6" s="61"/>
-      <c r="AO6" s="62"/>
-      <c r="AP6" s="63"/>
-      <c r="AQ6" s="60" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR6" s="61"/>
-      <c r="AS6" s="62"/>
-      <c r="AT6" s="64"/>
-      <c r="AU6" s="65" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="66"/>
-      <c r="AW6" s="67"/>
-      <c r="AX6" s="68"/>
-      <c r="AY6" s="71" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA6" s="81" t="s">
-        <v>16</v>
-      </c>
-      <c r="BB6" s="79"/>
-      <c r="BC6" s="79"/>
-      <c r="BD6" s="79"/>
-      <c r="BE6" s="81" t="s">
-        <v>10</v>
-      </c>
-      <c r="BF6" s="79"/>
-      <c r="BG6" s="79"/>
-      <c r="BH6" s="79"/>
-      <c r="BI6" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="BJ6" s="61"/>
-      <c r="BK6" s="62"/>
-      <c r="BL6" s="64"/>
-      <c r="BM6" s="81" t="s">
+      <c r="BN6" s="53"/>
+      <c r="BO6" s="53"/>
+      <c r="BP6" s="53"/>
+      <c r="BQ6" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="BR6" s="53"/>
+      <c r="BS6" s="53"/>
+      <c r="BT6" s="61"/>
+      <c r="BU6" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="BV6" s="53"/>
+      <c r="BW6" s="53"/>
+      <c r="BX6" s="53"/>
+      <c r="BY6" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="BN6" s="79"/>
-      <c r="BO6" s="79"/>
-      <c r="BP6" s="79"/>
-      <c r="BQ6" s="81" t="s">
+      <c r="BZ6" s="55"/>
+      <c r="CA6" s="56"/>
+      <c r="CB6" s="57"/>
+    </row>
+    <row r="7" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A7" s="67"/>
+      <c r="B7" s="69"/>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AK7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AO7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP7" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AS7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="AU7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="AV7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AW7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX7" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="BR6" s="79"/>
-      <c r="BS6" s="79"/>
-      <c r="BT6" s="82"/>
-      <c r="BU6" s="79" t="s">
-        <v>33</v>
-      </c>
-      <c r="BV6" s="79"/>
-      <c r="BW6" s="79"/>
-      <c r="BX6" s="79"/>
-      <c r="BY6" s="60" t="s">
-        <v>6</v>
-      </c>
-      <c r="BZ6" s="61"/>
-      <c r="CA6" s="62"/>
-      <c r="CB6" s="64"/>
-      <c r="CC6" s="81"/>
-      <c r="CD6" s="79"/>
-      <c r="CE6" s="79"/>
-      <c r="CF6" s="79"/>
-      <c r="CG6" s="81"/>
-      <c r="CH6" s="79"/>
-      <c r="CI6" s="79"/>
-      <c r="CJ6" s="82"/>
-      <c r="CK6" s="79"/>
-      <c r="CL6" s="79"/>
-      <c r="CM6" s="79"/>
-      <c r="CN6" s="79"/>
-      <c r="CO6" s="83"/>
-      <c r="CP6" s="84"/>
-      <c r="CQ6" s="85"/>
-      <c r="CR6" s="86"/>
+      <c r="AY7" s="67"/>
+      <c r="AZ7" s="69"/>
+      <c r="BA7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="BB7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BC7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BE7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="BF7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BG7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH7" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BJ7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="BK7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="BM7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="BN7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BO7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BQ7" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="BR7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BS7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT7" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="BU7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="BV7" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="BW7" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="BZ7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="CA7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB7" s="5" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="7" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A7" s="72"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="T7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="U7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Y7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AC7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AF7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AJ7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AK7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AL7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AM7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AO7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AP7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AR7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="AS7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="AT7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="AU7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="AV7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="AW7" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AX7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="AY7" s="72"/>
-      <c r="AZ7" s="74"/>
-      <c r="BA7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="BB7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BC7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="BD7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BE7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="BF7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BG7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="BH7" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="BI7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="BJ7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="BK7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="BL7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="BM7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="BN7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BO7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="BP7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BQ7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="BR7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BS7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="BT7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="BU7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="BV7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BW7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="BX7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BY7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="BZ7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="CA7" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="CB7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="CC7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="CD7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="CE7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="CF7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="CG7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="CH7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="CI7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="CJ7" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="CK7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="CL7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="CM7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="CN7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="CO7" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="CP7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="CQ7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="CR7" s="15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" s="16">
         <v>1</v>
       </c>
@@ -3025,36 +2843,8 @@
         <f t="shared" ref="CB8:CB37" si="19">IF(SUM(BY8:CA8)=0,"",ROUND(AVERAGE(BY8:CA8),0))</f>
         <v/>
       </c>
-      <c r="CC8" s="29"/>
-      <c r="CD8" s="27"/>
-      <c r="CE8" s="28"/>
-      <c r="CF8" s="28" t="str">
-        <f t="shared" ref="CF8:CF37" si="20">IF(SUM(CC8:CE8)=0,"",ROUND(AVERAGE(CC8:CE8),0))</f>
-        <v/>
-      </c>
-      <c r="CG8" s="29"/>
-      <c r="CH8" s="27"/>
-      <c r="CI8" s="28"/>
-      <c r="CJ8" s="30" t="str">
-        <f t="shared" ref="CJ8:CJ37" si="21">IF(SUM(CG8:CI8)=0,"",ROUND(AVERAGE(CG8:CI8),0))</f>
-        <v/>
-      </c>
-      <c r="CK8" s="29"/>
-      <c r="CL8" s="27"/>
-      <c r="CM8" s="28"/>
-      <c r="CN8" s="28" t="str">
-        <f t="shared" ref="CN8:CN37" si="22">IF(SUM(CK8:CM8)=0,"",ROUND(AVERAGE(CK8:CM8),0))</f>
-        <v/>
-      </c>
-      <c r="CO8" s="29"/>
-      <c r="CP8" s="27"/>
-      <c r="CQ8" s="28"/>
-      <c r="CR8" s="87" t="str">
-        <f t="shared" ref="CR8:CR37" si="23">IF(SUM(CO8:CQ8)=0,"",ROUND(AVERAGE(CO8:CQ8),0))</f>
-        <v/>
-      </c>
     </row>
-    <row r="9" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A9" s="31">
         <v>2</v>
       </c>
@@ -3067,19 +2857,19 @@
         <v/>
       </c>
       <c r="G9" s="33" t="str">
-        <f t="shared" ref="G9:G37" si="24">IF(BI9="","",BI9)</f>
+        <f t="shared" ref="G9:G37" si="20">IF(BI9="","",BI9)</f>
         <v/>
       </c>
       <c r="H9" s="34" t="str">
-        <f t="shared" ref="H9:H37" si="25">IF(BJ9="","",BJ9)</f>
+        <f t="shared" ref="H9:H37" si="21">IF(BJ9="","",BJ9)</f>
         <v/>
       </c>
       <c r="I9" s="35" t="str">
-        <f t="shared" ref="I9:I37" si="26">IF(BK9="","",BK9)</f>
+        <f t="shared" ref="I9:I37" si="22">IF(BK9="","",BK9)</f>
         <v/>
       </c>
       <c r="J9" s="36" t="str">
-        <f t="shared" ref="J9:J37" si="27">IF(BL9="","",BL9)</f>
+        <f t="shared" ref="J9:J37" si="23">IF(BL9="","",BL9)</f>
         <v/>
       </c>
       <c r="K9" s="33"/>
@@ -3125,7 +2915,7 @@
         <v/>
       </c>
       <c r="AI9" s="33" t="str">
-        <f t="shared" ref="AI9:AI37" si="28">IF(BY9="","",BY9)</f>
+        <f t="shared" ref="AI9:AI37" si="24">IF(BY9="","",BY9)</f>
         <v/>
       </c>
       <c r="AJ9" s="34" t="str">
@@ -3165,7 +2955,7 @@
         <v>2</v>
       </c>
       <c r="AZ9" s="32" t="str">
-        <f t="shared" ref="AZ9:AZ37" si="29">IF(B9="","",B9)</f>
+        <f t="shared" ref="AZ9:AZ37" si="25">IF(B9="","",B9)</f>
         <v/>
       </c>
       <c r="BA9" s="40"/>
@@ -3217,36 +3007,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC9" s="40"/>
-      <c r="CD9" s="38"/>
-      <c r="CE9" s="39"/>
-      <c r="CF9" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG9" s="40"/>
-      <c r="CH9" s="38"/>
-      <c r="CI9" s="39"/>
-      <c r="CJ9" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK9" s="40"/>
-      <c r="CL9" s="38"/>
-      <c r="CM9" s="39"/>
-      <c r="CN9" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO9" s="40"/>
-      <c r="CP9" s="38"/>
-      <c r="CQ9" s="39"/>
-      <c r="CR9" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="10" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A10" s="31">
         <v>3</v>
       </c>
@@ -3259,19 +3021,19 @@
         <v/>
       </c>
       <c r="G10" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H10" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I10" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J10" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K10" s="33"/>
@@ -3317,7 +3079,7 @@
         <v/>
       </c>
       <c r="AI10" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ10" s="34" t="str">
@@ -3357,7 +3119,7 @@
         <v>3</v>
       </c>
       <c r="AZ10" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA10" s="40"/>
@@ -3409,36 +3171,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC10" s="40"/>
-      <c r="CD10" s="38"/>
-      <c r="CE10" s="39"/>
-      <c r="CF10" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG10" s="40"/>
-      <c r="CH10" s="38"/>
-      <c r="CI10" s="39"/>
-      <c r="CJ10" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK10" s="40"/>
-      <c r="CL10" s="38"/>
-      <c r="CM10" s="39"/>
-      <c r="CN10" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO10" s="40"/>
-      <c r="CP10" s="38"/>
-      <c r="CQ10" s="39"/>
-      <c r="CR10" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="11" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A11" s="31">
         <v>4</v>
       </c>
@@ -3447,23 +3181,23 @@
       <c r="D11" s="34"/>
       <c r="E11" s="35"/>
       <c r="F11" s="36" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(SUM(C11:E11)=0,"",ROUND(AVERAGE(C11:E11),0))</f>
         <v/>
       </c>
       <c r="G11" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H11" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I11" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J11" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K11" s="33"/>
@@ -3509,7 +3243,7 @@
         <v/>
       </c>
       <c r="AI11" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ11" s="34" t="str">
@@ -3549,7 +3283,7 @@
         <v>4</v>
       </c>
       <c r="AZ11" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA11" s="40"/>
@@ -3601,36 +3335,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC11" s="40"/>
-      <c r="CD11" s="38"/>
-      <c r="CE11" s="39"/>
-      <c r="CF11" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG11" s="40"/>
-      <c r="CH11" s="38"/>
-      <c r="CI11" s="39"/>
-      <c r="CJ11" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK11" s="40"/>
-      <c r="CL11" s="38"/>
-      <c r="CM11" s="39"/>
-      <c r="CN11" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO11" s="40"/>
-      <c r="CP11" s="38"/>
-      <c r="CQ11" s="39"/>
-      <c r="CR11" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="12" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A12" s="31">
         <v>5</v>
       </c>
@@ -3643,19 +3349,19 @@
         <v/>
       </c>
       <c r="G12" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H12" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I12" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J12" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K12" s="33"/>
@@ -3701,7 +3407,7 @@
         <v/>
       </c>
       <c r="AI12" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ12" s="34" t="str">
@@ -3741,7 +3447,7 @@
         <v>5</v>
       </c>
       <c r="AZ12" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA12" s="40"/>
@@ -3793,36 +3499,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC12" s="40"/>
-      <c r="CD12" s="38"/>
-      <c r="CE12" s="39"/>
-      <c r="CF12" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG12" s="40"/>
-      <c r="CH12" s="38"/>
-      <c r="CI12" s="39"/>
-      <c r="CJ12" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK12" s="40"/>
-      <c r="CL12" s="38"/>
-      <c r="CM12" s="39"/>
-      <c r="CN12" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO12" s="40"/>
-      <c r="CP12" s="38"/>
-      <c r="CQ12" s="39"/>
-      <c r="CR12" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="13" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A13" s="31">
         <v>6</v>
       </c>
@@ -3831,23 +3509,23 @@
       <c r="D13" s="34"/>
       <c r="E13" s="35"/>
       <c r="F13" s="36" t="str">
-        <f>IF(SUM(C13:E13)=0,"",ROUND(AVERAGE(C13:E13),0))</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="G13" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H13" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I13" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J13" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K13" s="33"/>
@@ -3893,7 +3571,7 @@
         <v/>
       </c>
       <c r="AI13" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ13" s="34" t="str">
@@ -3933,7 +3611,7 @@
         <v>6</v>
       </c>
       <c r="AZ13" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA13" s="40"/>
@@ -3985,36 +3663,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC13" s="40"/>
-      <c r="CD13" s="38"/>
-      <c r="CE13" s="39"/>
-      <c r="CF13" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG13" s="40"/>
-      <c r="CH13" s="38"/>
-      <c r="CI13" s="39"/>
-      <c r="CJ13" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK13" s="40"/>
-      <c r="CL13" s="38"/>
-      <c r="CM13" s="39"/>
-      <c r="CN13" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO13" s="40"/>
-      <c r="CP13" s="38"/>
-      <c r="CQ13" s="39"/>
-      <c r="CR13" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="14" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A14" s="31">
         <v>7</v>
       </c>
@@ -4027,19 +3677,19 @@
         <v/>
       </c>
       <c r="G14" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H14" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I14" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J14" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K14" s="33"/>
@@ -4085,7 +3735,7 @@
         <v/>
       </c>
       <c r="AI14" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ14" s="34" t="str">
@@ -4125,7 +3775,7 @@
         <v>7</v>
       </c>
       <c r="AZ14" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA14" s="40"/>
@@ -4177,36 +3827,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC14" s="40"/>
-      <c r="CD14" s="38"/>
-      <c r="CE14" s="39"/>
-      <c r="CF14" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG14" s="40"/>
-      <c r="CH14" s="38"/>
-      <c r="CI14" s="39"/>
-      <c r="CJ14" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK14" s="40"/>
-      <c r="CL14" s="38"/>
-      <c r="CM14" s="39"/>
-      <c r="CN14" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO14" s="40"/>
-      <c r="CP14" s="38"/>
-      <c r="CQ14" s="39"/>
-      <c r="CR14" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="15" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A15" s="31">
         <v>8</v>
       </c>
@@ -4219,19 +3841,19 @@
         <v/>
       </c>
       <c r="G15" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H15" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I15" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J15" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K15" s="33"/>
@@ -4277,7 +3899,7 @@
         <v/>
       </c>
       <c r="AI15" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ15" s="34" t="str">
@@ -4317,7 +3939,7 @@
         <v>8</v>
       </c>
       <c r="AZ15" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA15" s="40"/>
@@ -4369,36 +3991,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC15" s="40"/>
-      <c r="CD15" s="38"/>
-      <c r="CE15" s="39"/>
-      <c r="CF15" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG15" s="40"/>
-      <c r="CH15" s="38"/>
-      <c r="CI15" s="39"/>
-      <c r="CJ15" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK15" s="40"/>
-      <c r="CL15" s="38"/>
-      <c r="CM15" s="39"/>
-      <c r="CN15" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO15" s="40"/>
-      <c r="CP15" s="38"/>
-      <c r="CQ15" s="39"/>
-      <c r="CR15" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="16" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A16" s="31">
         <v>9</v>
       </c>
@@ -4411,19 +4005,19 @@
         <v/>
       </c>
       <c r="G16" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H16" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I16" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J16" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K16" s="33"/>
@@ -4469,7 +4063,7 @@
         <v/>
       </c>
       <c r="AI16" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ16" s="34" t="str">
@@ -4509,7 +4103,7 @@
         <v>9</v>
       </c>
       <c r="AZ16" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA16" s="40"/>
@@ -4561,36 +4155,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC16" s="40"/>
-      <c r="CD16" s="38"/>
-      <c r="CE16" s="39"/>
-      <c r="CF16" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG16" s="40"/>
-      <c r="CH16" s="38"/>
-      <c r="CI16" s="39"/>
-      <c r="CJ16" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK16" s="40"/>
-      <c r="CL16" s="38"/>
-      <c r="CM16" s="39"/>
-      <c r="CN16" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO16" s="40"/>
-      <c r="CP16" s="38"/>
-      <c r="CQ16" s="39"/>
-      <c r="CR16" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="17" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" s="31">
         <v>10</v>
       </c>
@@ -4603,19 +4169,19 @@
         <v/>
       </c>
       <c r="G17" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H17" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I17" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J17" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K17" s="33"/>
@@ -4661,7 +4227,7 @@
         <v/>
       </c>
       <c r="AI17" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ17" s="34" t="str">
@@ -4701,7 +4267,7 @@
         <v>10</v>
       </c>
       <c r="AZ17" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA17" s="40"/>
@@ -4753,36 +4319,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC17" s="40"/>
-      <c r="CD17" s="38"/>
-      <c r="CE17" s="39"/>
-      <c r="CF17" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG17" s="40"/>
-      <c r="CH17" s="38"/>
-      <c r="CI17" s="39"/>
-      <c r="CJ17" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK17" s="40"/>
-      <c r="CL17" s="38"/>
-      <c r="CM17" s="39"/>
-      <c r="CN17" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO17" s="40"/>
-      <c r="CP17" s="38"/>
-      <c r="CQ17" s="39"/>
-      <c r="CR17" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="18" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" s="31">
         <v>11</v>
       </c>
@@ -4795,19 +4333,19 @@
         <v/>
       </c>
       <c r="G18" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H18" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I18" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J18" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K18" s="33"/>
@@ -4853,7 +4391,7 @@
         <v/>
       </c>
       <c r="AI18" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ18" s="34" t="str">
@@ -4893,7 +4431,7 @@
         <v>11</v>
       </c>
       <c r="AZ18" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA18" s="40"/>
@@ -4945,36 +4483,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC18" s="40"/>
-      <c r="CD18" s="38"/>
-      <c r="CE18" s="39"/>
-      <c r="CF18" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG18" s="40"/>
-      <c r="CH18" s="38"/>
-      <c r="CI18" s="39"/>
-      <c r="CJ18" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK18" s="40"/>
-      <c r="CL18" s="38"/>
-      <c r="CM18" s="39"/>
-      <c r="CN18" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO18" s="40"/>
-      <c r="CP18" s="38"/>
-      <c r="CQ18" s="39"/>
-      <c r="CR18" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="19" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" s="31">
         <v>12</v>
       </c>
@@ -4987,19 +4497,19 @@
         <v/>
       </c>
       <c r="G19" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H19" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I19" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J19" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K19" s="33"/>
@@ -5045,7 +4555,7 @@
         <v/>
       </c>
       <c r="AI19" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ19" s="34" t="str">
@@ -5085,7 +4595,7 @@
         <v>12</v>
       </c>
       <c r="AZ19" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA19" s="40"/>
@@ -5137,36 +4647,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC19" s="40"/>
-      <c r="CD19" s="38"/>
-      <c r="CE19" s="39"/>
-      <c r="CF19" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG19" s="40"/>
-      <c r="CH19" s="38"/>
-      <c r="CI19" s="39"/>
-      <c r="CJ19" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK19" s="40"/>
-      <c r="CL19" s="38"/>
-      <c r="CM19" s="39"/>
-      <c r="CN19" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO19" s="40"/>
-      <c r="CP19" s="38"/>
-      <c r="CQ19" s="39"/>
-      <c r="CR19" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="20" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" s="31">
         <v>13</v>
       </c>
@@ -5179,19 +4661,19 @@
         <v/>
       </c>
       <c r="G20" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H20" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I20" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J20" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K20" s="33"/>
@@ -5237,7 +4719,7 @@
         <v/>
       </c>
       <c r="AI20" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ20" s="34" t="str">
@@ -5277,7 +4759,7 @@
         <v>13</v>
       </c>
       <c r="AZ20" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA20" s="40"/>
@@ -5329,36 +4811,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC20" s="40"/>
-      <c r="CD20" s="38"/>
-      <c r="CE20" s="39"/>
-      <c r="CF20" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG20" s="40"/>
-      <c r="CH20" s="38"/>
-      <c r="CI20" s="39"/>
-      <c r="CJ20" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK20" s="40"/>
-      <c r="CL20" s="38"/>
-      <c r="CM20" s="39"/>
-      <c r="CN20" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO20" s="40"/>
-      <c r="CP20" s="38"/>
-      <c r="CQ20" s="39"/>
-      <c r="CR20" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="21" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" s="31">
         <v>14</v>
       </c>
@@ -5371,19 +4825,19 @@
         <v/>
       </c>
       <c r="G21" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H21" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I21" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J21" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K21" s="33"/>
@@ -5429,7 +4883,7 @@
         <v/>
       </c>
       <c r="AI21" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ21" s="34" t="str">
@@ -5469,7 +4923,7 @@
         <v>14</v>
       </c>
       <c r="AZ21" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA21" s="40"/>
@@ -5521,36 +4975,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC21" s="40"/>
-      <c r="CD21" s="38"/>
-      <c r="CE21" s="39"/>
-      <c r="CF21" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG21" s="40"/>
-      <c r="CH21" s="38"/>
-      <c r="CI21" s="39"/>
-      <c r="CJ21" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK21" s="40"/>
-      <c r="CL21" s="38"/>
-      <c r="CM21" s="39"/>
-      <c r="CN21" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO21" s="40"/>
-      <c r="CP21" s="38"/>
-      <c r="CQ21" s="39"/>
-      <c r="CR21" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="22" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" s="31">
         <v>15</v>
       </c>
@@ -5563,19 +4989,19 @@
         <v/>
       </c>
       <c r="G22" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H22" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I22" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J22" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K22" s="33"/>
@@ -5621,7 +5047,7 @@
         <v/>
       </c>
       <c r="AI22" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ22" s="34" t="str">
@@ -5661,7 +5087,7 @@
         <v>15</v>
       </c>
       <c r="AZ22" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA22" s="40"/>
@@ -5713,36 +5139,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC22" s="40"/>
-      <c r="CD22" s="38"/>
-      <c r="CE22" s="39"/>
-      <c r="CF22" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG22" s="40"/>
-      <c r="CH22" s="38"/>
-      <c r="CI22" s="39"/>
-      <c r="CJ22" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK22" s="40"/>
-      <c r="CL22" s="38"/>
-      <c r="CM22" s="39"/>
-      <c r="CN22" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO22" s="40"/>
-      <c r="CP22" s="38"/>
-      <c r="CQ22" s="39"/>
-      <c r="CR22" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="23" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" s="31">
         <v>16</v>
       </c>
@@ -5755,19 +5153,19 @@
         <v/>
       </c>
       <c r="G23" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H23" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I23" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J23" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K23" s="33"/>
@@ -5813,7 +5211,7 @@
         <v/>
       </c>
       <c r="AI23" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ23" s="34" t="str">
@@ -5853,7 +5251,7 @@
         <v>16</v>
       </c>
       <c r="AZ23" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA23" s="40"/>
@@ -5905,36 +5303,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC23" s="40"/>
-      <c r="CD23" s="38"/>
-      <c r="CE23" s="39"/>
-      <c r="CF23" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG23" s="40"/>
-      <c r="CH23" s="38"/>
-      <c r="CI23" s="39"/>
-      <c r="CJ23" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK23" s="40"/>
-      <c r="CL23" s="38"/>
-      <c r="CM23" s="39"/>
-      <c r="CN23" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO23" s="40"/>
-      <c r="CP23" s="38"/>
-      <c r="CQ23" s="39"/>
-      <c r="CR23" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="24" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A24" s="31">
         <v>17</v>
       </c>
@@ -5947,19 +5317,19 @@
         <v/>
       </c>
       <c r="G24" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H24" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I24" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J24" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K24" s="33"/>
@@ -6005,19 +5375,19 @@
         <v/>
       </c>
       <c r="AI24" s="33" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="AJ24" s="34" t="str">
-        <f t="shared" ref="AJ24:AJ37" si="30">IF(BZ24="","",BZ24)</f>
+        <f t="shared" ref="AJ24:AJ37" si="26">IF(BZ24="","",BZ24)</f>
         <v/>
       </c>
       <c r="AK24" s="35" t="str">
-        <f t="shared" ref="AK24:AK37" si="31">IF(CA24="","",CA24)</f>
+        <f t="shared" ref="AK24:AK37" si="27">IF(CA24="","",CA24)</f>
         <v/>
       </c>
       <c r="AL24" s="35" t="str">
-        <f t="shared" ref="AL24:AL37" si="32">IF(CB24="","",CB24)</f>
+        <f t="shared" ref="AL24:AL37" si="28">IF(CB24="","",CB24)</f>
         <v/>
       </c>
       <c r="AM24" s="33"/>
@@ -6045,7 +5415,7 @@
         <v>17</v>
       </c>
       <c r="AZ24" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA24" s="40"/>
@@ -6097,36 +5467,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC24" s="40"/>
-      <c r="CD24" s="38"/>
-      <c r="CE24" s="39"/>
-      <c r="CF24" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG24" s="40"/>
-      <c r="CH24" s="38"/>
-      <c r="CI24" s="39"/>
-      <c r="CJ24" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK24" s="40"/>
-      <c r="CL24" s="38"/>
-      <c r="CM24" s="39"/>
-      <c r="CN24" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO24" s="40"/>
-      <c r="CP24" s="38"/>
-      <c r="CQ24" s="39"/>
-      <c r="CR24" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="25" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A25" s="31">
         <v>18</v>
       </c>
@@ -6139,19 +5481,19 @@
         <v/>
       </c>
       <c r="G25" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H25" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I25" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J25" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K25" s="33"/>
@@ -6197,19 +5539,19 @@
         <v/>
       </c>
       <c r="AI25" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ25" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK25" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL25" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ25" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK25" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL25" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM25" s="33"/>
@@ -6237,7 +5579,7 @@
         <v>18</v>
       </c>
       <c r="AZ25" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA25" s="40"/>
@@ -6289,36 +5631,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC25" s="40"/>
-      <c r="CD25" s="38"/>
-      <c r="CE25" s="39"/>
-      <c r="CF25" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG25" s="40"/>
-      <c r="CH25" s="38"/>
-      <c r="CI25" s="39"/>
-      <c r="CJ25" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK25" s="40"/>
-      <c r="CL25" s="38"/>
-      <c r="CM25" s="39"/>
-      <c r="CN25" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO25" s="40"/>
-      <c r="CP25" s="38"/>
-      <c r="CQ25" s="39"/>
-      <c r="CR25" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="26" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A26" s="31">
         <v>19</v>
       </c>
@@ -6331,19 +5645,19 @@
         <v/>
       </c>
       <c r="G26" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H26" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I26" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J26" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K26" s="33"/>
@@ -6389,19 +5703,19 @@
         <v/>
       </c>
       <c r="AI26" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ26" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK26" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL26" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ26" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK26" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL26" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM26" s="33"/>
@@ -6429,7 +5743,7 @@
         <v>19</v>
       </c>
       <c r="AZ26" s="46" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA26" s="40"/>
@@ -6481,36 +5795,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC26" s="40"/>
-      <c r="CD26" s="38"/>
-      <c r="CE26" s="39"/>
-      <c r="CF26" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG26" s="40"/>
-      <c r="CH26" s="38"/>
-      <c r="CI26" s="39"/>
-      <c r="CJ26" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK26" s="40"/>
-      <c r="CL26" s="38"/>
-      <c r="CM26" s="39"/>
-      <c r="CN26" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO26" s="40"/>
-      <c r="CP26" s="38"/>
-      <c r="CQ26" s="39"/>
-      <c r="CR26" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="27" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A27" s="31">
         <v>20</v>
       </c>
@@ -6523,19 +5809,19 @@
         <v/>
       </c>
       <c r="G27" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H27" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I27" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J27" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K27" s="33"/>
@@ -6581,19 +5867,19 @@
         <v/>
       </c>
       <c r="AI27" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ27" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK27" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL27" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ27" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK27" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL27" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM27" s="33"/>
@@ -6621,7 +5907,7 @@
         <v>20</v>
       </c>
       <c r="AZ27" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA27" s="40"/>
@@ -6673,36 +5959,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC27" s="40"/>
-      <c r="CD27" s="38"/>
-      <c r="CE27" s="39"/>
-      <c r="CF27" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG27" s="40"/>
-      <c r="CH27" s="38"/>
-      <c r="CI27" s="39"/>
-      <c r="CJ27" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK27" s="40"/>
-      <c r="CL27" s="38"/>
-      <c r="CM27" s="39"/>
-      <c r="CN27" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO27" s="40"/>
-      <c r="CP27" s="38"/>
-      <c r="CQ27" s="39"/>
-      <c r="CR27" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="28" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A28" s="31">
         <v>21</v>
       </c>
@@ -6715,19 +5973,19 @@
         <v/>
       </c>
       <c r="G28" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H28" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I28" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J28" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K28" s="33"/>
@@ -6773,19 +6031,19 @@
         <v/>
       </c>
       <c r="AI28" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ28" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK28" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL28" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ28" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK28" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL28" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM28" s="33"/>
@@ -6813,7 +6071,7 @@
         <v>21</v>
       </c>
       <c r="AZ28" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA28" s="40"/>
@@ -6865,36 +6123,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC28" s="40"/>
-      <c r="CD28" s="38"/>
-      <c r="CE28" s="39"/>
-      <c r="CF28" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG28" s="40"/>
-      <c r="CH28" s="38"/>
-      <c r="CI28" s="39"/>
-      <c r="CJ28" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK28" s="40"/>
-      <c r="CL28" s="38"/>
-      <c r="CM28" s="39"/>
-      <c r="CN28" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO28" s="40"/>
-      <c r="CP28" s="38"/>
-      <c r="CQ28" s="39"/>
-      <c r="CR28" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="29" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A29" s="31">
         <v>22</v>
       </c>
@@ -6907,19 +6137,19 @@
         <v/>
       </c>
       <c r="G29" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H29" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I29" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J29" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K29" s="33"/>
@@ -6965,19 +6195,19 @@
         <v/>
       </c>
       <c r="AI29" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ29" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK29" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL29" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ29" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK29" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL29" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM29" s="33"/>
@@ -7005,7 +6235,7 @@
         <v>22</v>
       </c>
       <c r="AZ29" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA29" s="40"/>
@@ -7031,7 +6261,7 @@
       </c>
       <c r="BM29" s="40"/>
       <c r="BN29" s="38"/>
-      <c r="BO29" s="89"/>
+      <c r="BO29" s="39"/>
       <c r="BP29" s="39" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -7057,36 +6287,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC29" s="40"/>
-      <c r="CD29" s="38"/>
-      <c r="CE29" s="39"/>
-      <c r="CF29" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG29" s="40"/>
-      <c r="CH29" s="38"/>
-      <c r="CI29" s="39"/>
-      <c r="CJ29" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK29" s="40"/>
-      <c r="CL29" s="38"/>
-      <c r="CM29" s="39"/>
-      <c r="CN29" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO29" s="40"/>
-      <c r="CP29" s="38"/>
-      <c r="CQ29" s="39"/>
-      <c r="CR29" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="30" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A30" s="31">
         <v>23</v>
       </c>
@@ -7099,19 +6301,19 @@
         <v/>
       </c>
       <c r="G30" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H30" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I30" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J30" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K30" s="33"/>
@@ -7157,19 +6359,19 @@
         <v/>
       </c>
       <c r="AI30" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ30" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK30" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL30" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ30" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK30" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL30" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM30" s="33"/>
@@ -7197,7 +6399,7 @@
         <v>23</v>
       </c>
       <c r="AZ30" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA30" s="40"/>
@@ -7249,36 +6451,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC30" s="40"/>
-      <c r="CD30" s="38"/>
-      <c r="CE30" s="39"/>
-      <c r="CF30" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG30" s="40"/>
-      <c r="CH30" s="38"/>
-      <c r="CI30" s="39"/>
-      <c r="CJ30" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK30" s="40"/>
-      <c r="CL30" s="38"/>
-      <c r="CM30" s="39"/>
-      <c r="CN30" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO30" s="40"/>
-      <c r="CP30" s="38"/>
-      <c r="CQ30" s="39"/>
-      <c r="CR30" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="31" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A31" s="31">
         <v>24</v>
       </c>
@@ -7291,19 +6465,19 @@
         <v/>
       </c>
       <c r="G31" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H31" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I31" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J31" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K31" s="33"/>
@@ -7349,19 +6523,19 @@
         <v/>
       </c>
       <c r="AI31" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ31" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK31" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL31" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ31" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK31" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL31" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM31" s="33"/>
@@ -7389,7 +6563,7 @@
         <v>24</v>
       </c>
       <c r="AZ31" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA31" s="40"/>
@@ -7441,36 +6615,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC31" s="40"/>
-      <c r="CD31" s="38"/>
-      <c r="CE31" s="39"/>
-      <c r="CF31" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG31" s="40"/>
-      <c r="CH31" s="38"/>
-      <c r="CI31" s="39"/>
-      <c r="CJ31" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK31" s="40"/>
-      <c r="CL31" s="38"/>
-      <c r="CM31" s="39"/>
-      <c r="CN31" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO31" s="40"/>
-      <c r="CP31" s="38"/>
-      <c r="CQ31" s="39"/>
-      <c r="CR31" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="32" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A32" s="31">
         <v>25</v>
       </c>
@@ -7483,19 +6629,19 @@
         <v/>
       </c>
       <c r="G32" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H32" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I32" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J32" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K32" s="33"/>
@@ -7541,19 +6687,19 @@
         <v/>
       </c>
       <c r="AI32" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ32" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK32" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL32" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ32" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK32" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL32" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM32" s="33"/>
@@ -7581,7 +6727,7 @@
         <v>25</v>
       </c>
       <c r="AZ32" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA32" s="40"/>
@@ -7633,36 +6779,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC32" s="40"/>
-      <c r="CD32" s="38"/>
-      <c r="CE32" s="39"/>
-      <c r="CF32" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG32" s="40"/>
-      <c r="CH32" s="38"/>
-      <c r="CI32" s="39"/>
-      <c r="CJ32" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK32" s="40"/>
-      <c r="CL32" s="38"/>
-      <c r="CM32" s="39"/>
-      <c r="CN32" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO32" s="40"/>
-      <c r="CP32" s="38"/>
-      <c r="CQ32" s="39"/>
-      <c r="CR32" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="33" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A33" s="31">
         <v>26</v>
       </c>
@@ -7675,19 +6793,19 @@
         <v/>
       </c>
       <c r="G33" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H33" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I33" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J33" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K33" s="33"/>
@@ -7733,19 +6851,19 @@
         <v/>
       </c>
       <c r="AI33" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ33" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK33" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL33" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ33" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK33" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL33" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM33" s="33"/>
@@ -7773,7 +6891,7 @@
         <v>26</v>
       </c>
       <c r="AZ33" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA33" s="40"/>
@@ -7825,36 +6943,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC33" s="40"/>
-      <c r="CD33" s="38"/>
-      <c r="CE33" s="39"/>
-      <c r="CF33" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG33" s="40"/>
-      <c r="CH33" s="38"/>
-      <c r="CI33" s="39"/>
-      <c r="CJ33" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK33" s="40"/>
-      <c r="CL33" s="38"/>
-      <c r="CM33" s="39"/>
-      <c r="CN33" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO33" s="40"/>
-      <c r="CP33" s="38"/>
-      <c r="CQ33" s="39"/>
-      <c r="CR33" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="34" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A34" s="31">
         <v>27</v>
       </c>
@@ -7867,19 +6957,19 @@
         <v/>
       </c>
       <c r="G34" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H34" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I34" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J34" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K34" s="33"/>
@@ -7925,19 +7015,19 @@
         <v/>
       </c>
       <c r="AI34" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ34" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK34" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL34" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ34" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK34" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL34" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM34" s="33"/>
@@ -7965,7 +7055,7 @@
         <v>27</v>
       </c>
       <c r="AZ34" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA34" s="40"/>
@@ -8017,36 +7107,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC34" s="40"/>
-      <c r="CD34" s="38"/>
-      <c r="CE34" s="39"/>
-      <c r="CF34" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG34" s="40"/>
-      <c r="CH34" s="38"/>
-      <c r="CI34" s="39"/>
-      <c r="CJ34" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK34" s="40"/>
-      <c r="CL34" s="38"/>
-      <c r="CM34" s="39"/>
-      <c r="CN34" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO34" s="40"/>
-      <c r="CP34" s="38"/>
-      <c r="CQ34" s="39"/>
-      <c r="CR34" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="35" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A35" s="31">
         <v>28</v>
       </c>
@@ -8059,19 +7121,19 @@
         <v/>
       </c>
       <c r="G35" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H35" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I35" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J35" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K35" s="33"/>
@@ -8117,19 +7179,19 @@
         <v/>
       </c>
       <c r="AI35" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ35" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK35" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL35" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ35" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK35" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL35" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM35" s="33"/>
@@ -8157,7 +7219,7 @@
         <v>28</v>
       </c>
       <c r="AZ35" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA35" s="40"/>
@@ -8209,36 +7271,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC35" s="40"/>
-      <c r="CD35" s="38"/>
-      <c r="CE35" s="39"/>
-      <c r="CF35" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG35" s="40"/>
-      <c r="CH35" s="38"/>
-      <c r="CI35" s="39"/>
-      <c r="CJ35" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK35" s="40"/>
-      <c r="CL35" s="38"/>
-      <c r="CM35" s="39"/>
-      <c r="CN35" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO35" s="40"/>
-      <c r="CP35" s="38"/>
-      <c r="CQ35" s="39"/>
-      <c r="CR35" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="36" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A36" s="31">
         <v>29</v>
       </c>
@@ -8251,19 +7285,19 @@
         <v/>
       </c>
       <c r="G36" s="33" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H36" s="34" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I36" s="35" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J36" s="36" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K36" s="33"/>
@@ -8309,19 +7343,19 @@
         <v/>
       </c>
       <c r="AI36" s="33" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ36" s="34" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK36" s="35" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL36" s="35" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ36" s="34" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK36" s="35" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL36" s="35" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM36" s="33"/>
@@ -8349,7 +7383,7 @@
         <v>29</v>
       </c>
       <c r="AZ36" s="32" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA36" s="40"/>
@@ -8401,36 +7435,8 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC36" s="40"/>
-      <c r="CD36" s="38"/>
-      <c r="CE36" s="39"/>
-      <c r="CF36" s="39" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG36" s="40"/>
-      <c r="CH36" s="38"/>
-      <c r="CI36" s="39"/>
-      <c r="CJ36" s="41" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK36" s="40"/>
-      <c r="CL36" s="38"/>
-      <c r="CM36" s="39"/>
-      <c r="CN36" s="39" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO36" s="40"/>
-      <c r="CP36" s="38"/>
-      <c r="CQ36" s="39"/>
-      <c r="CR36" s="88" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="37" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A37" s="47">
         <v>30</v>
       </c>
@@ -8443,19 +7449,19 @@
         <v/>
       </c>
       <c r="G37" s="2" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="H37" s="3" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="I37" s="4" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="J37" s="5" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="K37" s="2"/>
@@ -8501,19 +7507,19 @@
         <v/>
       </c>
       <c r="AI37" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="AJ37" s="3" t="str">
+        <f t="shared" si="26"/>
+        <v/>
+      </c>
+      <c r="AK37" s="4" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="AL37" s="4" t="str">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="AJ37" s="3" t="str">
-        <f t="shared" si="30"/>
-        <v/>
-      </c>
-      <c r="AK37" s="4" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="AL37" s="4" t="str">
-        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="AM37" s="2"/>
@@ -8541,7 +7547,7 @@
         <v>30</v>
       </c>
       <c r="AZ37" s="48" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="BA37" s="13"/>
@@ -8593,962 +7599,806 @@
         <f t="shared" si="19"/>
         <v/>
       </c>
-      <c r="CC37" s="13"/>
-      <c r="CD37" s="11"/>
-      <c r="CE37" s="12"/>
-      <c r="CF37" s="12" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="CG37" s="13"/>
-      <c r="CH37" s="11"/>
-      <c r="CI37" s="12"/>
-      <c r="CJ37" s="14" t="str">
-        <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="CK37" s="13"/>
-      <c r="CL37" s="11"/>
-      <c r="CM37" s="12"/>
-      <c r="CN37" s="12" t="str">
-        <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="CO37" s="13"/>
-      <c r="CP37" s="11"/>
-      <c r="CQ37" s="12"/>
-      <c r="CR37" s="15" t="str">
-        <f t="shared" si="23"/>
-        <v/>
-      </c>
     </row>
-    <row r="38" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A38" s="75" t="s">
+    <row r="38" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A38" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B38" s="76"/>
+      <c r="B38" s="71"/>
       <c r="C38" s="33" t="str">
-        <f t="shared" ref="C38:AX38" si="33">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
+        <f t="shared" ref="C38:AX38" si="29">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
       </c>
       <c r="D38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="E38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="F38" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="G38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="H38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="I38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="J38" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="K38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="L38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="M38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="N38" s="37" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="O38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="P38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Q38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="R38" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="S38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="T38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="U38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="V38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="W38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="X38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Y38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="Z38" s="37" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AA38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AB38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AC38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AD38" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AE38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AF38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AG38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AH38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AI38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AJ38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AK38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AL38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AM38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AN38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AO38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AP38" s="37" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AQ38" s="33" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AR38" s="34" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AS38" s="35" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AT38" s="36" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AU38" s="23" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AV38" s="24" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AW38" s="25" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AX38" s="50" t="str">
+        <f t="shared" si="29"/>
+        <v/>
+      </c>
+      <c r="AY38" s="70" t="s">
+        <v>11</v>
+      </c>
+      <c r="AZ38" s="71"/>
+      <c r="BA38" s="33" t="str">
+        <f t="shared" ref="BA38:BL38" si="30">IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
+        <v/>
+      </c>
+      <c r="BB38" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BC38" s="35" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BD38" s="35" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BE38" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BF38" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BG38" s="35" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BH38" s="37" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BI38" s="33" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BJ38" s="34" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BK38" s="35" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BL38" s="36" t="str">
+        <f t="shared" si="30"/>
+        <v/>
+      </c>
+      <c r="BM38" s="33" t="str">
+        <f t="shared" ref="BM38:BT38" si="31">IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
+        <v/>
+      </c>
+      <c r="BN38" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BO38" s="35" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BP38" s="35" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BQ38" s="33" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BR38" s="34" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BS38" s="35" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BT38" s="37" t="str">
+        <f t="shared" si="31"/>
+        <v/>
+      </c>
+      <c r="BU38" s="33" t="str">
+        <f t="shared" ref="BU38:CB38" si="32">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV38" s="34" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BW38" s="35" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BX38" s="35" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BY38" s="33" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="BZ38" s="34" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="CA38" s="35" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+      <c r="CB38" s="36" t="str">
+        <f t="shared" si="32"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A39" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="63"/>
+      <c r="C39" s="33" t="str">
+        <f t="shared" ref="C39:AX39" si="33">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
+        <v/>
+      </c>
+      <c r="D39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="E38" s="35" t="str">
+      <c r="E39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="F38" s="36" t="str">
+      <c r="F39" s="36" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="G38" s="33" t="str">
+      <c r="G39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="H38" s="34" t="str">
+      <c r="H39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="I38" s="35" t="str">
+      <c r="I39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="J38" s="36" t="str">
+      <c r="J39" s="36" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="K38" s="33" t="str">
+      <c r="K39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="L38" s="34" t="str">
+      <c r="L39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="M38" s="35" t="str">
+      <c r="M39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="N38" s="37" t="str">
+      <c r="N39" s="37" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="O38" s="33" t="str">
+      <c r="O39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="P38" s="34" t="str">
+      <c r="P39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="Q38" s="35" t="str">
+      <c r="Q39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="R38" s="36" t="str">
+      <c r="R39" s="36" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="S38" s="33" t="str">
+      <c r="S39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="T38" s="34" t="str">
+      <c r="T39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="U38" s="35" t="str">
+      <c r="U39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="V38" s="35" t="str">
+      <c r="V39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="W38" s="33" t="str">
+      <c r="W39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="X38" s="34" t="str">
+      <c r="X39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="Y38" s="35" t="str">
+      <c r="Y39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="Z38" s="37" t="str">
+      <c r="Z39" s="37" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AA38" s="33" t="str">
+      <c r="AA39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AB38" s="34" t="str">
+      <c r="AB39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AC38" s="35" t="str">
+      <c r="AC39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AD38" s="36" t="str">
+      <c r="AD39" s="36" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AE38" s="33" t="str">
+      <c r="AE39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AF38" s="34" t="str">
+      <c r="AF39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AG38" s="35" t="str">
+      <c r="AG39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AH38" s="35" t="str">
+      <c r="AH39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AI38" s="33" t="str">
+      <c r="AI39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AJ38" s="34" t="str">
+      <c r="AJ39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AK38" s="35" t="str">
+      <c r="AK39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AL38" s="35" t="str">
+      <c r="AL39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AM38" s="33" t="str">
+      <c r="AM39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AN38" s="34" t="str">
+      <c r="AN39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AO38" s="35" t="str">
+      <c r="AO39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AP38" s="37" t="str">
+      <c r="AP39" s="37" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AQ38" s="33" t="str">
+      <c r="AQ39" s="33" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AR38" s="34" t="str">
+      <c r="AR39" s="34" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AS38" s="35" t="str">
+      <c r="AS39" s="35" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AT38" s="36" t="str">
+      <c r="AT39" s="36" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AU38" s="23" t="str">
+      <c r="AU39" s="23" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AV38" s="24" t="str">
+      <c r="AV39" s="24" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AW38" s="25" t="str">
+      <c r="AW39" s="25" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AX38" s="50" t="str">
+      <c r="AX39" s="50" t="str">
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AY38" s="75" t="s">
-        <v>11</v>
-      </c>
-      <c r="AZ38" s="76"/>
-      <c r="BA38" s="33" t="str">
-        <f t="shared" ref="BA38:BL38" si="34">IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
-        <v/>
-      </c>
-      <c r="BB38" s="34" t="str">
+      <c r="AY39" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="AZ39" s="63"/>
+      <c r="BA39" s="33" t="str">
+        <f t="shared" ref="BA39:BL39" si="34">IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
+        <v/>
+      </c>
+      <c r="BB39" s="34" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BC38" s="35" t="str">
+      <c r="BC39" s="35" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BD38" s="35" t="str">
+      <c r="BD39" s="35" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BE38" s="33" t="str">
+      <c r="BE39" s="33" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BF38" s="34" t="str">
+      <c r="BF39" s="34" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BG38" s="35" t="str">
+      <c r="BG39" s="35" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BH38" s="37" t="str">
+      <c r="BH39" s="37" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BI38" s="33" t="str">
+      <c r="BI39" s="33" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BJ38" s="34" t="str">
+      <c r="BJ39" s="34" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BK38" s="35" t="str">
+      <c r="BK39" s="35" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BL38" s="36" t="str">
+      <c r="BL39" s="36" t="str">
         <f t="shared" si="34"/>
         <v/>
       </c>
-      <c r="BM38" s="33" t="str">
-        <f t="shared" ref="BM38:BT38" si="35">IF(SUM(BM8:BM37)=0,"",AVERAGE(BM8:BM37))</f>
-        <v/>
-      </c>
-      <c r="BN38" s="34" t="str">
+      <c r="BM39" s="33" t="str">
+        <f t="shared" ref="BM39:BT39" si="35">IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
+        <v/>
+      </c>
+      <c r="BN39" s="34" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BO38" s="35" t="str">
+      <c r="BO39" s="35" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BP38" s="35" t="str">
+      <c r="BP39" s="35" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BQ38" s="33" t="str">
+      <c r="BQ39" s="33" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BR38" s="34" t="str">
+      <c r="BR39" s="34" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BS38" s="35" t="str">
+      <c r="BS39" s="35" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BT38" s="37" t="str">
+      <c r="BT39" s="37" t="str">
         <f t="shared" si="35"/>
         <v/>
       </c>
-      <c r="BU38" s="33" t="str">
-        <f t="shared" ref="BU38:CJ38" si="36">IF(SUM(BU8:BU37)=0,"",AVERAGE(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV38" s="34" t="str">
+      <c r="BU39" s="33" t="str">
+        <f t="shared" ref="BU39:CB39" si="36">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV39" s="34" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="BW38" s="35" t="str">
+      <c r="BW39" s="35" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="BX38" s="35" t="str">
+      <c r="BX39" s="35" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="BY38" s="33" t="str">
+      <c r="BY39" s="33" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="BZ38" s="34" t="str">
+      <c r="BZ39" s="34" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="CA38" s="35" t="str">
+      <c r="CA39" s="35" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="CB38" s="36" t="str">
+      <c r="CB39" s="36" t="str">
         <f t="shared" si="36"/>
         <v/>
       </c>
-      <c r="CC38" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CD38" s="34" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CE38" s="35" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CF38" s="35" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CG38" s="33" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CH38" s="34" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CI38" s="35" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CJ38" s="37" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="CK38" s="33" t="str">
-        <f t="shared" ref="CK38:CR38" si="37">IF(SUM(CK8:CK37)=0,"",AVERAGE(CK8:CK37))</f>
-        <v/>
-      </c>
-      <c r="CL38" s="34" t="str">
+    </row>
+    <row r="40" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A40" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="63"/>
+      <c r="C40" s="33" t="str">
+        <f t="shared" ref="C40:AX40" si="37">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
+        <v/>
+      </c>
+      <c r="D40" s="34" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CM38" s="35" t="str">
+      <c r="E40" s="35" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CN38" s="35" t="str">
+      <c r="F40" s="36" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CO38" s="40" t="str">
+      <c r="G40" s="33" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CP38" s="38" t="str">
+      <c r="H40" s="34" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CQ38" s="39" t="str">
+      <c r="I40" s="35" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="CR38" s="88" t="str">
+      <c r="J40" s="36" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-    </row>
-    <row r="39" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A39" s="77" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="78"/>
-      <c r="C39" s="33" t="str">
-        <f t="shared" ref="C39:AX39" si="38">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
-        <v/>
-      </c>
-      <c r="D39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="E39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="F39" s="36" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="G39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="H39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="I39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="J39" s="36" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="L39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="M39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="N39" s="37" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="O39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="P39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="Q39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="R39" s="36" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="S39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="T39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="U39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="V39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="W39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="X39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="Y39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="Z39" s="37" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AA39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AB39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AC39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AD39" s="36" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AE39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AF39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AG39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AH39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AI39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AJ39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AK39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AL39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AM39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AN39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AO39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AP39" s="37" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AQ39" s="33" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AR39" s="34" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AS39" s="35" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AT39" s="36" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AU39" s="23" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AV39" s="24" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AW39" s="25" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AX39" s="50" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="AY39" s="77" t="s">
-        <v>12</v>
-      </c>
-      <c r="AZ39" s="78"/>
-      <c r="BA39" s="33" t="str">
-        <f t="shared" ref="BA39:BL39" si="39">IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
-        <v/>
-      </c>
-      <c r="BB39" s="34" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BC39" s="35" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BD39" s="35" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BE39" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BF39" s="34" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BG39" s="35" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BH39" s="37" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BI39" s="33" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BJ39" s="34" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BK39" s="35" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BL39" s="36" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="BM39" s="33" t="str">
-        <f t="shared" ref="BM39:BT39" si="40">IF(SUM(BM8:BM37)=0,"",MEDIAN(BM8:BM37))</f>
-        <v/>
-      </c>
-      <c r="BN39" s="34" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BO39" s="35" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BP39" s="35" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BQ39" s="33" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BR39" s="34" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BS39" s="35" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BT39" s="37" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="BU39" s="33" t="str">
-        <f t="shared" ref="BU39:CJ39" si="41">IF(SUM(BU8:BU37)=0,"",MEDIAN(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV39" s="34" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="BW39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="BX39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="BY39" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="BZ39" s="34" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CA39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CB39" s="36" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CC39" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CD39" s="34" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CE39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CF39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CG39" s="33" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CH39" s="34" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CI39" s="35" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CJ39" s="37" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="CK39" s="33" t="str">
-        <f t="shared" ref="CK39:CR39" si="42">IF(SUM(CK8:CK37)=0,"",MEDIAN(CK8:CK37))</f>
-        <v/>
-      </c>
-      <c r="CL39" s="34" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CM39" s="35" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CN39" s="35" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CO39" s="40" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CP39" s="38" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CQ39" s="39" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="CR39" s="88" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-    </row>
-    <row r="40" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A40" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="78"/>
-      <c r="C40" s="33" t="str">
-        <f t="shared" ref="C40:AX40" si="43">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
-        <v/>
-      </c>
-      <c r="D40" s="34" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="E40" s="35" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="F40" s="36" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="G40" s="33" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="H40" s="34" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="I40" s="35" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
-      <c r="J40" s="36" t="str">
-        <f t="shared" si="43"/>
-        <v/>
-      </c>
       <c r="K40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="L40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="M40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="N40" s="37" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="O40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Q40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="R40" s="36" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="S40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="T40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="U40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="V40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="W40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="X40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Y40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="Z40" s="37" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AA40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AB40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AC40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AD40" s="36" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AE40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AF40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AG40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AH40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AI40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AJ40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AK40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AL40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AM40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AN40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AO40" s="35" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AP40" s="37" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AQ40" s="33" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AR40" s="34" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="AS40" s="35" t="str">
@@ -9556,963 +8406,771 @@
         <v/>
       </c>
       <c r="AT40" s="36" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AU40" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AV40" s="24" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AW40" s="25" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AX40" s="50" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="AY40" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="AZ40" s="63"/>
+      <c r="BA40" s="33" t="str">
+        <f t="shared" ref="BA40:BL40" si="38">IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
+        <v/>
+      </c>
+      <c r="BB40" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BC40" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BD40" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BE40" s="33" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BF40" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BG40" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BH40" s="37" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BI40" s="33" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BJ40" s="34" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BK40" s="35" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BL40" s="36" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="BM40" s="33" t="str">
+        <f t="shared" ref="BM40:BT40" si="39">IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
+        <v/>
+      </c>
+      <c r="BN40" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BO40" s="35" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BP40" s="35" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BQ40" s="33" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BR40" s="34" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BS40" s="35" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BT40" s="37" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="BU40" s="33" t="str">
+        <f t="shared" ref="BU40:CB40" si="40">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV40" s="34" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BW40" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BX40" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BY40" s="33" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="BZ40" s="34" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="CA40" s="35" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="CB40" s="36" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A41" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="63"/>
+      <c r="C41" s="33" t="str">
+        <f t="shared" ref="C41:AX41" si="41">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
+        <v/>
+      </c>
+      <c r="D41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="E41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="F41" s="36" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="G41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="H41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="I41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="J41" s="36" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="K41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="L41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="N41" s="37" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="O41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="P41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Q41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="R41" s="36" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="S41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="T41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="U41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="V41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="W41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="X41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Y41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="Z41" s="37" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AA41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AB41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AC41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AD41" s="36" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AE41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AF41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AG41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AH41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AI41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AJ41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AK41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AL41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AM41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AN41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AO41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AP41" s="37" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AQ41" s="33" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AR41" s="34" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AS41" s="35" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AT41" s="36" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AU41" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AV41" s="24" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AW41" s="25" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AX41" s="50" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="AY41" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ41" s="63"/>
+      <c r="BA41" s="33" t="str">
+        <f t="shared" ref="BA41:BL41" si="42">IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
+        <v/>
+      </c>
+      <c r="BB41" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BC41" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BD41" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BE41" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BF41" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BG41" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BH41" s="37" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BI41" s="33" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BJ41" s="34" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BK41" s="35" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BL41" s="36" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="BM41" s="33" t="str">
+        <f t="shared" ref="BM41:BT41" si="43">IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
+        <v/>
+      </c>
+      <c r="BN41" s="34" t="str">
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AU40" s="23" t="str">
+      <c r="BO41" s="35" t="str">
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AV40" s="24" t="str">
+      <c r="BP41" s="35" t="str">
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AW40" s="25" t="str">
+      <c r="BQ41" s="33" t="str">
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AX40" s="50" t="str">
+      <c r="BR41" s="34" t="str">
         <f t="shared" si="43"/>
         <v/>
       </c>
-      <c r="AY40" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="AZ40" s="78"/>
-      <c r="BA40" s="33" t="str">
-        <f t="shared" ref="BA40:BL40" si="44">IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
-        <v/>
-      </c>
-      <c r="BB40" s="34" t="str">
+      <c r="BS41" s="35" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="BT41" s="37" t="str">
+        <f t="shared" si="43"/>
+        <v/>
+      </c>
+      <c r="BU41" s="33" t="str">
+        <f t="shared" ref="BU41:CB41" si="44">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
+        <v/>
+      </c>
+      <c r="BV41" s="34" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BC40" s="35" t="str">
+      <c r="BW41" s="35" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BD40" s="35" t="str">
+      <c r="BX41" s="35" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BE40" s="33" t="str">
+      <c r="BY41" s="33" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BF40" s="34" t="str">
+      <c r="BZ41" s="34" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BG40" s="35" t="str">
+      <c r="CA41" s="35" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BH40" s="37" t="str">
+      <c r="CB41" s="36" t="str">
         <f t="shared" si="44"/>
         <v/>
       </c>
-      <c r="BI40" s="33" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="BJ40" s="34" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="BK40" s="35" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="BL40" s="36" t="str">
-        <f t="shared" si="44"/>
-        <v/>
-      </c>
-      <c r="BM40" s="33" t="str">
-        <f t="shared" ref="BM40:BT40" si="45">IF(SUM(BM8:BM37)=0,"",MAX(BM8:BM37))</f>
-        <v/>
-      </c>
-      <c r="BN40" s="34" t="str">
+    </row>
+    <row r="42" spans="1:80" x14ac:dyDescent="0.25">
+      <c r="A42" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" s="65"/>
+      <c r="C42" s="2" t="str">
+        <f t="shared" ref="C42:AX42" si="45">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
+        <v/>
+      </c>
+      <c r="D42" s="3" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BO40" s="35" t="str">
+      <c r="E42" s="4" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BP40" s="35" t="str">
+      <c r="F42" s="5" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BQ40" s="33" t="str">
+      <c r="G42" s="2" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BR40" s="34" t="str">
+      <c r="H42" s="3" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BS40" s="35" t="str">
+      <c r="I42" s="4" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BT40" s="37" t="str">
+      <c r="J42" s="5" t="str">
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="BU40" s="33" t="str">
-        <f t="shared" ref="BU40:CJ40" si="46">IF(SUM(BU8:BU37)=0,"",MAX(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV40" s="34" t="str">
+      <c r="K42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="L42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="M42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="N42" s="6" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="O42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="P42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Q42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="R42" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="S42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="T42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="U42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="V42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="W42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="X42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Y42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="Z42" s="6" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AA42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AB42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AC42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AD42" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AE42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AF42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AG42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AH42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AI42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AJ42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AK42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AL42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AM42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AN42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AO42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AP42" s="6" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AQ42" s="2" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AR42" s="3" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AS42" s="4" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AT42" s="5" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AU42" s="7" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AV42" s="8" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AW42" s="9" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AX42" s="10" t="str">
+        <f t="shared" si="45"/>
+        <v/>
+      </c>
+      <c r="AY42" s="64" t="s">
+        <v>15</v>
+      </c>
+      <c r="AZ42" s="65"/>
+      <c r="BA42" s="2" t="str">
+        <f t="shared" ref="BA42:BL42" si="46">IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
+        <v/>
+      </c>
+      <c r="BB42" s="3" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="BW40" s="35" t="str">
+      <c r="BC42" s="4" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="BX40" s="35" t="str">
+      <c r="BD42" s="4" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="BY40" s="33" t="str">
+      <c r="BE42" s="2" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="BZ40" s="34" t="str">
+      <c r="BF42" s="3" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CA40" s="35" t="str">
+      <c r="BG42" s="4" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CB40" s="36" t="str">
+      <c r="BH42" s="6" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CC40" s="33" t="str">
+      <c r="BI42" s="2" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CD40" s="34" t="str">
+      <c r="BJ42" s="3" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CE40" s="35" t="str">
+      <c r="BK42" s="4" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CF40" s="35" t="str">
+      <c r="BL42" s="5" t="str">
         <f t="shared" si="46"/>
         <v/>
       </c>
-      <c r="CG40" s="33" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CH40" s="34" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CI40" s="35" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CJ40" s="37" t="str">
-        <f t="shared" si="46"/>
-        <v/>
-      </c>
-      <c r="CK40" s="33" t="str">
-        <f t="shared" ref="CK40:CR40" si="47">IF(SUM(CK8:CK37)=0,"",MAX(CK8:CK37))</f>
-        <v/>
-      </c>
-      <c r="CL40" s="34" t="str">
+      <c r="BM42" s="2" t="str">
+        <f t="shared" ref="BM42:BT42" si="47">IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
+        <v/>
+      </c>
+      <c r="BN42" s="3" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CM40" s="35" t="str">
+      <c r="BO42" s="4" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CN40" s="35" t="str">
+      <c r="BP42" s="4" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CO40" s="40" t="str">
+      <c r="BQ42" s="2" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CP40" s="38" t="str">
+      <c r="BR42" s="3" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CQ40" s="39" t="str">
+      <c r="BS42" s="4" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
-      <c r="CR40" s="88" t="str">
+      <c r="BT42" s="6" t="str">
         <f t="shared" si="47"/>
         <v/>
       </c>
+      <c r="BU42" s="2" t="str">
+        <f t="shared" ref="BU42:CB42" si="48">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
+        <v/>
+      </c>
+      <c r="BV42" s="3" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="BW42" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="BX42" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="BY42" s="2" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="BZ42" s="3" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="CA42" s="4" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
+      <c r="CB42" s="5" t="str">
+        <f t="shared" si="48"/>
+        <v/>
+      </c>
     </row>
-    <row r="41" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A41" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="78"/>
-      <c r="C41" s="33" t="str">
-        <f t="shared" ref="C41:AX41" si="48">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
-        <v/>
-      </c>
-      <c r="D41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="E41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="F41" s="36" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="G41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="H41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="I41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="J41" s="36" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="K41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="L41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="M41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="N41" s="37" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="O41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="P41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Q41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="R41" s="36" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="S41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="T41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="U41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="V41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="W41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="X41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Y41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="Z41" s="37" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AA41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AB41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AC41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AD41" s="36" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AE41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AF41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AG41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AH41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AI41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AJ41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AK41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AL41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AM41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AN41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AO41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AP41" s="37" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AQ41" s="33" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AR41" s="34" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AS41" s="35" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AT41" s="36" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AU41" s="23" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AV41" s="24" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AW41" s="25" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AX41" s="50" t="str">
-        <f t="shared" si="48"/>
-        <v/>
-      </c>
-      <c r="AY41" s="77" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ41" s="78"/>
-      <c r="BA41" s="33" t="str">
-        <f t="shared" ref="BA41:BL41" si="49">IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
-        <v/>
-      </c>
-      <c r="BB41" s="34" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BC41" s="35" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BD41" s="35" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BE41" s="33" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BF41" s="34" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BG41" s="35" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BH41" s="37" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BI41" s="33" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BJ41" s="34" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BK41" s="35" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BL41" s="36" t="str">
-        <f t="shared" si="49"/>
-        <v/>
-      </c>
-      <c r="BM41" s="33" t="str">
-        <f t="shared" ref="BM41:BT41" si="50">IF(SUM(BM8:BM37)=0,"",MIN(BM8:BM37))</f>
-        <v/>
-      </c>
-      <c r="BN41" s="34" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BO41" s="35" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BP41" s="35" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BQ41" s="33" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BR41" s="34" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BS41" s="35" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BT41" s="37" t="str">
-        <f t="shared" si="50"/>
-        <v/>
-      </c>
-      <c r="BU41" s="33" t="str">
-        <f t="shared" ref="BU41:CJ41" si="51">IF(SUM(BU8:BU37)=0,"",MIN(BU8:BU37))</f>
-        <v/>
-      </c>
-      <c r="BV41" s="34" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="BW41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="BX41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="BY41" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="BZ41" s="34" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CA41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CB41" s="36" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CC41" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CD41" s="34" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CE41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CF41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CG41" s="33" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CH41" s="34" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CI41" s="35" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CJ41" s="37" t="str">
-        <f t="shared" si="51"/>
-        <v/>
-      </c>
-      <c r="CK41" s="33" t="str">
-        <f t="shared" ref="CK41:CR41" si="52">IF(SUM(CK8:CK37)=0,"",MIN(CK8:CK37))</f>
-        <v/>
-      </c>
-      <c r="CL41" s="34" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CM41" s="35" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CN41" s="35" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CO41" s="40" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CP41" s="38" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CQ41" s="39" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-      <c r="CR41" s="88" t="str">
-        <f t="shared" si="52"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="1:96" x14ac:dyDescent="0.3">
-      <c r="A42" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="70"/>
-      <c r="C42" s="2" t="str">
-        <f t="shared" ref="C42:AX42" si="53">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
-        <v/>
-      </c>
-      <c r="D42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="E42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="F42" s="5" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="G42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="H42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="I42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="J42" s="5" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="K42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="L42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="M42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="N42" s="6" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="O42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="P42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="Q42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="R42" s="5" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="S42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="T42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="U42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="V42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="W42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="X42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="Y42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="Z42" s="6" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AA42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AB42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AC42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AD42" s="5" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AE42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AF42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AG42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AH42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AI42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AJ42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AK42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AL42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AM42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AN42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AO42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AP42" s="6" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AQ42" s="2" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AR42" s="3" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AS42" s="4" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AT42" s="5" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AU42" s="7" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AV42" s="8" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AW42" s="9" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AX42" s="10" t="str">
-        <f t="shared" si="53"/>
-        <v/>
-      </c>
-      <c r="AY42" s="69" t="s">
-        <v>15</v>
-      </c>
-      <c r="AZ42" s="70"/>
-      <c r="BA42" s="2" t="str">
-        <f t="shared" ref="BA42:BL42" si="54">IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
-        <v/>
-      </c>
-      <c r="BB42" s="3" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BC42" s="4" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BD42" s="4" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BE42" s="2" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BF42" s="3" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BG42" s="4" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BH42" s="6" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BI42" s="2" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BJ42" s="3" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BK42" s="4" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BL42" s="5" t="str">
-        <f t="shared" si="54"/>
-        <v/>
-      </c>
-      <c r="BM42" s="2" t="str">
-        <f t="shared" ref="BM42:BT42" si="55">IF(BM38="","",COUNTIF(BM8:BM37,"&lt;51")/COUNT(BM8:BM37)*100)</f>
-        <v/>
-      </c>
-      <c r="BN42" s="3" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BO42" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BP42" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BQ42" s="2" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BR42" s="3" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BS42" s="4" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BT42" s="6" t="str">
-        <f t="shared" si="55"/>
-        <v/>
-      </c>
-      <c r="BU42" s="2" t="str">
-        <f t="shared" ref="BU42:CJ42" si="56">IF(BU38="","",COUNTIF(BU8:BU37,"&lt;51")/COUNT(BU8:BU37)*100)</f>
-        <v/>
-      </c>
-      <c r="BV42" s="3" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="BW42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="BX42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="BY42" s="2" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="BZ42" s="3" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CA42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CB42" s="5" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CC42" s="2" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CD42" s="3" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CE42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CF42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CG42" s="2" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CH42" s="3" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CI42" s="4" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CJ42" s="6" t="str">
-        <f t="shared" si="56"/>
-        <v/>
-      </c>
-      <c r="CK42" s="2" t="str">
-        <f t="shared" ref="CK42:CR42" si="57">IF(CK38="","",COUNTIF(CK8:CK37,"&lt;51")/COUNT(CK8:CK37)*100)</f>
-        <v/>
-      </c>
-      <c r="CL42" s="3" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CM42" s="4" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CN42" s="4" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CO42" s="13" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CP42" s="11" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CQ42" s="12" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-      <c r="CR42" s="15" t="str">
-        <f t="shared" si="57"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:96" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -10564,7 +9222,7 @@
       <c r="AW43" s="1"/>
       <c r="AX43" s="1"/>
     </row>
-    <row r="44" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -10616,7 +9274,7 @@
       <c r="AW44" s="1"/>
       <c r="AX44" s="1"/>
     </row>
-    <row r="45" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -10662,7 +9320,7 @@
       <c r="AW45" s="1"/>
       <c r="AX45" s="1"/>
     </row>
-    <row r="46" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -10684,7 +9342,7 @@
       <c r="AW46" s="1"/>
       <c r="AX46" s="1"/>
     </row>
-    <row r="47" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -10712,7 +9370,7 @@
       <c r="AW47" s="1"/>
       <c r="AX47" s="1"/>
     </row>
-    <row r="48" spans="1:96" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:80" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -10764,7 +9422,7 @@
       <c r="AW48" s="1"/>
       <c r="AX48" s="1"/>
     </row>
-    <row r="49" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -10816,200 +9474,181 @@
       <c r="AW49" s="1"/>
       <c r="AX49" s="1"/>
     </row>
-    <row r="50" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="51" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="B51" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="C51" s="55"/>
-      <c r="D51" s="55"/>
-      <c r="E51" s="55"/>
-      <c r="F51" s="55"/>
-      <c r="G51" s="55"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-      <c r="J51" s="53"/>
-      <c r="M51" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="N51" s="55"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="55"/>
-      <c r="Q51" s="55"/>
-      <c r="R51" s="55"/>
-      <c r="S51" s="55"/>
-      <c r="T51" s="55"/>
-      <c r="U51" s="55"/>
-      <c r="V51" s="55"/>
-      <c r="W51" s="55"/>
-      <c r="X51" s="55"/>
-      <c r="Y51" s="53"/>
-      <c r="Z51" s="53"/>
-      <c r="AD51" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE51" s="55"/>
-      <c r="AF51" s="55"/>
-      <c r="AG51" s="55"/>
-      <c r="AH51" s="55"/>
-      <c r="AI51" s="55"/>
-      <c r="AJ51" s="55"/>
-      <c r="AK51" s="55"/>
-      <c r="AL51" s="55"/>
-      <c r="AM51" s="55"/>
-      <c r="AN51" s="55"/>
-      <c r="AO51" s="55"/>
-      <c r="AP51" s="53"/>
-      <c r="AY51" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="AZ51" s="55"/>
-      <c r="BA51" s="55"/>
-      <c r="BB51" s="55"/>
-      <c r="BC51" s="55"/>
-      <c r="BD51" s="55"/>
-      <c r="BE51" s="55"/>
-      <c r="BF51" s="55"/>
-      <c r="BG51" s="55"/>
-      <c r="BH51" s="55"/>
-      <c r="BI51" s="52"/>
-      <c r="BJ51" s="53"/>
-      <c r="BK51" s="53"/>
-      <c r="BL51" s="53"/>
-      <c r="BM51" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="BN51" s="55"/>
-      <c r="BO51" s="55"/>
-      <c r="BP51" s="55"/>
-      <c r="BQ51" s="55"/>
-      <c r="BR51" s="55"/>
-      <c r="BS51" s="55"/>
-      <c r="BT51" s="55"/>
-      <c r="BU51" s="55"/>
-      <c r="BV51" s="55"/>
-      <c r="BW51" s="55"/>
-      <c r="BX51" s="55"/>
+    <row r="50" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="B51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="C51" s="80"/>
+      <c r="D51" s="80"/>
+      <c r="E51" s="80"/>
+      <c r="F51" s="80"/>
+      <c r="G51" s="80"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+      <c r="J51" s="52"/>
+      <c r="M51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="80"/>
+      <c r="O51" s="80"/>
+      <c r="P51" s="80"/>
+      <c r="Q51" s="80"/>
+      <c r="R51" s="80"/>
+      <c r="S51" s="80"/>
+      <c r="T51" s="80"/>
+      <c r="U51" s="80"/>
+      <c r="V51" s="80"/>
+      <c r="W51" s="80"/>
+      <c r="X51" s="80"/>
+      <c r="Y51" s="52"/>
+      <c r="Z51" s="52"/>
+      <c r="AD51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE51" s="80"/>
+      <c r="AF51" s="80"/>
+      <c r="AG51" s="80"/>
+      <c r="AH51" s="80"/>
+      <c r="AI51" s="80"/>
+      <c r="AJ51" s="80"/>
+      <c r="AK51" s="80"/>
+      <c r="AL51" s="80"/>
+      <c r="AM51" s="80"/>
+      <c r="AN51" s="80"/>
+      <c r="AO51" s="80"/>
+      <c r="AP51" s="52"/>
+      <c r="AY51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="AZ51" s="80"/>
+      <c r="BA51" s="82"/>
+      <c r="BB51" s="82"/>
+      <c r="BC51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="BD51" s="80"/>
+      <c r="BE51" s="80"/>
+      <c r="BF51" s="80"/>
+      <c r="BG51" s="80"/>
+      <c r="BH51" s="80"/>
+      <c r="BI51" s="80"/>
+      <c r="BJ51" s="80"/>
+      <c r="BK51" s="80"/>
+      <c r="BL51" s="80"/>
+      <c r="BM51" s="80"/>
+      <c r="BN51" s="80"/>
+      <c r="BO51" s="82"/>
+      <c r="BP51" s="80" t="s">
+        <v>22</v>
+      </c>
+      <c r="BQ51" s="80"/>
+      <c r="BR51" s="80"/>
+      <c r="BS51" s="80"/>
+      <c r="BT51" s="80"/>
+      <c r="BU51" s="80"/>
+      <c r="BV51" s="80"/>
+      <c r="BW51" s="80"/>
+      <c r="BX51" s="80"/>
+      <c r="BY51" s="80"/>
     </row>
-    <row r="52" spans="1:79" x14ac:dyDescent="0.3">
-      <c r="B52" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="C52" s="54"/>
-      <c r="D52" s="54"/>
-      <c r="E52" s="54"/>
-      <c r="F52" s="54"/>
-      <c r="G52" s="54"/>
-      <c r="H52" s="53"/>
-      <c r="I52" s="53"/>
-      <c r="J52" s="53"/>
-      <c r="M52" s="54" t="s">
-        <v>22</v>
-      </c>
-      <c r="N52" s="54"/>
-      <c r="O52" s="54"/>
-      <c r="P52" s="54"/>
-      <c r="Q52" s="54"/>
-      <c r="R52" s="54"/>
-      <c r="S52" s="54"/>
-      <c r="T52" s="54"/>
-      <c r="U52" s="54"/>
-      <c r="V52" s="54"/>
-      <c r="W52" s="54"/>
-      <c r="X52" s="54"/>
-      <c r="Y52" s="53"/>
-      <c r="Z52" s="53"/>
-      <c r="AD52" s="54" t="s">
+    <row r="52" spans="1:79" x14ac:dyDescent="0.25">
+      <c r="B52" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="52"/>
+      <c r="I52" s="52"/>
+      <c r="J52" s="52"/>
+      <c r="M52" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="AE52" s="54"/>
-      <c r="AF52" s="54"/>
-      <c r="AG52" s="54"/>
-      <c r="AH52" s="54"/>
-      <c r="AI52" s="54"/>
-      <c r="AJ52" s="54"/>
-      <c r="AK52" s="54"/>
-      <c r="AL52" s="54"/>
-      <c r="AM52" s="54"/>
-      <c r="AN52" s="54"/>
-      <c r="AO52" s="54"/>
-      <c r="AP52" s="53"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="81"/>
+      <c r="S52" s="81"/>
+      <c r="T52" s="81"/>
+      <c r="U52" s="81"/>
+      <c r="V52" s="81"/>
+      <c r="W52" s="81"/>
+      <c r="X52" s="81"/>
+      <c r="Y52" s="52"/>
+      <c r="Z52" s="52"/>
+      <c r="AD52" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="AE52" s="81"/>
+      <c r="AF52" s="81"/>
+      <c r="AG52" s="81"/>
+      <c r="AH52" s="81"/>
+      <c r="AI52" s="81"/>
+      <c r="AJ52" s="81"/>
+      <c r="AK52" s="81"/>
+      <c r="AL52" s="81"/>
+      <c r="AM52" s="81"/>
+      <c r="AN52" s="81"/>
+      <c r="AO52" s="81"/>
+      <c r="AP52" s="52"/>
       <c r="AW52" t="s">
+        <v>37</v>
+      </c>
+      <c r="AY52" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="AY52" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="AZ52" s="54"/>
-      <c r="BA52" s="54"/>
-      <c r="BB52" s="54"/>
-      <c r="BC52" s="54"/>
-      <c r="BD52" s="54"/>
-      <c r="BE52" s="54"/>
-      <c r="BF52" s="54"/>
-      <c r="BG52" s="54"/>
-      <c r="BH52" s="54"/>
-      <c r="BI52" s="53"/>
-      <c r="BJ52" s="53"/>
-      <c r="BK52" s="53"/>
-      <c r="BL52" s="53"/>
-      <c r="BM52" s="54" t="s">
+      <c r="AZ52" s="81"/>
+      <c r="BA52" s="52"/>
+      <c r="BB52" s="52"/>
+      <c r="BC52" s="81" t="s">
         <v>23</v>
       </c>
-      <c r="BN52" s="54"/>
-      <c r="BO52" s="54"/>
-      <c r="BP52" s="54"/>
-      <c r="BQ52" s="54"/>
-      <c r="BR52" s="54"/>
-      <c r="BS52" s="54"/>
-      <c r="BT52" s="54"/>
-      <c r="BU52" s="54"/>
-      <c r="BV52" s="54"/>
-      <c r="BW52" s="54"/>
-      <c r="BX52" s="54"/>
+      <c r="BD52" s="81"/>
+      <c r="BE52" s="81"/>
+      <c r="BF52" s="81"/>
+      <c r="BG52" s="81"/>
+      <c r="BH52" s="81"/>
+      <c r="BI52" s="81"/>
+      <c r="BJ52" s="81"/>
+      <c r="BK52" s="81"/>
+      <c r="BL52" s="81"/>
+      <c r="BM52" s="81"/>
+      <c r="BN52" s="81"/>
+      <c r="BO52" s="52"/>
+      <c r="BP52" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="BQ52" s="81"/>
+      <c r="BR52" s="81"/>
+      <c r="BS52" s="81"/>
+      <c r="BT52" s="81"/>
+      <c r="BU52" s="81"/>
+      <c r="BV52" s="81"/>
+      <c r="BW52" s="81"/>
+      <c r="BX52" s="81"/>
+      <c r="BY52" s="81"/>
       <c r="CA52" s="51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="CC6:CF6"/>
-    <mergeCell ref="CG6:CJ6"/>
-    <mergeCell ref="CK6:CN6"/>
-    <mergeCell ref="CO6:CR6"/>
-    <mergeCell ref="AY2:CR2"/>
-    <mergeCell ref="AY3:CR3"/>
-    <mergeCell ref="AY4:CR4"/>
-    <mergeCell ref="AY5:CR5"/>
-    <mergeCell ref="BU6:BX6"/>
-    <mergeCell ref="BY6:CB6"/>
-    <mergeCell ref="BA6:BD6"/>
-    <mergeCell ref="BE6:BH6"/>
-    <mergeCell ref="BI6:BL6"/>
-    <mergeCell ref="BM6:BP6"/>
-    <mergeCell ref="BQ6:BT6"/>
-    <mergeCell ref="AY41:AZ41"/>
-    <mergeCell ref="AY42:AZ42"/>
-    <mergeCell ref="AY6:AY7"/>
-    <mergeCell ref="AZ6:AZ7"/>
-    <mergeCell ref="AY38:AZ38"/>
-    <mergeCell ref="AY39:AZ39"/>
-    <mergeCell ref="AY40:AZ40"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="BM51:BX51"/>
+  <mergeCells count="53">
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="M52:X52"/>
+    <mergeCell ref="AD52:AO52"/>
+    <mergeCell ref="AY51:AZ51"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="M51:X51"/>
+    <mergeCell ref="AD51:AO51"/>
     <mergeCell ref="AY52:AZ52"/>
-    <mergeCell ref="BA52:BH52"/>
-    <mergeCell ref="BM52:BX52"/>
+    <mergeCell ref="BP51:BY51"/>
+    <mergeCell ref="BP52:BY52"/>
+    <mergeCell ref="BC51:BN51"/>
+    <mergeCell ref="BC52:BN52"/>
     <mergeCell ref="A2:AX2"/>
     <mergeCell ref="A3:AX3"/>
     <mergeCell ref="A4:AX4"/>
@@ -11022,52 +9661,55 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="W6:Z6"/>
     <mergeCell ref="AI6:AL6"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="M52:X52"/>
-    <mergeCell ref="AD52:AO52"/>
-    <mergeCell ref="AY51:AZ51"/>
-    <mergeCell ref="BA51:BH51"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="M51:X51"/>
-    <mergeCell ref="AD51:AO51"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="AY41:AZ41"/>
+    <mergeCell ref="AY42:AZ42"/>
+    <mergeCell ref="AY6:AY7"/>
+    <mergeCell ref="AZ6:AZ7"/>
+    <mergeCell ref="AY38:AZ38"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="AY40:AZ40"/>
+    <mergeCell ref="BU6:BX6"/>
+    <mergeCell ref="BY6:CB6"/>
+    <mergeCell ref="AY2:CB2"/>
+    <mergeCell ref="AY3:CB3"/>
+    <mergeCell ref="AY4:CB4"/>
+    <mergeCell ref="AY5:CB5"/>
+    <mergeCell ref="BA6:BD6"/>
+    <mergeCell ref="BE6:BH6"/>
+    <mergeCell ref="BI6:BL6"/>
+    <mergeCell ref="BM6:BP6"/>
+    <mergeCell ref="BQ6:BT6"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:AX37 BA8:BL37">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="between">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BM8:BT37">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="between">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BU8:BX37">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="between">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>1</formula>
       <formula>50</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BY8:CB37">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CC8:CJ37">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CK8:CN37">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
-      <formula>1</formula>
-      <formula>50</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="CO8:CR37">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="between">
       <formula>1</formula>
       <formula>50</formula>

--- a/public/templates/cs12.xlsx
+++ b/public/templates/cs12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\saat\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61D4B03-37B6-45E0-B6B2-EFD7370260E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2076CD78-7637-44C6-B67F-A9F22D9FAD18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Central" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="40">
   <si>
     <t>Nº</t>
   </si>
@@ -69,9 +69,6 @@
     <t>(CONSEJEROS Y DIRECCIONES TÉCNICAS)</t>
   </si>
   <si>
-    <t>Grammar</t>
-  </si>
-  <si>
     <t>PROMEDIOS MATERIAS</t>
   </si>
   <si>
@@ -88,9 +85,6 @@
   </si>
   <si>
     <t>Lenguaje</t>
-  </si>
-  <si>
-    <t>Literature</t>
   </si>
   <si>
     <t>P. Inglés</t>
@@ -138,12 +132,6 @@
     <t>PF</t>
   </si>
   <si>
-    <t>Física</t>
-  </si>
-  <si>
-    <t>Química</t>
-  </si>
-  <si>
     <t>CENTRALIZADOR DE NOTAS</t>
   </si>
   <si>
@@ -154,6 +142,21 @@
   </si>
   <si>
     <t>1 de 2</t>
+  </si>
+  <si>
+    <t>Literature [50%]</t>
+  </si>
+  <si>
+    <t>Grammar [50%]</t>
+  </si>
+  <si>
+    <t>Física [10%]</t>
+  </si>
+  <si>
+    <t>C. Naturales [80%]</t>
+  </si>
+  <si>
+    <t>Química [10%]</t>
   </si>
 </sst>
 </file>
@@ -1271,7 +1274,23 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1283,26 +1302,23 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1328,37 +1344,24 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="62" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="71">
     <cellStyle name="20% - Accent1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1572,7 +1575,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>51</xdr:col>
-      <xdr:colOff>912301</xdr:colOff>
+      <xdr:colOff>756437</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
@@ -1967,717 +1970,717 @@
     <col min="1" max="1" width="3.140625" customWidth="1"/>
     <col min="2" max="2" width="35" customWidth="1"/>
     <col min="3" max="50" width="3.85546875" customWidth="1"/>
-    <col min="51" max="51" width="3" customWidth="1"/>
-    <col min="52" max="52" width="35" customWidth="1"/>
+    <col min="51" max="51" width="5.140625" customWidth="1"/>
+    <col min="52" max="52" width="42.28515625" customWidth="1"/>
     <col min="53" max="64" width="5" customWidth="1"/>
     <col min="65" max="80" width="4.5703125" customWidth="1"/>
     <col min="81" max="82" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58"/>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AH2" s="58"/>
-      <c r="AI2" s="58"/>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="58"/>
-      <c r="AL2" s="58"/>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AO2" s="58"/>
-      <c r="AP2" s="58"/>
-      <c r="AQ2" s="58"/>
-      <c r="AR2" s="58"/>
-      <c r="AS2" s="58"/>
-      <c r="AT2" s="58"/>
-      <c r="AU2" s="58"/>
-      <c r="AV2" s="58"/>
-      <c r="AW2" s="58"/>
-      <c r="AX2" s="58"/>
-      <c r="AY2" s="58" t="str">
+      <c r="A2" s="56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="56"/>
+      <c r="M2" s="56"/>
+      <c r="N2" s="56"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="56"/>
+      <c r="Q2" s="56"/>
+      <c r="R2" s="56"/>
+      <c r="S2" s="56"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="56"/>
+      <c r="V2" s="56"/>
+      <c r="W2" s="56"/>
+      <c r="X2" s="56"/>
+      <c r="Y2" s="56"/>
+      <c r="Z2" s="56"/>
+      <c r="AA2" s="56"/>
+      <c r="AB2" s="56"/>
+      <c r="AC2" s="56"/>
+      <c r="AD2" s="56"/>
+      <c r="AE2" s="56"/>
+      <c r="AF2" s="56"/>
+      <c r="AG2" s="56"/>
+      <c r="AH2" s="56"/>
+      <c r="AI2" s="56"/>
+      <c r="AJ2" s="56"/>
+      <c r="AK2" s="56"/>
+      <c r="AL2" s="56"/>
+      <c r="AM2" s="56"/>
+      <c r="AN2" s="56"/>
+      <c r="AO2" s="56"/>
+      <c r="AP2" s="56"/>
+      <c r="AQ2" s="56"/>
+      <c r="AR2" s="56"/>
+      <c r="AS2" s="56"/>
+      <c r="AT2" s="56"/>
+      <c r="AU2" s="56"/>
+      <c r="AV2" s="56"/>
+      <c r="AW2" s="56"/>
+      <c r="AX2" s="56"/>
+      <c r="AY2" s="56" t="str">
         <f>A2</f>
         <v>CENTRALIZADOR DE NOTAS</v>
       </c>
-      <c r="AZ2" s="58"/>
-      <c r="BA2" s="58"/>
-      <c r="BB2" s="58"/>
-      <c r="BC2" s="58"/>
-      <c r="BD2" s="58"/>
-      <c r="BE2" s="58"/>
-      <c r="BF2" s="58"/>
-      <c r="BG2" s="58"/>
-      <c r="BH2" s="58"/>
-      <c r="BI2" s="58"/>
-      <c r="BJ2" s="58"/>
-      <c r="BK2" s="58"/>
-      <c r="BL2" s="58"/>
-      <c r="BM2" s="58"/>
-      <c r="BN2" s="58"/>
-      <c r="BO2" s="58"/>
-      <c r="BP2" s="58"/>
-      <c r="BQ2" s="58"/>
-      <c r="BR2" s="58"/>
-      <c r="BS2" s="58"/>
-      <c r="BT2" s="58"/>
-      <c r="BU2" s="58"/>
-      <c r="BV2" s="58"/>
-      <c r="BW2" s="58"/>
-      <c r="BX2" s="58"/>
-      <c r="BY2" s="58"/>
-      <c r="BZ2" s="58"/>
-      <c r="CA2" s="58"/>
-      <c r="CB2" s="58"/>
+      <c r="AZ2" s="56"/>
+      <c r="BA2" s="56"/>
+      <c r="BB2" s="56"/>
+      <c r="BC2" s="56"/>
+      <c r="BD2" s="56"/>
+      <c r="BE2" s="56"/>
+      <c r="BF2" s="56"/>
+      <c r="BG2" s="56"/>
+      <c r="BH2" s="56"/>
+      <c r="BI2" s="56"/>
+      <c r="BJ2" s="56"/>
+      <c r="BK2" s="56"/>
+      <c r="BL2" s="56"/>
+      <c r="BM2" s="56"/>
+      <c r="BN2" s="56"/>
+      <c r="BO2" s="56"/>
+      <c r="BP2" s="56"/>
+      <c r="BQ2" s="56"/>
+      <c r="BR2" s="56"/>
+      <c r="BS2" s="56"/>
+      <c r="BT2" s="56"/>
+      <c r="BU2" s="56"/>
+      <c r="BV2" s="56"/>
+      <c r="BW2" s="56"/>
+      <c r="BX2" s="56"/>
+      <c r="BY2" s="56"/>
+      <c r="BZ2" s="56"/>
+      <c r="CA2" s="56"/>
+      <c r="CB2" s="56"/>
     </row>
     <row r="3" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
-      <c r="P3" s="72"/>
-      <c r="Q3" s="72"/>
-      <c r="R3" s="72"/>
-      <c r="S3" s="72"/>
-      <c r="T3" s="72"/>
-      <c r="U3" s="72"/>
-      <c r="V3" s="72"/>
-      <c r="W3" s="72"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="72"/>
-      <c r="Z3" s="72"/>
-      <c r="AA3" s="72"/>
-      <c r="AB3" s="72"/>
-      <c r="AC3" s="72"/>
-      <c r="AD3" s="72"/>
-      <c r="AE3" s="72"/>
-      <c r="AF3" s="72"/>
-      <c r="AG3" s="72"/>
-      <c r="AH3" s="72"/>
-      <c r="AI3" s="72"/>
-      <c r="AJ3" s="72"/>
-      <c r="AK3" s="72"/>
-      <c r="AL3" s="72"/>
-      <c r="AM3" s="72"/>
-      <c r="AN3" s="72"/>
-      <c r="AO3" s="72"/>
-      <c r="AP3" s="72"/>
-      <c r="AQ3" s="72"/>
-      <c r="AR3" s="72"/>
-      <c r="AS3" s="72"/>
-      <c r="AT3" s="72"/>
-      <c r="AU3" s="72"/>
-      <c r="AV3" s="72"/>
-      <c r="AW3" s="72"/>
-      <c r="AX3" s="72"/>
-      <c r="AY3" s="58" t="str">
+      <c r="B3" s="57"/>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="57"/>
+      <c r="L3" s="57"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
+      <c r="O3" s="57"/>
+      <c r="P3" s="57"/>
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="57"/>
+      <c r="T3" s="57"/>
+      <c r="U3" s="57"/>
+      <c r="V3" s="57"/>
+      <c r="W3" s="57"/>
+      <c r="X3" s="57"/>
+      <c r="Y3" s="57"/>
+      <c r="Z3" s="57"/>
+      <c r="AA3" s="57"/>
+      <c r="AB3" s="57"/>
+      <c r="AC3" s="57"/>
+      <c r="AD3" s="57"/>
+      <c r="AE3" s="57"/>
+      <c r="AF3" s="57"/>
+      <c r="AG3" s="57"/>
+      <c r="AH3" s="57"/>
+      <c r="AI3" s="57"/>
+      <c r="AJ3" s="57"/>
+      <c r="AK3" s="57"/>
+      <c r="AL3" s="57"/>
+      <c r="AM3" s="57"/>
+      <c r="AN3" s="57"/>
+      <c r="AO3" s="57"/>
+      <c r="AP3" s="57"/>
+      <c r="AQ3" s="57"/>
+      <c r="AR3" s="57"/>
+      <c r="AS3" s="57"/>
+      <c r="AT3" s="57"/>
+      <c r="AU3" s="57"/>
+      <c r="AV3" s="57"/>
+      <c r="AW3" s="57"/>
+      <c r="AX3" s="57"/>
+      <c r="AY3" s="56" t="str">
         <f t="shared" ref="AY3:AY4" si="0">A3</f>
         <v>(CONSEJEROS Y DIRECCIONES TÉCNICAS)</v>
       </c>
-      <c r="AZ3" s="58"/>
-      <c r="BA3" s="58"/>
-      <c r="BB3" s="58"/>
-      <c r="BC3" s="58"/>
-      <c r="BD3" s="58"/>
-      <c r="BE3" s="58"/>
-      <c r="BF3" s="58"/>
-      <c r="BG3" s="58"/>
-      <c r="BH3" s="58"/>
-      <c r="BI3" s="58"/>
-      <c r="BJ3" s="58"/>
-      <c r="BK3" s="58"/>
-      <c r="BL3" s="58"/>
-      <c r="BM3" s="58"/>
-      <c r="BN3" s="58"/>
-      <c r="BO3" s="58"/>
-      <c r="BP3" s="58"/>
-      <c r="BQ3" s="58"/>
-      <c r="BR3" s="58"/>
-      <c r="BS3" s="58"/>
-      <c r="BT3" s="58"/>
-      <c r="BU3" s="58"/>
-      <c r="BV3" s="58"/>
-      <c r="BW3" s="58"/>
-      <c r="BX3" s="58"/>
-      <c r="BY3" s="58"/>
-      <c r="BZ3" s="58"/>
-      <c r="CA3" s="58"/>
-      <c r="CB3" s="58"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="56"/>
+      <c r="BD3" s="56"/>
+      <c r="BE3" s="56"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="56"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="56"/>
+      <c r="BL3" s="56"/>
+      <c r="BM3" s="56"/>
+      <c r="BN3" s="56"/>
+      <c r="BO3" s="56"/>
+      <c r="BP3" s="56"/>
+      <c r="BQ3" s="56"/>
+      <c r="BR3" s="56"/>
+      <c r="BS3" s="56"/>
+      <c r="BT3" s="56"/>
+      <c r="BU3" s="56"/>
+      <c r="BV3" s="56"/>
+      <c r="BW3" s="56"/>
+      <c r="BX3" s="56"/>
+      <c r="BY3" s="56"/>
+      <c r="BZ3" s="56"/>
+      <c r="CA3" s="56"/>
+      <c r="CB3" s="56"/>
     </row>
     <row r="4" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A4" s="73"/>
-      <c r="B4" s="73"/>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="73"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="73"/>
-      <c r="M4" s="73"/>
-      <c r="N4" s="73"/>
-      <c r="O4" s="73"/>
-      <c r="P4" s="73"/>
-      <c r="Q4" s="73"/>
-      <c r="R4" s="73"/>
-      <c r="S4" s="73"/>
-      <c r="T4" s="73"/>
-      <c r="U4" s="73"/>
-      <c r="V4" s="73"/>
-      <c r="W4" s="73"/>
-      <c r="X4" s="73"/>
-      <c r="Y4" s="73"/>
-      <c r="Z4" s="73"/>
-      <c r="AA4" s="73"/>
-      <c r="AB4" s="73"/>
-      <c r="AC4" s="73"/>
-      <c r="AD4" s="73"/>
-      <c r="AE4" s="73"/>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
-      <c r="AH4" s="73"/>
-      <c r="AI4" s="73"/>
-      <c r="AJ4" s="73"/>
-      <c r="AK4" s="73"/>
-      <c r="AL4" s="73"/>
-      <c r="AM4" s="73"/>
-      <c r="AN4" s="73"/>
-      <c r="AO4" s="73"/>
-      <c r="AP4" s="73"/>
-      <c r="AQ4" s="73"/>
-      <c r="AR4" s="73"/>
-      <c r="AS4" s="73"/>
-      <c r="AT4" s="73"/>
-      <c r="AU4" s="73"/>
-      <c r="AV4" s="73"/>
-      <c r="AW4" s="73"/>
-      <c r="AX4" s="73"/>
-      <c r="AY4" s="58">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="58"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
+      <c r="V4" s="58"/>
+      <c r="W4" s="58"/>
+      <c r="X4" s="58"/>
+      <c r="Y4" s="58"/>
+      <c r="Z4" s="58"/>
+      <c r="AA4" s="58"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58"/>
+      <c r="AE4" s="58"/>
+      <c r="AF4" s="58"/>
+      <c r="AG4" s="58"/>
+      <c r="AH4" s="58"/>
+      <c r="AI4" s="58"/>
+      <c r="AJ4" s="58"/>
+      <c r="AK4" s="58"/>
+      <c r="AL4" s="58"/>
+      <c r="AM4" s="58"/>
+      <c r="AN4" s="58"/>
+      <c r="AO4" s="58"/>
+      <c r="AP4" s="58"/>
+      <c r="AQ4" s="58"/>
+      <c r="AR4" s="58"/>
+      <c r="AS4" s="58"/>
+      <c r="AT4" s="58"/>
+      <c r="AU4" s="58"/>
+      <c r="AV4" s="58"/>
+      <c r="AW4" s="58"/>
+      <c r="AX4" s="58"/>
+      <c r="AY4" s="56">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AZ4" s="58"/>
-      <c r="BA4" s="58"/>
-      <c r="BB4" s="58"/>
-      <c r="BC4" s="58"/>
-      <c r="BD4" s="58"/>
-      <c r="BE4" s="58"/>
-      <c r="BF4" s="58"/>
-      <c r="BG4" s="58"/>
-      <c r="BH4" s="58"/>
-      <c r="BI4" s="58"/>
-      <c r="BJ4" s="58"/>
-      <c r="BK4" s="58"/>
-      <c r="BL4" s="58"/>
-      <c r="BM4" s="58"/>
-      <c r="BN4" s="58"/>
-      <c r="BO4" s="58"/>
-      <c r="BP4" s="58"/>
-      <c r="BQ4" s="58"/>
-      <c r="BR4" s="58"/>
-      <c r="BS4" s="58"/>
-      <c r="BT4" s="58"/>
-      <c r="BU4" s="58"/>
-      <c r="BV4" s="58"/>
-      <c r="BW4" s="58"/>
-      <c r="BX4" s="58"/>
-      <c r="BY4" s="58"/>
-      <c r="BZ4" s="58"/>
-      <c r="CA4" s="58"/>
-      <c r="CB4" s="58"/>
+      <c r="AZ4" s="56"/>
+      <c r="BA4" s="56"/>
+      <c r="BB4" s="56"/>
+      <c r="BC4" s="56"/>
+      <c r="BD4" s="56"/>
+      <c r="BE4" s="56"/>
+      <c r="BF4" s="56"/>
+      <c r="BG4" s="56"/>
+      <c r="BH4" s="56"/>
+      <c r="BI4" s="56"/>
+      <c r="BJ4" s="56"/>
+      <c r="BK4" s="56"/>
+      <c r="BL4" s="56"/>
+      <c r="BM4" s="56"/>
+      <c r="BN4" s="56"/>
+      <c r="BO4" s="56"/>
+      <c r="BP4" s="56"/>
+      <c r="BQ4" s="56"/>
+      <c r="BR4" s="56"/>
+      <c r="BS4" s="56"/>
+      <c r="BT4" s="56"/>
+      <c r="BU4" s="56"/>
+      <c r="BV4" s="56"/>
+      <c r="BW4" s="56"/>
+      <c r="BX4" s="56"/>
+      <c r="BY4" s="56"/>
+      <c r="BZ4" s="56"/>
+      <c r="CA4" s="56"/>
+      <c r="CB4" s="56"/>
     </row>
     <row r="5" spans="1:80" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="74"/>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="74"/>
-      <c r="U5" s="74"/>
-      <c r="V5" s="74"/>
-      <c r="W5" s="74"/>
-      <c r="X5" s="74"/>
-      <c r="Y5" s="74"/>
-      <c r="Z5" s="74"/>
-      <c r="AA5" s="74"/>
-      <c r="AB5" s="74"/>
-      <c r="AC5" s="74"/>
-      <c r="AD5" s="74"/>
-      <c r="AE5" s="74"/>
-      <c r="AF5" s="74"/>
-      <c r="AG5" s="74"/>
-      <c r="AH5" s="74"/>
-      <c r="AI5" s="74"/>
-      <c r="AJ5" s="74"/>
-      <c r="AK5" s="74"/>
-      <c r="AL5" s="74"/>
-      <c r="AM5" s="74"/>
-      <c r="AN5" s="74"/>
-      <c r="AO5" s="74"/>
-      <c r="AP5" s="74"/>
-      <c r="AQ5" s="74"/>
-      <c r="AR5" s="74"/>
-      <c r="AS5" s="74"/>
-      <c r="AT5" s="74"/>
-      <c r="AU5" s="74"/>
-      <c r="AV5" s="74"/>
-      <c r="AW5" s="74"/>
-      <c r="AX5" s="74"/>
-      <c r="AY5" s="59">
+      <c r="A5" s="59"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="59"/>
+      <c r="K5" s="59"/>
+      <c r="L5" s="59"/>
+      <c r="M5" s="59"/>
+      <c r="N5" s="59"/>
+      <c r="O5" s="59"/>
+      <c r="P5" s="59"/>
+      <c r="Q5" s="59"/>
+      <c r="R5" s="59"/>
+      <c r="S5" s="59"/>
+      <c r="T5" s="59"/>
+      <c r="U5" s="59"/>
+      <c r="V5" s="59"/>
+      <c r="W5" s="59"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="59"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="59"/>
+      <c r="AE5" s="59"/>
+      <c r="AF5" s="59"/>
+      <c r="AG5" s="59"/>
+      <c r="AH5" s="59"/>
+      <c r="AI5" s="59"/>
+      <c r="AJ5" s="59"/>
+      <c r="AK5" s="59"/>
+      <c r="AL5" s="59"/>
+      <c r="AM5" s="59"/>
+      <c r="AN5" s="59"/>
+      <c r="AO5" s="59"/>
+      <c r="AP5" s="59"/>
+      <c r="AQ5" s="59"/>
+      <c r="AR5" s="59"/>
+      <c r="AS5" s="59"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="59"/>
+      <c r="AW5" s="59"/>
+      <c r="AX5" s="59"/>
+      <c r="AY5" s="80">
         <f>A5</f>
         <v>0</v>
       </c>
-      <c r="AZ5" s="59"/>
-      <c r="BA5" s="59"/>
-      <c r="BB5" s="59"/>
-      <c r="BC5" s="59"/>
-      <c r="BD5" s="59"/>
-      <c r="BE5" s="59"/>
-      <c r="BF5" s="59"/>
-      <c r="BG5" s="59"/>
-      <c r="BH5" s="59"/>
-      <c r="BI5" s="59"/>
-      <c r="BJ5" s="59"/>
-      <c r="BK5" s="59"/>
-      <c r="BL5" s="59"/>
-      <c r="BM5" s="59"/>
-      <c r="BN5" s="59"/>
-      <c r="BO5" s="59"/>
-      <c r="BP5" s="59"/>
-      <c r="BQ5" s="59"/>
-      <c r="BR5" s="59"/>
-      <c r="BS5" s="59"/>
-      <c r="BT5" s="59"/>
-      <c r="BU5" s="59"/>
-      <c r="BV5" s="59"/>
-      <c r="BW5" s="59"/>
-      <c r="BX5" s="59"/>
-      <c r="BY5" s="59"/>
-      <c r="BZ5" s="59"/>
-      <c r="CA5" s="59"/>
-      <c r="CB5" s="59"/>
+      <c r="AZ5" s="80"/>
+      <c r="BA5" s="80"/>
+      <c r="BB5" s="80"/>
+      <c r="BC5" s="80"/>
+      <c r="BD5" s="80"/>
+      <c r="BE5" s="80"/>
+      <c r="BF5" s="80"/>
+      <c r="BG5" s="80"/>
+      <c r="BH5" s="80"/>
+      <c r="BI5" s="80"/>
+      <c r="BJ5" s="80"/>
+      <c r="BK5" s="80"/>
+      <c r="BL5" s="80"/>
+      <c r="BM5" s="80"/>
+      <c r="BN5" s="80"/>
+      <c r="BO5" s="80"/>
+      <c r="BP5" s="80"/>
+      <c r="BQ5" s="80"/>
+      <c r="BR5" s="80"/>
+      <c r="BS5" s="80"/>
+      <c r="BT5" s="80"/>
+      <c r="BU5" s="80"/>
+      <c r="BV5" s="80"/>
+      <c r="BW5" s="80"/>
+      <c r="BX5" s="80"/>
+      <c r="BY5" s="80"/>
+      <c r="BZ5" s="80"/>
+      <c r="CA5" s="80"/>
+      <c r="CB5" s="80"/>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="68" t="s">
+      <c r="B6" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="54" t="s">
+      <c r="C6" s="60" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="61"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="56"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="54" t="s">
+      <c r="H6" s="61"/>
+      <c r="I6" s="62"/>
+      <c r="J6" s="64"/>
+      <c r="K6" s="60" t="s">
+        <v>2</v>
+      </c>
+      <c r="L6" s="61"/>
+      <c r="M6" s="62"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="60" t="s">
+        <v>3</v>
+      </c>
+      <c r="P6" s="61"/>
+      <c r="Q6" s="62"/>
+      <c r="R6" s="64"/>
+      <c r="S6" s="60" t="s">
+        <v>4</v>
+      </c>
+      <c r="T6" s="61"/>
+      <c r="U6" s="62"/>
+      <c r="V6" s="62"/>
+      <c r="W6" s="60" t="s">
+        <v>17</v>
+      </c>
+      <c r="X6" s="61"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="60" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="62"/>
+      <c r="AD6" s="64"/>
+      <c r="AE6" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="55"/>
-      <c r="I6" s="56"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
-      <c r="N6" s="75"/>
-      <c r="O6" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="56"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="T6" s="55"/>
-      <c r="U6" s="56"/>
-      <c r="V6" s="56"/>
-      <c r="W6" s="54" t="s">
+      <c r="AF6" s="61"/>
+      <c r="AG6" s="62"/>
+      <c r="AH6" s="62"/>
+      <c r="AI6" s="60" t="s">
+        <v>6</v>
+      </c>
+      <c r="AJ6" s="61"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="62"/>
+      <c r="AM6" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="56"/>
-      <c r="Z6" s="75"/>
-      <c r="AA6" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB6" s="55"/>
-      <c r="AC6" s="56"/>
-      <c r="AD6" s="57"/>
-      <c r="AE6" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF6" s="55"/>
-      <c r="AG6" s="56"/>
-      <c r="AH6" s="56"/>
-      <c r="AI6" s="54" t="s">
+      <c r="AN6" s="61"/>
+      <c r="AO6" s="62"/>
+      <c r="AP6" s="63"/>
+      <c r="AQ6" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="AR6" s="61"/>
+      <c r="AS6" s="62"/>
+      <c r="AT6" s="64"/>
+      <c r="AU6" s="65" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV6" s="66"/>
+      <c r="AW6" s="67"/>
+      <c r="AX6" s="68"/>
+      <c r="AY6" s="71" t="s">
+        <v>0</v>
+      </c>
+      <c r="AZ6" s="73" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA6" s="81" t="s">
+        <v>35</v>
+      </c>
+      <c r="BB6" s="79"/>
+      <c r="BC6" s="79"/>
+      <c r="BD6" s="79"/>
+      <c r="BE6" s="81" t="s">
+        <v>36</v>
+      </c>
+      <c r="BF6" s="79"/>
+      <c r="BG6" s="79"/>
+      <c r="BH6" s="79"/>
+      <c r="BI6" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="BJ6" s="61"/>
+      <c r="BK6" s="62"/>
+      <c r="BL6" s="64"/>
+      <c r="BM6" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="BN6" s="79"/>
+      <c r="BO6" s="79"/>
+      <c r="BP6" s="79"/>
+      <c r="BQ6" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="BR6" s="79"/>
+      <c r="BS6" s="79"/>
+      <c r="BT6" s="82"/>
+      <c r="BU6" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="BV6" s="79"/>
+      <c r="BW6" s="79"/>
+      <c r="BX6" s="79"/>
+      <c r="BY6" s="60" t="s">
         <v>6</v>
       </c>
-      <c r="AJ6" s="55"/>
-      <c r="AK6" s="56"/>
-      <c r="AL6" s="56"/>
-      <c r="AM6" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="AN6" s="55"/>
-      <c r="AO6" s="56"/>
-      <c r="AP6" s="75"/>
-      <c r="AQ6" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="AR6" s="55"/>
-      <c r="AS6" s="56"/>
-      <c r="AT6" s="57"/>
-      <c r="AU6" s="76" t="s">
-        <v>8</v>
-      </c>
-      <c r="AV6" s="77"/>
-      <c r="AW6" s="78"/>
-      <c r="AX6" s="79"/>
-      <c r="AY6" s="66" t="s">
-        <v>0</v>
-      </c>
-      <c r="AZ6" s="68" t="s">
-        <v>1</v>
-      </c>
-      <c r="BA6" s="60" t="s">
-        <v>17</v>
-      </c>
-      <c r="BB6" s="53"/>
-      <c r="BC6" s="53"/>
-      <c r="BD6" s="53"/>
-      <c r="BE6" s="60" t="s">
-        <v>10</v>
-      </c>
-      <c r="BF6" s="53"/>
-      <c r="BG6" s="53"/>
-      <c r="BH6" s="53"/>
-      <c r="BI6" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="BJ6" s="55"/>
-      <c r="BK6" s="56"/>
-      <c r="BL6" s="57"/>
-      <c r="BM6" s="60" t="s">
-        <v>6</v>
-      </c>
-      <c r="BN6" s="53"/>
-      <c r="BO6" s="53"/>
-      <c r="BP6" s="53"/>
-      <c r="BQ6" s="60" t="s">
-        <v>33</v>
-      </c>
-      <c r="BR6" s="53"/>
-      <c r="BS6" s="53"/>
-      <c r="BT6" s="61"/>
-      <c r="BU6" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="BV6" s="53"/>
-      <c r="BW6" s="53"/>
-      <c r="BX6" s="53"/>
-      <c r="BY6" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="BZ6" s="55"/>
-      <c r="CA6" s="56"/>
-      <c r="CB6" s="57"/>
+      <c r="BZ6" s="61"/>
+      <c r="CA6" s="62"/>
+      <c r="CB6" s="64"/>
     </row>
     <row r="7" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A7" s="67"/>
-      <c r="B7" s="69"/>
+      <c r="A7" s="72"/>
+      <c r="B7" s="74"/>
       <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="R7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="X7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Y7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AG7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AH7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AJ7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AK7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AL7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AN7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AP7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="AR7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AS7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AT7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="AU7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="AV7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="AW7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="AX7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AY7" s="72"/>
+      <c r="AZ7" s="74"/>
+      <c r="BA7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BB7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="BC7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="BD7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="2" t="s">
+      <c r="BE7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="BH7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="M7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="BI7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BJ7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="BL7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="R7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="S7" s="2" t="s">
+      <c r="BM7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BN7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="BO7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="T7" s="3" t="s">
+      <c r="BP7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="U7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="V7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="W7" s="2" t="s">
+      <c r="BQ7" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BR7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="BS7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="X7" s="3" t="s">
+      <c r="BT7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="Y7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA7" s="2" t="s">
+      <c r="BU7" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BV7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="BW7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="AB7" s="3" t="s">
+      <c r="BX7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="AC7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE7" s="2" t="s">
+      <c r="BY7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BZ7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="CA7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AF7" s="3" t="s">
+      <c r="CB7" s="5" t="s">
         <v>26</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AH7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AJ7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AK7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="AM7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AN7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AO7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AP7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="AQ7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AR7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AS7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="AT7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="AV7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AW7" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="AX7" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="AY7" s="67"/>
-      <c r="AZ7" s="69"/>
-      <c r="BA7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BB7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BC7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BD7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="BE7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="BF7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BG7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BH7" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="BI7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="BJ7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="BK7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="BL7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="BM7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BN7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BO7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BP7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="BQ7" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="BR7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BS7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BT7" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="BU7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="BV7" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="BW7" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="BX7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="BY7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="BZ7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="CA7" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="CB7" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.25">
@@ -7601,10 +7604,10 @@
       </c>
     </row>
     <row r="38" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A38" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="B38" s="71"/>
+      <c r="A38" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="76"/>
       <c r="C38" s="33" t="str">
         <f t="shared" ref="C38:AX38" si="29">IF(SUM(C8:C37)=0,"",AVERAGE(C8:C37))</f>
         <v/>
@@ -7797,10 +7800,10 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="AY38" s="70" t="s">
-        <v>11</v>
-      </c>
-      <c r="AZ38" s="71"/>
+      <c r="AY38" s="75" t="s">
+        <v>10</v>
+      </c>
+      <c r="AZ38" s="76"/>
       <c r="BA38" s="33" t="str">
         <f t="shared" ref="BA38:BL38" si="30">IF(SUM(BA8:BA37)=0,"",AVERAGE(BA8:BA37))</f>
         <v/>
@@ -7915,10 +7918,10 @@
       </c>
     </row>
     <row r="39" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A39" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="B39" s="63"/>
+      <c r="A39" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="78"/>
       <c r="C39" s="33" t="str">
         <f t="shared" ref="C39:AX39" si="33">IF(SUM(C8:C37)=0,"",MEDIAN(C8:C37))</f>
         <v/>
@@ -8111,10 +8114,10 @@
         <f t="shared" si="33"/>
         <v/>
       </c>
-      <c r="AY39" s="62" t="s">
-        <v>12</v>
-      </c>
-      <c r="AZ39" s="63"/>
+      <c r="AY39" s="77" t="s">
+        <v>11</v>
+      </c>
+      <c r="AZ39" s="78"/>
       <c r="BA39" s="33" t="str">
         <f t="shared" ref="BA39:BL39" si="34">IF(SUM(BA8:BA37)=0,"",MEDIAN(BA8:BA37))</f>
         <v/>
@@ -8229,10 +8232,10 @@
       </c>
     </row>
     <row r="40" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A40" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="63"/>
+      <c r="A40" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" s="78"/>
       <c r="C40" s="33" t="str">
         <f t="shared" ref="C40:AX40" si="37">IF(SUM(C8:C37)=0,"",MAX(C8:C37))</f>
         <v/>
@@ -8425,10 +8428,10 @@
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="AY40" s="62" t="s">
-        <v>13</v>
-      </c>
-      <c r="AZ40" s="63"/>
+      <c r="AY40" s="77" t="s">
+        <v>12</v>
+      </c>
+      <c r="AZ40" s="78"/>
       <c r="BA40" s="33" t="str">
         <f t="shared" ref="BA40:BL40" si="38">IF(SUM(BA8:BA37)=0,"",MAX(BA8:BA37))</f>
         <v/>
@@ -8543,10 +8546,10 @@
       </c>
     </row>
     <row r="41" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A41" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="63"/>
+      <c r="A41" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="78"/>
       <c r="C41" s="33" t="str">
         <f t="shared" ref="C41:AX41" si="41">IF(SUM(C8:C37)=0,"",MIN(C8:C37))</f>
         <v/>
@@ -8739,10 +8742,10 @@
         <f t="shared" si="41"/>
         <v/>
       </c>
-      <c r="AY41" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="AZ41" s="63"/>
+      <c r="AY41" s="77" t="s">
+        <v>13</v>
+      </c>
+      <c r="AZ41" s="78"/>
       <c r="BA41" s="33" t="str">
         <f t="shared" ref="BA41:BL41" si="42">IF(SUM(BA8:BA37)=0,"",MIN(BA8:BA37))</f>
         <v/>
@@ -8857,10 +8860,10 @@
       </c>
     </row>
     <row r="42" spans="1:80" x14ac:dyDescent="0.25">
-      <c r="A42" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" s="65"/>
+      <c r="A42" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="70"/>
       <c r="C42" s="2" t="str">
         <f t="shared" ref="C42:AX42" si="45">IF(C38="","",COUNTIF(C8:C37,"&lt;51")/COUNT(C8:C37)*100)</f>
         <v/>
@@ -9053,10 +9056,10 @@
         <f t="shared" si="45"/>
         <v/>
       </c>
-      <c r="AY42" s="64" t="s">
-        <v>15</v>
-      </c>
-      <c r="AZ42" s="65"/>
+      <c r="AY42" s="69" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ42" s="70"/>
       <c r="BA42" s="2" t="str">
         <f t="shared" ref="BA42:BL42" si="46">IF(BA38="","",COUNTIF(BA8:BA37,"&lt;51")/COUNT(BA8:BA37)*100)</f>
         <v/>
@@ -9476,175 +9479,196 @@
     </row>
     <row r="50" spans="1:79" ht="11.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="B51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="C51" s="80"/>
-      <c r="D51" s="80"/>
-      <c r="E51" s="80"/>
-      <c r="F51" s="80"/>
-      <c r="G51" s="80"/>
+      <c r="B51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
       <c r="H51" s="52"/>
       <c r="I51" s="52"/>
       <c r="J51" s="52"/>
-      <c r="M51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="N51" s="80"/>
-      <c r="O51" s="80"/>
-      <c r="P51" s="80"/>
-      <c r="Q51" s="80"/>
-      <c r="R51" s="80"/>
-      <c r="S51" s="80"/>
-      <c r="T51" s="80"/>
-      <c r="U51" s="80"/>
-      <c r="V51" s="80"/>
-      <c r="W51" s="80"/>
-      <c r="X51" s="80"/>
+      <c r="M51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="N51" s="55"/>
+      <c r="O51" s="55"/>
+      <c r="P51" s="55"/>
+      <c r="Q51" s="55"/>
+      <c r="R51" s="55"/>
+      <c r="S51" s="55"/>
+      <c r="T51" s="55"/>
+      <c r="U51" s="55"/>
+      <c r="V51" s="55"/>
+      <c r="W51" s="55"/>
+      <c r="X51" s="55"/>
       <c r="Y51" s="52"/>
       <c r="Z51" s="52"/>
-      <c r="AD51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="AE51" s="80"/>
-      <c r="AF51" s="80"/>
-      <c r="AG51" s="80"/>
-      <c r="AH51" s="80"/>
-      <c r="AI51" s="80"/>
-      <c r="AJ51" s="80"/>
-      <c r="AK51" s="80"/>
-      <c r="AL51" s="80"/>
-      <c r="AM51" s="80"/>
-      <c r="AN51" s="80"/>
-      <c r="AO51" s="80"/>
+      <c r="AD51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AE51" s="55"/>
+      <c r="AF51" s="55"/>
+      <c r="AG51" s="55"/>
+      <c r="AH51" s="55"/>
+      <c r="AI51" s="55"/>
+      <c r="AJ51" s="55"/>
+      <c r="AK51" s="55"/>
+      <c r="AL51" s="55"/>
+      <c r="AM51" s="55"/>
+      <c r="AN51" s="55"/>
+      <c r="AO51" s="55"/>
       <c r="AP51" s="52"/>
-      <c r="AY51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="AZ51" s="80"/>
-      <c r="BA51" s="82"/>
-      <c r="BB51" s="82"/>
-      <c r="BC51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="BD51" s="80"/>
-      <c r="BE51" s="80"/>
-      <c r="BF51" s="80"/>
-      <c r="BG51" s="80"/>
-      <c r="BH51" s="80"/>
-      <c r="BI51" s="80"/>
-      <c r="BJ51" s="80"/>
-      <c r="BK51" s="80"/>
-      <c r="BL51" s="80"/>
-      <c r="BM51" s="80"/>
-      <c r="BN51" s="80"/>
-      <c r="BO51" s="82"/>
-      <c r="BP51" s="80" t="s">
-        <v>22</v>
-      </c>
-      <c r="BQ51" s="80"/>
-      <c r="BR51" s="80"/>
-      <c r="BS51" s="80"/>
-      <c r="BT51" s="80"/>
-      <c r="BU51" s="80"/>
-      <c r="BV51" s="80"/>
-      <c r="BW51" s="80"/>
-      <c r="BX51" s="80"/>
-      <c r="BY51" s="80"/>
+      <c r="AY51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="AZ51" s="55"/>
+      <c r="BA51" s="53"/>
+      <c r="BB51" s="53"/>
+      <c r="BC51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="BD51" s="55"/>
+      <c r="BE51" s="55"/>
+      <c r="BF51" s="55"/>
+      <c r="BG51" s="55"/>
+      <c r="BH51" s="55"/>
+      <c r="BI51" s="55"/>
+      <c r="BJ51" s="55"/>
+      <c r="BK51" s="55"/>
+      <c r="BL51" s="55"/>
+      <c r="BM51" s="55"/>
+      <c r="BN51" s="55"/>
+      <c r="BO51" s="53"/>
+      <c r="BP51" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="BQ51" s="55"/>
+      <c r="BR51" s="55"/>
+      <c r="BS51" s="55"/>
+      <c r="BT51" s="55"/>
+      <c r="BU51" s="55"/>
+      <c r="BV51" s="55"/>
+      <c r="BW51" s="55"/>
+      <c r="BX51" s="55"/>
+      <c r="BY51" s="55"/>
     </row>
     <row r="52" spans="1:79" x14ac:dyDescent="0.25">
-      <c r="B52" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="81"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
+      <c r="B52" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="54"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="54"/>
       <c r="H52" s="52"/>
       <c r="I52" s="52"/>
       <c r="J52" s="52"/>
-      <c r="M52" s="81" t="s">
-        <v>23</v>
-      </c>
-      <c r="N52" s="81"/>
-      <c r="O52" s="81"/>
-      <c r="P52" s="81"/>
-      <c r="Q52" s="81"/>
-      <c r="R52" s="81"/>
-      <c r="S52" s="81"/>
-      <c r="T52" s="81"/>
-      <c r="U52" s="81"/>
-      <c r="V52" s="81"/>
-      <c r="W52" s="81"/>
-      <c r="X52" s="81"/>
+      <c r="M52" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="N52" s="54"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="54"/>
+      <c r="Q52" s="54"/>
+      <c r="R52" s="54"/>
+      <c r="S52" s="54"/>
+      <c r="T52" s="54"/>
+      <c r="U52" s="54"/>
+      <c r="V52" s="54"/>
+      <c r="W52" s="54"/>
+      <c r="X52" s="54"/>
       <c r="Y52" s="52"/>
       <c r="Z52" s="52"/>
-      <c r="AD52" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="AE52" s="81"/>
-      <c r="AF52" s="81"/>
-      <c r="AG52" s="81"/>
-      <c r="AH52" s="81"/>
-      <c r="AI52" s="81"/>
-      <c r="AJ52" s="81"/>
-      <c r="AK52" s="81"/>
-      <c r="AL52" s="81"/>
-      <c r="AM52" s="81"/>
-      <c r="AN52" s="81"/>
-      <c r="AO52" s="81"/>
+      <c r="AD52" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="AE52" s="54"/>
+      <c r="AF52" s="54"/>
+      <c r="AG52" s="54"/>
+      <c r="AH52" s="54"/>
+      <c r="AI52" s="54"/>
+      <c r="AJ52" s="54"/>
+      <c r="AK52" s="54"/>
+      <c r="AL52" s="54"/>
+      <c r="AM52" s="54"/>
+      <c r="AN52" s="54"/>
+      <c r="AO52" s="54"/>
       <c r="AP52" s="52"/>
       <c r="AW52" t="s">
-        <v>37</v>
-      </c>
-      <c r="AY52" s="81" t="s">
-        <v>36</v>
-      </c>
-      <c r="AZ52" s="81"/>
+        <v>33</v>
+      </c>
+      <c r="AY52" s="54" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ52" s="54"/>
       <c r="BA52" s="52"/>
       <c r="BB52" s="52"/>
-      <c r="BC52" s="81" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD52" s="81"/>
-      <c r="BE52" s="81"/>
-      <c r="BF52" s="81"/>
-      <c r="BG52" s="81"/>
-      <c r="BH52" s="81"/>
-      <c r="BI52" s="81"/>
-      <c r="BJ52" s="81"/>
-      <c r="BK52" s="81"/>
-      <c r="BL52" s="81"/>
-      <c r="BM52" s="81"/>
-      <c r="BN52" s="81"/>
+      <c r="BC52" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="BD52" s="54"/>
+      <c r="BE52" s="54"/>
+      <c r="BF52" s="54"/>
+      <c r="BG52" s="54"/>
+      <c r="BH52" s="54"/>
+      <c r="BI52" s="54"/>
+      <c r="BJ52" s="54"/>
+      <c r="BK52" s="54"/>
+      <c r="BL52" s="54"/>
+      <c r="BM52" s="54"/>
+      <c r="BN52" s="54"/>
       <c r="BO52" s="52"/>
-      <c r="BP52" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="BQ52" s="81"/>
-      <c r="BR52" s="81"/>
-      <c r="BS52" s="81"/>
-      <c r="BT52" s="81"/>
-      <c r="BU52" s="81"/>
-      <c r="BV52" s="81"/>
-      <c r="BW52" s="81"/>
-      <c r="BX52" s="81"/>
-      <c r="BY52" s="81"/>
+      <c r="BP52" s="54" t="s">
+        <v>22</v>
+      </c>
+      <c r="BQ52" s="54"/>
+      <c r="BR52" s="54"/>
+      <c r="BS52" s="54"/>
+      <c r="BT52" s="54"/>
+      <c r="BU52" s="54"/>
+      <c r="BV52" s="54"/>
+      <c r="BW52" s="54"/>
+      <c r="BX52" s="54"/>
+      <c r="BY52" s="54"/>
       <c r="CA52" s="51" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="M52:X52"/>
-    <mergeCell ref="AD52:AO52"/>
-    <mergeCell ref="AY51:AZ51"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="M51:X51"/>
-    <mergeCell ref="AD51:AO51"/>
-    <mergeCell ref="AY52:AZ52"/>
+    <mergeCell ref="BU6:BX6"/>
+    <mergeCell ref="BY6:CB6"/>
+    <mergeCell ref="AY2:CB2"/>
+    <mergeCell ref="AY3:CB3"/>
+    <mergeCell ref="AY4:CB4"/>
+    <mergeCell ref="AY5:CB5"/>
+    <mergeCell ref="BA6:BD6"/>
+    <mergeCell ref="BE6:BH6"/>
+    <mergeCell ref="BI6:BL6"/>
+    <mergeCell ref="BM6:BP6"/>
+    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="AY41:AZ41"/>
+    <mergeCell ref="AY42:AZ42"/>
+    <mergeCell ref="AY6:AY7"/>
+    <mergeCell ref="AZ6:AZ7"/>
+    <mergeCell ref="AY38:AZ38"/>
+    <mergeCell ref="AY39:AZ39"/>
+    <mergeCell ref="AY40:AZ40"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AE6:AH6"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A41:B41"/>
     <mergeCell ref="BP51:BY51"/>
     <mergeCell ref="BP52:BY52"/>
     <mergeCell ref="BC51:BN51"/>
@@ -9661,35 +9685,14 @@
     <mergeCell ref="S6:V6"/>
     <mergeCell ref="W6:Z6"/>
     <mergeCell ref="AI6:AL6"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AE6:AH6"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="AY41:AZ41"/>
-    <mergeCell ref="AY42:AZ42"/>
-    <mergeCell ref="AY6:AY7"/>
-    <mergeCell ref="AZ6:AZ7"/>
-    <mergeCell ref="AY38:AZ38"/>
-    <mergeCell ref="AY39:AZ39"/>
-    <mergeCell ref="AY40:AZ40"/>
-    <mergeCell ref="BU6:BX6"/>
-    <mergeCell ref="BY6:CB6"/>
-    <mergeCell ref="AY2:CB2"/>
-    <mergeCell ref="AY3:CB3"/>
-    <mergeCell ref="AY4:CB4"/>
-    <mergeCell ref="AY5:CB5"/>
-    <mergeCell ref="BA6:BD6"/>
-    <mergeCell ref="BE6:BH6"/>
-    <mergeCell ref="BI6:BL6"/>
-    <mergeCell ref="BM6:BP6"/>
-    <mergeCell ref="BQ6:BT6"/>
+    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="M52:X52"/>
+    <mergeCell ref="AD52:AO52"/>
+    <mergeCell ref="AY51:AZ51"/>
+    <mergeCell ref="B51:G51"/>
+    <mergeCell ref="M51:X51"/>
+    <mergeCell ref="AD51:AO51"/>
+    <mergeCell ref="AY52:AZ52"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:AX37 BA8:BL37">
     <cfRule type="cellIs" dxfId="3" priority="5" operator="between">
